--- a/Assets/ExcelSource/Localization.xlsx
+++ b/Assets/ExcelSource/Localization.xlsx
@@ -79528,6 +79528,2121 @@
         </is>
       </c>
     </row>
+    <row r="2950">
+      <c r="A2950" t="inlineStr">
+        <is>
+          <t>ui.assets.project.scripts.battlecharacterpanelui.text.49c2150e</t>
+        </is>
+      </c>
+      <c r="C2950" t="inlineStr">
+        <is>
+          <t>이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="2951">
+      <c r="A2951" t="inlineStr">
+        <is>
+          <t>ui.assets.project.scripts.battlemonsterinfopanelui.text.49c2150e</t>
+        </is>
+      </c>
+      <c r="C2951" t="inlineStr">
+        <is>
+          <t>이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="2952">
+      <c r="A2952" t="inlineStr">
+        <is>
+          <t>ui.assets.project.scripts.battlemonsterinfopanelui.text.90b997a9</t>
+        </is>
+      </c>
+      <c r="C2952" t="inlineStr">
+        <is>
+          <t>원한</t>
+        </is>
+      </c>
+    </row>
+    <row r="2953">
+      <c r="A2953" t="inlineStr">
+        <is>
+          <t>ui.assets.project.scripts.battlemonsterinfopanelui.text.fc777a3e</t>
+        </is>
+      </c>
+      <c r="C2953" t="inlineStr">
+        <is>
+          <t>침식</t>
+        </is>
+      </c>
+    </row>
+    <row r="2954">
+      <c r="A2954" t="inlineStr">
+        <is>
+          <t>ui.assets.project.scripts.battlemonsterinfopanelui.text.3e65f5bf</t>
+        </is>
+      </c>
+      <c r="C2954" t="inlineStr">
+        <is>
+          <t>거미알 생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="2955">
+      <c r="A2955" t="inlineStr">
+        <is>
+          <t>ui.assets.project.scripts.battlemonsterinfopanelui.text.e407a267</t>
+        </is>
+      </c>
+      <c r="C2955" t="inlineStr">
+        <is>
+          <t>거미줄 생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="2956">
+      <c r="A2956" t="inlineStr">
+        <is>
+          <t>ui.assets.project.scripts.battlemonsterinfopanelui.text.369422cb</t>
+        </is>
+      </c>
+      <c r="C2956" t="inlineStr">
+        <is>
+          <t>장막</t>
+        </is>
+      </c>
+    </row>
+    <row r="2957">
+      <c r="A2957" t="inlineStr">
+        <is>
+          <t>ui.assets.project.scripts.core.managers.uimanager.text.9c8a9f7f</t>
+        </is>
+      </c>
+      <c r="C2957" t="inlineStr">
+        <is>
+          <t>아니오</t>
+        </is>
+      </c>
+    </row>
+    <row r="2958">
+      <c r="A2958" t="inlineStr">
+        <is>
+          <t>ui.assets.project.scripts.gameplay.scene.battle.battleroom.timeline.battletimelinecontroller.text.027a793c</t>
+        </is>
+      </c>
+      <c r="C2958" t="inlineStr">
+        <is>
+          <t>방어도</t>
+        </is>
+      </c>
+    </row>
+    <row r="2959">
+      <c r="A2959" t="inlineStr">
+        <is>
+          <t>ui.assets.project.scripts.gameplay.scene.battle.eventroom.eventroomcontroller.text.9516c5ee</t>
+        </is>
+      </c>
+      <c r="C2959" t="inlineStr">
+        <is>
+          <t>기억</t>
+        </is>
+      </c>
+    </row>
+    <row r="2960">
+      <c r="A2960" t="inlineStr">
+        <is>
+          <t>ui.assets.project.scripts.gameplay.scene.battle.restroom.goodsiconitem.text.9516c5ee</t>
+        </is>
+      </c>
+      <c r="C2960" t="inlineStr">
+        <is>
+          <t>기억</t>
+        </is>
+      </c>
+    </row>
+    <row r="2961">
+      <c r="A2961" t="inlineStr">
+        <is>
+          <t>ui.assets.project.scripts.ui.battlebagpanelui.text.1e43e60e</t>
+        </is>
+      </c>
+      <c r="C2961" t="inlineStr">
+        <is>
+          <t>?띾뱷???꾩씠?쒖엯?덈떎.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2962">
+      <c r="A2962" t="inlineStr">
+        <is>
+          <t>ui.assets.project.scripts.ui.battlebagpanelui.text.201cadd4</t>
+        </is>
+      </c>
+      <c r="C2962" t="inlineStr">
+        <is>
+          <t>硫??諛고??먯꽌???몄뒪?몃쭔 媛諛⑹쓣 蹂寃쏀븷 ???덉뒿?덈떎.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2963">
+      <c r="A2963" t="inlineStr">
+        <is>
+          <t>ui.assets.project.scripts.ui.battlebagpanelui.text.a718dfdb</t>
+        </is>
+      </c>
+      <c r="C2963" t="inlineStr">
+        <is>
+          <t>踰꾨┫ 怨좎쑀?꾩씠?쒖쓣 癒쇱? ?좏깮?댁＜?몄슂.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2964">
+      <c r="A2964" t="inlineStr">
+        <is>
+          <t>ui.assets.project.scripts.ui.battlebagpanelui.text.92f17ad9</t>
+        </is>
+      </c>
+      <c r="C2964" t="inlineStr">
+        <is>
+          <t>?좏깮??怨좎쑀?꾩씠?쒖쓣 李얠쓣 ???놁뒿?덈떎.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2965">
+      <c r="A2965" t="inlineStr">
+        <is>
+          <t>ui.assets.project.scripts.ui.battlebagpanelui.text.c3c4d2b6</t>
+        </is>
+      </c>
+      <c r="C2965" t="inlineStr">
+        <is>
+          <t>[BattleBagPanelUI] 怨좎쑀?꾩씠?쒖쓣 踰꾨졇?듬땲?? Item:{removedItemId}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2966">
+      <c r="A2966" t="inlineStr">
+        <is>
+          <t>data.character.char_02.name.9d766d0d</t>
+        </is>
+      </c>
+      <c r="C2966" t="inlineStr">
+        <is>
+          <t>카야</t>
+        </is>
+      </c>
+    </row>
+    <row r="2967">
+      <c r="A2967" t="inlineStr">
+        <is>
+          <t>data.skillmaster.s_move_1.name</t>
+        </is>
+      </c>
+      <c r="C2967" t="inlineStr">
+        <is>
+          <t>이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="2968">
+      <c r="A2968" t="inlineStr">
+        <is>
+          <t>data.skillmaster.s_core_61.name</t>
+        </is>
+      </c>
+      <c r="C2968" t="inlineStr">
+        <is>
+          <t>위압</t>
+        </is>
+      </c>
+    </row>
+    <row r="2969">
+      <c r="A2969" t="inlineStr">
+        <is>
+          <t>data.skillmaster.s_core_62.name</t>
+        </is>
+      </c>
+      <c r="C2969" t="inlineStr">
+        <is>
+          <t>위압+</t>
+        </is>
+      </c>
+    </row>
+    <row r="2970">
+      <c r="A2970" t="inlineStr">
+        <is>
+          <t>data.skillmaster.s_core_63.name</t>
+        </is>
+      </c>
+      <c r="C2970" t="inlineStr">
+        <is>
+          <t>공격태세</t>
+        </is>
+      </c>
+    </row>
+    <row r="2971">
+      <c r="A2971" t="inlineStr">
+        <is>
+          <t>data.skillmaster.s_core_64.name</t>
+        </is>
+      </c>
+      <c r="C2971" t="inlineStr">
+        <is>
+          <t>공격태세+</t>
+        </is>
+      </c>
+    </row>
+    <row r="2972">
+      <c r="A2972" t="inlineStr">
+        <is>
+          <t>data.skillmaster.s_core_65.name</t>
+        </is>
+      </c>
+      <c r="C2972" t="inlineStr">
+        <is>
+          <t>틈새베기</t>
+        </is>
+      </c>
+    </row>
+    <row r="2973">
+      <c r="A2973" t="inlineStr">
+        <is>
+          <t>data.skillmaster.s_core_66.name</t>
+        </is>
+      </c>
+      <c r="C2973" t="inlineStr">
+        <is>
+          <t>틈새베기+</t>
+        </is>
+      </c>
+    </row>
+    <row r="2974">
+      <c r="A2974" t="inlineStr">
+        <is>
+          <t>data.skillmaster.s_core_67.name</t>
+        </is>
+      </c>
+      <c r="C2974" t="inlineStr">
+        <is>
+          <t>숨돌리기</t>
+        </is>
+      </c>
+    </row>
+    <row r="2975">
+      <c r="A2975" t="inlineStr">
+        <is>
+          <t>data.skillmaster.s_core_68.name</t>
+        </is>
+      </c>
+      <c r="C2975" t="inlineStr">
+        <is>
+          <t>숨돌리기+</t>
+        </is>
+      </c>
+    </row>
+    <row r="2976">
+      <c r="A2976" t="inlineStr">
+        <is>
+          <t>data.skillmaster.s_core_69.name</t>
+        </is>
+      </c>
+      <c r="C2976" t="inlineStr">
+        <is>
+          <t>밀쳐내기</t>
+        </is>
+      </c>
+    </row>
+    <row r="2977">
+      <c r="A2977" t="inlineStr">
+        <is>
+          <t>data.skillmaster.s_core_70.name</t>
+        </is>
+      </c>
+      <c r="C2977" t="inlineStr">
+        <is>
+          <t>밀쳐내기+</t>
+        </is>
+      </c>
+    </row>
+    <row r="2978">
+      <c r="A2978" t="inlineStr">
+        <is>
+          <t>data.skillmaster.s_core_71.name</t>
+        </is>
+      </c>
+      <c r="C2978" t="inlineStr">
+        <is>
+          <t>격려</t>
+        </is>
+      </c>
+    </row>
+    <row r="2979">
+      <c r="A2979" t="inlineStr">
+        <is>
+          <t>data.skillmaster.s_core_72.name</t>
+        </is>
+      </c>
+      <c r="C2979" t="inlineStr">
+        <is>
+          <t>격려+</t>
+        </is>
+      </c>
+    </row>
+    <row r="2980">
+      <c r="A2980" t="inlineStr">
+        <is>
+          <t>data.skillmaster.s_core_73.name</t>
+        </is>
+      </c>
+      <c r="C2980" t="inlineStr">
+        <is>
+          <t>버티기</t>
+        </is>
+      </c>
+    </row>
+    <row r="2981">
+      <c r="A2981" t="inlineStr">
+        <is>
+          <t>data.skillmaster.s_core_74.name</t>
+        </is>
+      </c>
+      <c r="C2981" t="inlineStr">
+        <is>
+          <t>버티기+</t>
+        </is>
+      </c>
+    </row>
+    <row r="2982">
+      <c r="A2982" t="inlineStr">
+        <is>
+          <t>data.skillmaster.s_core_75.name</t>
+        </is>
+      </c>
+      <c r="C2982" t="inlineStr">
+        <is>
+          <t>끌어당기기</t>
+        </is>
+      </c>
+    </row>
+    <row r="2983">
+      <c r="A2983" t="inlineStr">
+        <is>
+          <t>data.skillmaster.s_core_76.name</t>
+        </is>
+      </c>
+      <c r="C2983" t="inlineStr">
+        <is>
+          <t>끌어당기기+</t>
+        </is>
+      </c>
+    </row>
+    <row r="2984">
+      <c r="A2984" t="inlineStr">
+        <is>
+          <t>data.skillmaster.s_core_77.name</t>
+        </is>
+      </c>
+      <c r="C2984" t="inlineStr">
+        <is>
+          <t>블러드피어스</t>
+        </is>
+      </c>
+    </row>
+    <row r="2985">
+      <c r="A2985" t="inlineStr">
+        <is>
+          <t>data.skillmaster.s_core_78.name</t>
+        </is>
+      </c>
+      <c r="C2985" t="inlineStr">
+        <is>
+          <t>블러드피어스+</t>
+        </is>
+      </c>
+    </row>
+    <row r="2986">
+      <c r="A2986" t="inlineStr">
+        <is>
+          <t>data.skillmaster.s_core_79.name</t>
+        </is>
+      </c>
+      <c r="C2986" t="inlineStr">
+        <is>
+          <t>스피드스터</t>
+        </is>
+      </c>
+    </row>
+    <row r="2987">
+      <c r="A2987" t="inlineStr">
+        <is>
+          <t>data.skillmaster.s_core_80.name</t>
+        </is>
+      </c>
+      <c r="C2987" t="inlineStr">
+        <is>
+          <t>스피드스터+</t>
+        </is>
+      </c>
+    </row>
+    <row r="2988">
+      <c r="A2988" t="inlineStr">
+        <is>
+          <t>data.monsterskill.s_monster_01.name</t>
+        </is>
+      </c>
+      <c r="C2988" t="inlineStr">
+        <is>
+          <t>이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="2989">
+      <c r="A2989" t="inlineStr">
+        <is>
+          <t>data.monsterskill.s_monster_01.effect_description</t>
+        </is>
+      </c>
+      <c r="C2989" t="inlineStr">
+        <is>
+          <t>가까운 캐릭터 주변으로 1칸 이동한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2990">
+      <c r="A2990" t="inlineStr">
+        <is>
+          <t>data.monsterskill.s_monster_03.name</t>
+        </is>
+      </c>
+      <c r="C2990" t="inlineStr">
+        <is>
+          <t>이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="2991">
+      <c r="A2991" t="inlineStr">
+        <is>
+          <t>data.monsterskill.s_monster_03.effect_description</t>
+        </is>
+      </c>
+      <c r="C2991" t="inlineStr">
+        <is>
+          <t>가까운 캐릭터를 향해 1칸 이동한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2992">
+      <c r="A2992" t="inlineStr">
+        <is>
+          <t>data.monsterskill.s_monster_04.effect_description</t>
+        </is>
+      </c>
+      <c r="C2992" t="inlineStr">
+        <is>
+          <t>대상에게 {ValueRate1}의 피해를 준다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2993">
+      <c r="A2993" t="inlineStr">
+        <is>
+          <t>data.monsterskill.s_monster_05.name</t>
+        </is>
+      </c>
+      <c r="C2993" t="inlineStr">
+        <is>
+          <t>이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="2994">
+      <c r="A2994" t="inlineStr">
+        <is>
+          <t>data.monsterskill.s_monster_05.effect_description</t>
+        </is>
+      </c>
+      <c r="C2994" t="inlineStr">
+        <is>
+          <t>범위 내에 캐릭터가 들어오면 2칸 도망간다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2995">
+      <c r="A2995" t="inlineStr">
+        <is>
+          <t>data.monsterskill.s_monster_06.effect_description</t>
+        </is>
+      </c>
+      <c r="C2995" t="inlineStr">
+        <is>
+          <t>주변에 {ValueRate1}의 피해를 준다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2996">
+      <c r="A2996" t="inlineStr">
+        <is>
+          <t>data.monsterskill.s_monster_08.name</t>
+        </is>
+      </c>
+      <c r="C2996" t="inlineStr">
+        <is>
+          <t>이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="2997">
+      <c r="A2997" t="inlineStr">
+        <is>
+          <t>data.monsterskill.s_monster_08.effect_description</t>
+        </is>
+      </c>
+      <c r="C2997" t="inlineStr">
+        <is>
+          <t>범위 내에 캐릭터가 들어오면 2칸 도망간다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2998">
+      <c r="A2998" t="inlineStr">
+        <is>
+          <t>data.monsterskill.s_monster_09.effect_description</t>
+        </is>
+      </c>
+      <c r="C2998" t="inlineStr">
+        <is>
+          <t>주변에 {ValueRate1}의 피해를 준다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2999">
+      <c r="A2999" t="inlineStr">
+        <is>
+          <t>data.monsterskill.s_monster_11.name</t>
+        </is>
+      </c>
+      <c r="C2999" t="inlineStr">
+        <is>
+          <t>이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="3000">
+      <c r="A3000" t="inlineStr">
+        <is>
+          <t>data.monsterskill.s_monster_13.name</t>
+        </is>
+      </c>
+      <c r="C3000" t="inlineStr">
+        <is>
+          <t>이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="3001">
+      <c r="A3001" t="inlineStr">
+        <is>
+          <t>data.monsterskill.s_monster_13.effect_description</t>
+        </is>
+      </c>
+      <c r="C3001" t="inlineStr">
+        <is>
+          <t>가까운 캐릭터 주변으로 1칸 이동한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3002">
+      <c r="A3002" t="inlineStr">
+        <is>
+          <t>data.monsterskill.s_monster_15.name</t>
+        </is>
+      </c>
+      <c r="C3002" t="inlineStr">
+        <is>
+          <t>이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="3003">
+      <c r="A3003" t="inlineStr">
+        <is>
+          <t>data.monsterskill.s_monster_15.effect_description</t>
+        </is>
+      </c>
+      <c r="C3003" t="inlineStr">
+        <is>
+          <t>가까운 캐릭터 주변으로 1칸 이동한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3004">
+      <c r="A3004" t="inlineStr">
+        <is>
+          <t>data.monsterskill.s_monster_18.effect_description</t>
+        </is>
+      </c>
+      <c r="C3004" t="inlineStr">
+        <is>
+          <t>대상에게 {ValueRate1}의 피해를 준다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3005">
+      <c r="A3005" t="inlineStr">
+        <is>
+          <t>data.monsterskill.s_monster_20.name</t>
+        </is>
+      </c>
+      <c r="C3005" t="inlineStr">
+        <is>
+          <t>이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="3006">
+      <c r="A3006" t="inlineStr">
+        <is>
+          <t>data.monsterskill.s_monster_21.effect_description</t>
+        </is>
+      </c>
+      <c r="C3006" t="inlineStr">
+        <is>
+          <t>주변에 {ValueRate1}의 피해를 준다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3007">
+      <c r="A3007" t="inlineStr">
+        <is>
+          <t>data.monsterskill.s_monster_26.name</t>
+        </is>
+      </c>
+      <c r="C3007" t="inlineStr">
+        <is>
+          <t>이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="3008">
+      <c r="A3008" t="inlineStr">
+        <is>
+          <t>data.monsterskill.s_monster_27.effect_description</t>
+        </is>
+      </c>
+      <c r="C3008" t="inlineStr">
+        <is>
+          <t>대상에게 {ValueRate1}의 피해를 준다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3009">
+      <c r="A3009" t="inlineStr">
+        <is>
+          <t>data.monsterskill.s_monster_29.name</t>
+        </is>
+      </c>
+      <c r="C3009" t="inlineStr">
+        <is>
+          <t>이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="3010">
+      <c r="A3010" t="inlineStr">
+        <is>
+          <t>data.monsterskill.s_monster_30.effect_description</t>
+        </is>
+      </c>
+      <c r="C3010" t="inlineStr">
+        <is>
+          <t>대상에게 {ValueRate1}의 피해를 준다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3011">
+      <c r="A3011" t="inlineStr">
+        <is>
+          <t>data.monsterskill.s_monster_32.name</t>
+        </is>
+      </c>
+      <c r="C3011" t="inlineStr">
+        <is>
+          <t>이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="3012">
+      <c r="A3012" t="inlineStr">
+        <is>
+          <t>data.monsterskill.s_monster_32.effect_description</t>
+        </is>
+      </c>
+      <c r="C3012" t="inlineStr">
+        <is>
+          <t>가까운 캐릭터를 향해 1칸 이동한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3013">
+      <c r="A3013" t="inlineStr">
+        <is>
+          <t>data.monsterskill.s_monster_37.name</t>
+        </is>
+      </c>
+      <c r="C3013" t="inlineStr">
+        <is>
+          <t>이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="3014">
+      <c r="A3014" t="inlineStr">
+        <is>
+          <t>data.monsterskill.s_monster_41.name.4ed63e62</t>
+        </is>
+      </c>
+      <c r="C3014" t="inlineStr">
+        <is>
+          <t>사령술</t>
+        </is>
+      </c>
+    </row>
+    <row r="3015">
+      <c r="A3015" t="inlineStr">
+        <is>
+          <t>data.grideffect.gr_thorn.tooltip.28721349</t>
+        </is>
+      </c>
+      <c r="C3015" t="inlineStr">
+        <is>
+          <t>대상에게 {ValueRate}의 피해를 준다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3016">
+      <c r="A3016" t="inlineStr">
+        <is>
+          <t>data.grideffect.gr_residue.tooltip.28721349</t>
+        </is>
+      </c>
+      <c r="C3016" t="inlineStr">
+        <is>
+          <t>대상에게 {ValueRate}의 피해를 준다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3017">
+      <c r="A3017" t="inlineStr">
+        <is>
+          <t>data.grideffect.gr_spider_web.name</t>
+        </is>
+      </c>
+      <c r="C3017" t="inlineStr">
+        <is>
+          <t>거미줄</t>
+        </is>
+      </c>
+    </row>
+    <row r="3018">
+      <c r="A3018" t="inlineStr">
+        <is>
+          <t>data.effect.e_move.name.49c2150e</t>
+        </is>
+      </c>
+      <c r="C3018" t="inlineStr">
+        <is>
+          <t>이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="3019">
+      <c r="A3019" t="inlineStr">
+        <is>
+          <t>data.effect.e_knockback.name.f407dc0f</t>
+        </is>
+      </c>
+      <c r="C3019" t="inlineStr">
+        <is>
+          <t>넉백</t>
+        </is>
+      </c>
+    </row>
+    <row r="3020">
+      <c r="A3020" t="inlineStr">
+        <is>
+          <t>data.effect.e_boost.name.0969adff</t>
+        </is>
+      </c>
+      <c r="C3020" t="inlineStr">
+        <is>
+          <t>증폭</t>
+        </is>
+      </c>
+    </row>
+    <row r="3021">
+      <c r="A3021" t="inlineStr">
+        <is>
+          <t>data.effect.e_armor.name.027a793c</t>
+        </is>
+      </c>
+      <c r="C3021" t="inlineStr">
+        <is>
+          <t>방어도</t>
+        </is>
+      </c>
+    </row>
+    <row r="3022">
+      <c r="A3022" t="inlineStr">
+        <is>
+          <t>data.effect.e_grudge.name.90b997a9</t>
+        </is>
+      </c>
+      <c r="C3022" t="inlineStr">
+        <is>
+          <t>원한</t>
+        </is>
+      </c>
+    </row>
+    <row r="3023">
+      <c r="A3023" t="inlineStr">
+        <is>
+          <t>data.effect.e_barrier.name.369422cb</t>
+        </is>
+      </c>
+      <c r="C3023" t="inlineStr">
+        <is>
+          <t>장막</t>
+        </is>
+      </c>
+    </row>
+    <row r="3024">
+      <c r="A3024" t="inlineStr">
+        <is>
+          <t>data.effect.e_bleed.name.41e1bbe9</t>
+        </is>
+      </c>
+      <c r="C3024" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="3025">
+      <c r="A3025" t="inlineStr">
+        <is>
+          <t>data.effect.e_corrosion.name.fc777a3e</t>
+        </is>
+      </c>
+      <c r="C3025" t="inlineStr">
+        <is>
+          <t>침식</t>
+        </is>
+      </c>
+    </row>
+    <row r="3026">
+      <c r="A3026" t="inlineStr">
+        <is>
+          <t>data.effect.e_spawn_spider_egg.name.3e65f5bf</t>
+        </is>
+      </c>
+      <c r="C3026" t="inlineStr">
+        <is>
+          <t>거미알 생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="3027">
+      <c r="A3027" t="inlineStr">
+        <is>
+          <t>data.effect.e_spawn_spider_web.name.e407a267</t>
+        </is>
+      </c>
+      <c r="C3027" t="inlineStr">
+        <is>
+          <t>거미줄 생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="3028">
+      <c r="A3028" t="inlineStr">
+        <is>
+          <t>data.effect.e_spawn_soldier.name.4ed63e62</t>
+        </is>
+      </c>
+      <c r="C3028" t="inlineStr">
+        <is>
+          <t>사령술</t>
+        </is>
+      </c>
+    </row>
+    <row r="3029">
+      <c r="A3029" t="inlineStr">
+        <is>
+          <t>data.effect.ar_damagereductionthisturn.tooltip.141b5a97</t>
+        </is>
+      </c>
+      <c r="C3029" t="inlineStr">
+        <is>
+          <t>이번 턴 동안 받는 피해가 50% 감소한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3030">
+      <c r="A3030" t="inlineStr">
+        <is>
+          <t>data.effect.ar_recovercosttomax.name.633634da</t>
+        </is>
+      </c>
+      <c r="C3030" t="inlineStr">
+        <is>
+          <t>마력 플라스크</t>
+        </is>
+      </c>
+    </row>
+    <row r="3031">
+      <c r="A3031" t="inlineStr">
+        <is>
+          <t>data.effect.ar_spawnpoisongrideffect.tooltip.314d9f46</t>
+        </is>
+      </c>
+      <c r="C3031" t="inlineStr">
+        <is>
+          <t>선택한 그리드에 독 장판을 생성한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3032">
+      <c r="A3032" t="inlineStr">
+        <is>
+          <t>data.effect.ar_spawnthorngrideffect.tooltip.3b657dfa</t>
+        </is>
+      </c>
+      <c r="C3032" t="inlineStr">
+        <is>
+          <t>선택한 그리드에 가시를 생성한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3033">
+      <c r="A3033" t="inlineStr">
+        <is>
+          <t>data.effect.ar_removegrideffect.tooltip.e4b38e89</t>
+        </is>
+      </c>
+      <c r="C3033" t="inlineStr">
+        <is>
+          <t>선택한 그리드의 장애물을 제거한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3034">
+      <c r="A3034" t="inlineStr">
+        <is>
+          <t>data.effect.ar_spawndummygrideffect.name.0fdd8c95</t>
+        </is>
+      </c>
+      <c r="C3034" t="inlineStr">
+        <is>
+          <t>호문쿨루스 루어</t>
+        </is>
+      </c>
+    </row>
+    <row r="3035">
+      <c r="A3035" t="inlineStr">
+        <is>
+          <t>data.effect.ar_spawndummygrideffect.tooltip.dffb4232</t>
+        </is>
+      </c>
+      <c r="C3035" t="inlineStr">
+        <is>
+          <t>선택한 빈 그리드에 루어를 생성한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3036">
+      <c r="A3036" t="inlineStr">
+        <is>
+          <t>data.effect.ar_spawnexplosivedollgrideffect.name.6ae4be35</t>
+        </is>
+      </c>
+      <c r="C3036" t="inlineStr">
+        <is>
+          <t>호문쿨루스 브룸</t>
+        </is>
+      </c>
+    </row>
+    <row r="3037">
+      <c r="A3037" t="inlineStr">
+        <is>
+          <t>data.effect.ar_spawnexplosivedollgrideffect.tooltip.b925bea2</t>
+        </is>
+      </c>
+      <c r="C3037" t="inlineStr">
+        <is>
+          <t>선택한 빈 그리드에 브룸을 생성한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3038">
+      <c r="A3038" t="inlineStr">
+        <is>
+          <t>data.event.event_01.name.532713e1</t>
+        </is>
+      </c>
+      <c r="C3038" t="inlineStr">
+        <is>
+          <t>세라피아의 지원</t>
+        </is>
+      </c>
+    </row>
+    <row r="3039">
+      <c r="A3039" t="inlineStr">
+        <is>
+          <t>data.event.event_01_a.name.532713e1</t>
+        </is>
+      </c>
+      <c r="C3039" t="inlineStr">
+        <is>
+          <t>세라피아의 지원</t>
+        </is>
+      </c>
+    </row>
+    <row r="3040">
+      <c r="A3040" t="inlineStr">
+        <is>
+          <t>data.event.event_01_b.name.532713e1</t>
+        </is>
+      </c>
+      <c r="C3040" t="inlineStr">
+        <is>
+          <t>세라피아의 지원</t>
+        </is>
+      </c>
+    </row>
+    <row r="3041">
+      <c r="A3041" t="inlineStr">
+        <is>
+          <t>data.event.event_01_c.name.532713e1</t>
+        </is>
+      </c>
+      <c r="C3041" t="inlineStr">
+        <is>
+          <t>세라피아의 지원</t>
+        </is>
+      </c>
+    </row>
+    <row r="3042">
+      <c r="A3042" t="inlineStr">
+        <is>
+          <t>data.event.event_02.name.d9285606</t>
+        </is>
+      </c>
+      <c r="C3042" t="inlineStr">
+        <is>
+          <t>금단의 의식</t>
+        </is>
+      </c>
+    </row>
+    <row r="3043">
+      <c r="A3043" t="inlineStr">
+        <is>
+          <t>data.event.event_02_a.name.d9285606</t>
+        </is>
+      </c>
+      <c r="C3043" t="inlineStr">
+        <is>
+          <t>금단의 의식</t>
+        </is>
+      </c>
+    </row>
+    <row r="3044">
+      <c r="A3044" t="inlineStr">
+        <is>
+          <t>data.event.event_02_b.name.d9285606</t>
+        </is>
+      </c>
+      <c r="C3044" t="inlineStr">
+        <is>
+          <t>금단의 의식</t>
+        </is>
+      </c>
+    </row>
+    <row r="3045">
+      <c r="A3045" t="inlineStr">
+        <is>
+          <t>data.event.event_02_c.name.d9285606</t>
+        </is>
+      </c>
+      <c r="C3045" t="inlineStr">
+        <is>
+          <t>금단의 의식</t>
+        </is>
+      </c>
+    </row>
+    <row r="3046">
+      <c r="A3046" t="inlineStr">
+        <is>
+          <t>data.event.event_02_d.name.d9285606</t>
+        </is>
+      </c>
+      <c r="C3046" t="inlineStr">
+        <is>
+          <t>금단의 의식</t>
+        </is>
+      </c>
+    </row>
+    <row r="3047">
+      <c r="A3047" t="inlineStr">
+        <is>
+          <t>data.event.event_02_e.name.d9285606</t>
+        </is>
+      </c>
+      <c r="C3047" t="inlineStr">
+        <is>
+          <t>금단의 의식</t>
+        </is>
+      </c>
+    </row>
+    <row r="3048">
+      <c r="A3048" t="inlineStr">
+        <is>
+          <t>data.event.event_02_f.name.d9285606</t>
+        </is>
+      </c>
+      <c r="C3048" t="inlineStr">
+        <is>
+          <t>금단의 의식</t>
+        </is>
+      </c>
+    </row>
+    <row r="3049">
+      <c r="A3049" t="inlineStr">
+        <is>
+          <t>data.event.event_02_g.name.d9285606</t>
+        </is>
+      </c>
+      <c r="C3049" t="inlineStr">
+        <is>
+          <t>금단의 의식</t>
+        </is>
+      </c>
+    </row>
+    <row r="3050">
+      <c r="A3050" t="inlineStr">
+        <is>
+          <t>data.event.event_02_h.name.d9285606</t>
+        </is>
+      </c>
+      <c r="C3050" t="inlineStr">
+        <is>
+          <t>금단의 의식</t>
+        </is>
+      </c>
+    </row>
+    <row r="3051">
+      <c r="A3051" t="inlineStr">
+        <is>
+          <t>data.event.event_02_i.name.d9285606</t>
+        </is>
+      </c>
+      <c r="C3051" t="inlineStr">
+        <is>
+          <t>금단의 의식</t>
+        </is>
+      </c>
+    </row>
+    <row r="3052">
+      <c r="A3052" t="inlineStr">
+        <is>
+          <t>data.event.event_04.name.06d54afa</t>
+        </is>
+      </c>
+      <c r="C3052" t="inlineStr">
+        <is>
+          <t>의문의 이방인</t>
+        </is>
+      </c>
+    </row>
+    <row r="3053">
+      <c r="A3053" t="inlineStr">
+        <is>
+          <t>data.event.event_04_a.name.06d54afa</t>
+        </is>
+      </c>
+      <c r="C3053" t="inlineStr">
+        <is>
+          <t>의문의 이방인</t>
+        </is>
+      </c>
+    </row>
+    <row r="3054">
+      <c r="A3054" t="inlineStr">
+        <is>
+          <t>data.event.event_04_b.name.06d54afa</t>
+        </is>
+      </c>
+      <c r="C3054" t="inlineStr">
+        <is>
+          <t>의문의 이방인</t>
+        </is>
+      </c>
+    </row>
+    <row r="3055">
+      <c r="A3055" t="inlineStr">
+        <is>
+          <t>data.event.event_04_c.name.06d54afa</t>
+        </is>
+      </c>
+      <c r="C3055" t="inlineStr">
+        <is>
+          <t>의문의 이방인</t>
+        </is>
+      </c>
+    </row>
+    <row r="3056">
+      <c r="A3056" t="inlineStr">
+        <is>
+          <t>data.event.event_04_d.name.06d54afa</t>
+        </is>
+      </c>
+      <c r="C3056" t="inlineStr">
+        <is>
+          <t>의문의 이방인</t>
+        </is>
+      </c>
+    </row>
+    <row r="3057">
+      <c r="A3057" t="inlineStr">
+        <is>
+          <t>data.event.event_05.name.ac67bf45</t>
+        </is>
+      </c>
+      <c r="C3057" t="inlineStr">
+        <is>
+          <t>더스티움 광맥</t>
+        </is>
+      </c>
+    </row>
+    <row r="3058">
+      <c r="A3058" t="inlineStr">
+        <is>
+          <t>data.event.event_05.description.73af1899</t>
+        </is>
+      </c>
+      <c r="C3058" t="inlineStr">
+        <is>
+          <t>주사위 판정 8
+레드 더스티움 15 누적</t>
+        </is>
+      </c>
+    </row>
+    <row r="3059">
+      <c r="A3059" t="inlineStr">
+        <is>
+          <t>data.event.event_05.failure_description.113898c4</t>
+        </is>
+      </c>
+      <c r="C3059" t="inlineStr">
+        <is>
+          <t>3~7: 누적 레드 더스티움 전부 소실</t>
+        </is>
+      </c>
+    </row>
+    <row r="3060">
+      <c r="A3060" t="inlineStr">
+        <is>
+          <t>data.event.event_05_a.name.ac67bf45</t>
+        </is>
+      </c>
+      <c r="C3060" t="inlineStr">
+        <is>
+          <t>더스티움 광맥</t>
+        </is>
+      </c>
+    </row>
+    <row r="3061">
+      <c r="A3061" t="inlineStr">
+        <is>
+          <t>data.event.event_05_a.description.73af1899</t>
+        </is>
+      </c>
+      <c r="C3061" t="inlineStr">
+        <is>
+          <t>주사위 판정 8
+레드 더스티움 15 누적</t>
+        </is>
+      </c>
+    </row>
+    <row r="3062">
+      <c r="A3062" t="inlineStr">
+        <is>
+          <t>data.event.event_05_a.failure_description.113898c4</t>
+        </is>
+      </c>
+      <c r="C3062" t="inlineStr">
+        <is>
+          <t>3~7: 누적 레드 더스티움 전부 소실</t>
+        </is>
+      </c>
+    </row>
+    <row r="3063">
+      <c r="A3063" t="inlineStr">
+        <is>
+          <t>data.event.event_05_b.name.ac67bf45</t>
+        </is>
+      </c>
+      <c r="C3063" t="inlineStr">
+        <is>
+          <t>더스티움 광맥</t>
+        </is>
+      </c>
+    </row>
+    <row r="3064">
+      <c r="A3064" t="inlineStr">
+        <is>
+          <t>data.event.event_05_b.description.73af1899</t>
+        </is>
+      </c>
+      <c r="C3064" t="inlineStr">
+        <is>
+          <t>주사위 판정 8
+레드 더스티움 15 누적</t>
+        </is>
+      </c>
+    </row>
+    <row r="3065">
+      <c r="A3065" t="inlineStr">
+        <is>
+          <t>data.event.event_05_b.failure_description.113898c4</t>
+        </is>
+      </c>
+      <c r="C3065" t="inlineStr">
+        <is>
+          <t>3~7: 누적 레드 더스티움 전부 소실</t>
+        </is>
+      </c>
+    </row>
+    <row r="3066">
+      <c r="A3066" t="inlineStr">
+        <is>
+          <t>data.event.event_05_c.name.ac67bf45</t>
+        </is>
+      </c>
+      <c r="C3066" t="inlineStr">
+        <is>
+          <t>더스티움 광맥</t>
+        </is>
+      </c>
+    </row>
+    <row r="3067">
+      <c r="A3067" t="inlineStr">
+        <is>
+          <t>data.event.event_05_d.name.ac67bf45</t>
+        </is>
+      </c>
+      <c r="C3067" t="inlineStr">
+        <is>
+          <t>더스티움 광맥</t>
+        </is>
+      </c>
+    </row>
+    <row r="3068">
+      <c r="A3068" t="inlineStr">
+        <is>
+          <t>data.event.event_05_e.name.ac67bf45</t>
+        </is>
+      </c>
+      <c r="C3068" t="inlineStr">
+        <is>
+          <t>더스티움 광맥</t>
+        </is>
+      </c>
+    </row>
+    <row r="3069">
+      <c r="A3069" t="inlineStr">
+        <is>
+          <t>data.event.event_06.name.54d46970</t>
+        </is>
+      </c>
+      <c r="C3069" t="inlineStr">
+        <is>
+          <t>그림자 상인</t>
+        </is>
+      </c>
+    </row>
+    <row r="3070">
+      <c r="A3070" t="inlineStr">
+        <is>
+          <t>data.event.event_06_a.name.54d46970</t>
+        </is>
+      </c>
+      <c r="C3070" t="inlineStr">
+        <is>
+          <t>그림자 상인</t>
+        </is>
+      </c>
+    </row>
+    <row r="3071">
+      <c r="A3071" t="inlineStr">
+        <is>
+          <t>data.event.event_08.name.761bd4a4</t>
+        </is>
+      </c>
+      <c r="C3071" t="inlineStr">
+        <is>
+          <t>공명의 비석</t>
+        </is>
+      </c>
+    </row>
+    <row r="3072">
+      <c r="A3072" t="inlineStr">
+        <is>
+          <t>data.event.event_08.failure_description.f775776f</t>
+        </is>
+      </c>
+      <c r="C3072" t="inlineStr">
+        <is>
+          <t>선택한 기억 소멸</t>
+        </is>
+      </c>
+    </row>
+    <row r="3073">
+      <c r="A3073" t="inlineStr">
+        <is>
+          <t>data.event.event_08_a.name.761bd4a4</t>
+        </is>
+      </c>
+      <c r="C3073" t="inlineStr">
+        <is>
+          <t>공명의 비석</t>
+        </is>
+      </c>
+    </row>
+    <row r="3074">
+      <c r="A3074" t="inlineStr">
+        <is>
+          <t>data.event.event_08_a.failure_description.f775776f</t>
+        </is>
+      </c>
+      <c r="C3074" t="inlineStr">
+        <is>
+          <t>선택한 기억 소멸</t>
+        </is>
+      </c>
+    </row>
+    <row r="3075">
+      <c r="A3075" t="inlineStr">
+        <is>
+          <t>data.event.event_08_b.name.761bd4a4</t>
+        </is>
+      </c>
+      <c r="C3075" t="inlineStr">
+        <is>
+          <t>공명의 비석</t>
+        </is>
+      </c>
+    </row>
+    <row r="3076">
+      <c r="A3076" t="inlineStr">
+        <is>
+          <t>data.event.event_08_b.failure_description.f775776f</t>
+        </is>
+      </c>
+      <c r="C3076" t="inlineStr">
+        <is>
+          <t>선택한 기억 소멸</t>
+        </is>
+      </c>
+    </row>
+    <row r="3077">
+      <c r="A3077" t="inlineStr">
+        <is>
+          <t>data.event.event_08_c.name.761bd4a4</t>
+        </is>
+      </c>
+      <c r="C3077" t="inlineStr">
+        <is>
+          <t>공명의 비석</t>
+        </is>
+      </c>
+    </row>
+    <row r="3078">
+      <c r="A3078" t="inlineStr">
+        <is>
+          <t>data.event.event_08_d.name.761bd4a4</t>
+        </is>
+      </c>
+      <c r="C3078" t="inlineStr">
+        <is>
+          <t>공명의 비석</t>
+        </is>
+      </c>
+    </row>
+    <row r="3079">
+      <c r="A3079" t="inlineStr">
+        <is>
+          <t>data.rune.rune_51.effect_description.89be216d</t>
+        </is>
+      </c>
+      <c r="C3079" t="inlineStr">
+        <is>
+          <t>탐사 시작 시 카르마를 {ValueRate1} 회복한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3080">
+      <c r="A3080" t="inlineStr">
+        <is>
+          <t>data.rune.rune_56.effect_description.89be216d</t>
+        </is>
+      </c>
+      <c r="C3080" t="inlineStr">
+        <is>
+          <t>탐사 시작 시 카르마를 {ValueRate1} 회복한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3081">
+      <c r="A3081" t="inlineStr">
+        <is>
+          <t>data.rune.rune_61.effect_description.89be216d</t>
+        </is>
+      </c>
+      <c r="C3081" t="inlineStr">
+        <is>
+          <t>탐사 시작 시 카르마를 {ValueRate1} 회복한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3082">
+      <c r="A3082" t="inlineStr">
+        <is>
+          <t>data.rune.rune_66.effect_description.89be216d</t>
+        </is>
+      </c>
+      <c r="C3082" t="inlineStr">
+        <is>
+          <t>탐사 시작 시 카르마를 {ValueRate1} 회복한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3083">
+      <c r="A3083" t="inlineStr">
+        <is>
+          <t>data.rune.rune_71.effect_description.89be216d</t>
+        </is>
+      </c>
+      <c r="C3083" t="inlineStr">
+        <is>
+          <t>탐사 시작 시 카르마를 {ValueRate1} 회복한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3084">
+      <c r="A3084" t="inlineStr">
+        <is>
+          <t>data.rune.rune_06.effect_description.0dc6592f</t>
+        </is>
+      </c>
+      <c r="C3084" t="inlineStr">
+        <is>
+          <t>최대 생명력이 {ValueRate1} 증가한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3085">
+      <c r="A3085" t="inlineStr">
+        <is>
+          <t>data.rune.rune_07.effect_description.24008e20</t>
+        </is>
+      </c>
+      <c r="C3085" t="inlineStr">
+        <is>
+          <t>최대 마나가 {ValueRate1} 증가한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3086">
+      <c r="A3086" t="inlineStr">
+        <is>
+          <t>data.rune.rune_08.effect_description.6701fc48</t>
+        </is>
+      </c>
+      <c r="C3086" t="inlineStr">
+        <is>
+          <t>마나 재생량이 {ValueRate1} 증가한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3087">
+      <c r="A3087" t="inlineStr">
+        <is>
+          <t>data.rune.rune_19.effect_description.e862bfd7</t>
+        </is>
+      </c>
+      <c r="C3087" t="inlineStr">
+        <is>
+          <t>전투 보상으로 획득하는 재화의 양이 {ValueRate1}% 증가한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3088">
+      <c r="A3088" t="inlineStr">
+        <is>
+          <t>data.rune.rune_20.effect_description.a1950ba6</t>
+        </is>
+      </c>
+      <c r="C3088" t="inlineStr">
+        <is>
+          <t>전투 종료 후 생명력을 {ValueRate1} 회복한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3089">
+      <c r="A3089" t="inlineStr">
+        <is>
+          <t>data.relic.relic_p_01.effect_description.0dc6592f</t>
+        </is>
+      </c>
+      <c r="C3089" t="inlineStr">
+        <is>
+          <t>최대 생명력이 {ValueRate1} 증가한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3090">
+      <c r="A3090" t="inlineStr">
+        <is>
+          <t>data.relic.relic_p_02.effect_description.24008e20</t>
+        </is>
+      </c>
+      <c r="C3090" t="inlineStr">
+        <is>
+          <t>최대 마나가 {ValueRate1} 증가한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3091">
+      <c r="A3091" t="inlineStr">
+        <is>
+          <t>data.relic.relic_p_03.effect_description.6701fc48</t>
+        </is>
+      </c>
+      <c r="C3091" t="inlineStr">
+        <is>
+          <t>마나 재생량이 {ValueRate1} 증가한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3092">
+      <c r="A3092" t="inlineStr">
+        <is>
+          <t>data.relic.relic_p_67.effect_description.e862bfd7</t>
+        </is>
+      </c>
+      <c r="C3092" t="inlineStr">
+        <is>
+          <t>전투 보상으로 획득하는 재화의 양이 {ValueRate1}% 증가한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3093">
+      <c r="A3093" t="inlineStr">
+        <is>
+          <t>data.relic.relic_p_68.name.7be0a3d0</t>
+        </is>
+      </c>
+      <c r="C3093" t="inlineStr">
+        <is>
+          <t>붕대</t>
+        </is>
+      </c>
+    </row>
+    <row r="3094">
+      <c r="A3094" t="inlineStr">
+        <is>
+          <t>data.relic.relic_p_68.effect_description.a1950ba6</t>
+        </is>
+      </c>
+      <c r="C3094" t="inlineStr">
+        <is>
+          <t>전투 종료 후 생명력을 {ValueRate1} 회복한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3095">
+      <c r="A3095" t="inlineStr">
+        <is>
+          <t>data.compound.compound_02.effect_description</t>
+        </is>
+      </c>
+      <c r="C3095" t="inlineStr">
+        <is>
+          <t>이번 턴 동안 받는 피해가 50% 감소한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3096">
+      <c r="A3096" t="inlineStr">
+        <is>
+          <t>data.compound.compound_04.name.633634da</t>
+        </is>
+      </c>
+      <c r="C3096" t="inlineStr">
+        <is>
+          <t>마력 플라스크</t>
+        </is>
+      </c>
+    </row>
+    <row r="3097">
+      <c r="A3097" t="inlineStr">
+        <is>
+          <t>data.compound.compound_09.effect_description</t>
+        </is>
+      </c>
+      <c r="C3097" t="inlineStr">
+        <is>
+          <t>선택한 그리드에 독 장판을 생성한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3098">
+      <c r="A3098" t="inlineStr">
+        <is>
+          <t>data.compound.compound_10.effect_description</t>
+        </is>
+      </c>
+      <c r="C3098" t="inlineStr">
+        <is>
+          <t>선택한 그리드에 가시를 생성한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3099">
+      <c r="A3099" t="inlineStr">
+        <is>
+          <t>data.compound.compound_13.effect_description</t>
+        </is>
+      </c>
+      <c r="C3099" t="inlineStr">
+        <is>
+          <t>선택한 그리드의 장애물을 제거한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3100">
+      <c r="A3100" t="inlineStr">
+        <is>
+          <t>data.compound.compound_14.name.0fdd8c95</t>
+        </is>
+      </c>
+      <c r="C3100" t="inlineStr">
+        <is>
+          <t>호문쿨루스 루어</t>
+        </is>
+      </c>
+    </row>
+    <row r="3101">
+      <c r="A3101" t="inlineStr">
+        <is>
+          <t>data.compound.compound_14.effect_description</t>
+        </is>
+      </c>
+      <c r="C3101" t="inlineStr">
+        <is>
+          <t>선택한 빈 그리드에 루어를 생성한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3102">
+      <c r="A3102" t="inlineStr">
+        <is>
+          <t>data.compound.compound_15.name.6ae4be35</t>
+        </is>
+      </c>
+      <c r="C3102" t="inlineStr">
+        <is>
+          <t>호문쿨루스 브룸</t>
+        </is>
+      </c>
+    </row>
+    <row r="3103">
+      <c r="A3103" t="inlineStr">
+        <is>
+          <t>data.compound.compound_15.effect_description</t>
+        </is>
+      </c>
+      <c r="C3103" t="inlineStr">
+        <is>
+          <t>선택한 빈 그리드에 브룸을 생성한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3104">
+      <c r="A3104" t="inlineStr">
+        <is>
+          <t>data.erosion.erosion_01_01.name.bd3c2e94</t>
+        </is>
+      </c>
+      <c r="C3104" t="inlineStr">
+        <is>
+          <t>강인한 변이체</t>
+        </is>
+      </c>
+    </row>
+    <row r="3105">
+      <c r="A3105" t="inlineStr">
+        <is>
+          <t>data.erosion.erosion_01_02.name.b4406914</t>
+        </is>
+      </c>
+      <c r="C3105" t="inlineStr">
+        <is>
+          <t>흉포한 변이체</t>
+        </is>
+      </c>
+    </row>
+    <row r="3106">
+      <c r="A3106" t="inlineStr">
+        <is>
+          <t>data.erosion.erosion_01_03.name.917b10ff</t>
+        </is>
+      </c>
+      <c r="C3106" t="inlineStr">
+        <is>
+          <t>쇠약한 육체</t>
+        </is>
+      </c>
+    </row>
+    <row r="3107">
+      <c r="A3107" t="inlineStr">
+        <is>
+          <t>data.erosion.erosion_01_04.name.b75e8430</t>
+        </is>
+      </c>
+      <c r="C3107" t="inlineStr">
+        <is>
+          <t>불길한 징후</t>
+        </is>
+      </c>
+    </row>
+    <row r="3108">
+      <c r="A3108" t="inlineStr">
+        <is>
+          <t>data.erosion.erosion_01_05.name.e2354222</t>
+        </is>
+      </c>
+      <c r="C3108" t="inlineStr">
+        <is>
+          <t>메마른 보급</t>
+        </is>
+      </c>
+    </row>
+    <row r="3109">
+      <c r="A3109" t="inlineStr">
+        <is>
+          <t>data.erosion.erosion_01_06.name.a611215e</t>
+        </is>
+      </c>
+      <c r="C3109" t="inlineStr">
+        <is>
+          <t>뒤틀린 운명</t>
+        </is>
+      </c>
+    </row>
+    <row r="3110">
+      <c r="A3110" t="inlineStr">
+        <is>
+          <t>data.erosion.erosion_01_06.description.7bb5ae6b</t>
+        </is>
+      </c>
+      <c r="C3110" t="inlineStr">
+        <is>
+          <t>난이도 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="3111">
+      <c r="A3111" t="inlineStr">
+        <is>
+          <t>data.erosion.erosion_02_01.name.bd3c2e94</t>
+        </is>
+      </c>
+      <c r="C3111" t="inlineStr">
+        <is>
+          <t>강인한 변이체</t>
+        </is>
+      </c>
+    </row>
+    <row r="3112">
+      <c r="A3112" t="inlineStr">
+        <is>
+          <t>data.erosion.erosion_02_02.name.b4406914</t>
+        </is>
+      </c>
+      <c r="C3112" t="inlineStr">
+        <is>
+          <t>흉포한 변이체</t>
+        </is>
+      </c>
+    </row>
+    <row r="3113">
+      <c r="A3113" t="inlineStr">
+        <is>
+          <t>data.erosion.erosion_02_03.name.917b10ff</t>
+        </is>
+      </c>
+      <c r="C3113" t="inlineStr">
+        <is>
+          <t>쇠약한 육체</t>
+        </is>
+      </c>
+    </row>
+    <row r="3114">
+      <c r="A3114" t="inlineStr">
+        <is>
+          <t>data.erosion.erosion_02_04.name.b75e8430</t>
+        </is>
+      </c>
+      <c r="C3114" t="inlineStr">
+        <is>
+          <t>불길한 징후</t>
+        </is>
+      </c>
+    </row>
+    <row r="3115">
+      <c r="A3115" t="inlineStr">
+        <is>
+          <t>data.erosion.erosion_02_04.description.7bb5ae6b</t>
+        </is>
+      </c>
+      <c r="C3115" t="inlineStr">
+        <is>
+          <t>난이도 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="3116">
+      <c r="A3116" t="inlineStr">
+        <is>
+          <t>data.erosion.erosion_02_05.name.e2354222</t>
+        </is>
+      </c>
+      <c r="C3116" t="inlineStr">
+        <is>
+          <t>메마른 보급</t>
+        </is>
+      </c>
+    </row>
+    <row r="3117">
+      <c r="A3117" t="inlineStr">
+        <is>
+          <t>data.erosion.erosion_02_06.name.a611215e</t>
+        </is>
+      </c>
+      <c r="C3117" t="inlineStr">
+        <is>
+          <t>뒤틀린 운명</t>
+        </is>
+      </c>
+    </row>
+    <row r="3118">
+      <c r="A3118" t="inlineStr">
+        <is>
+          <t>data.erosion.erosion_03_01.name.bd3c2e94</t>
+        </is>
+      </c>
+      <c r="C3118" t="inlineStr">
+        <is>
+          <t>강인한 변이체</t>
+        </is>
+      </c>
+    </row>
+    <row r="3119">
+      <c r="A3119" t="inlineStr">
+        <is>
+          <t>data.erosion.erosion_03_02.name.b4406914</t>
+        </is>
+      </c>
+      <c r="C3119" t="inlineStr">
+        <is>
+          <t>흉포한 변이체</t>
+        </is>
+      </c>
+    </row>
+    <row r="3120">
+      <c r="A3120" t="inlineStr">
+        <is>
+          <t>data.erosion.erosion_03_02.description.7bb5ae6b</t>
+        </is>
+      </c>
+      <c r="C3120" t="inlineStr">
+        <is>
+          <t>난이도 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="3121">
+      <c r="A3121" t="inlineStr">
+        <is>
+          <t>data.erosion.erosion_03_03.name.917b10ff</t>
+        </is>
+      </c>
+      <c r="C3121" t="inlineStr">
+        <is>
+          <t>쇠약한 육체</t>
+        </is>
+      </c>
+    </row>
+    <row r="3122">
+      <c r="A3122" t="inlineStr">
+        <is>
+          <t>data.erosion.erosion_03_04.name.b75e8430</t>
+        </is>
+      </c>
+      <c r="C3122" t="inlineStr">
+        <is>
+          <t>불길한 징후</t>
+        </is>
+      </c>
+    </row>
+    <row r="3123">
+      <c r="A3123" t="inlineStr">
+        <is>
+          <t>data.erosion.erosion_03_05.name.e2354222</t>
+        </is>
+      </c>
+      <c r="C3123" t="inlineStr">
+        <is>
+          <t>메마른 보급</t>
+        </is>
+      </c>
+    </row>
+    <row r="3124">
+      <c r="A3124" t="inlineStr">
+        <is>
+          <t>data.erosion.erosion_03_05.description.7bb5ae6b</t>
+        </is>
+      </c>
+      <c r="C3124" t="inlineStr">
+        <is>
+          <t>난이도 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="3125">
+      <c r="A3125" t="inlineStr">
+        <is>
+          <t>data.erosion.erosion_03_06.name.a611215e</t>
+        </is>
+      </c>
+      <c r="C3125" t="inlineStr">
+        <is>
+          <t>뒤틀린 운명</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Assets/ExcelSource/Localization.xlsx
+++ b/Assets/ExcelSource/Localization.xlsx
@@ -32493,7 +32493,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G1266"/>
+  <dimension ref="A1:G1267"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="212.125" customWidth="1"/>
@@ -53237,6 +53237,128 @@
         </is>
       </c>
     </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>ui.record.effect.cef1448c</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>해당 아이템의 효과
+해당 아이템의 효과
+해당 아이템의 효과</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>intro.story.01</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>더스티움이 과도하게 응축되며 침식 구역이 생겨났다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>intro.story.02</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>침식된 땅에는 정체를 알 수 없는 변이체가 나타났고,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>intro.story.03</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>그곳은 점차 함부로 발을 들이기 어려운 위험한 장소가 되었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>intro.story.04</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>학회는 침식의 원인을 파악하고 현상을 연구하고자</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>intro.story.05</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>침식 구역에 대한 조사를 결정했다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>intro.story.06</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>얼마 뒤, 탐사 인원을 모집하는 의뢰서가 내걸렸다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>intro.story.07</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>저마다 다른 이유를 가진 이들이 그 의뢰서를 집어 들었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>intro.story.08</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>침식 구역의 경계에는 탐사 거점이 세워졌고,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>intro.story.09</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>하나둘 그곳으로 모여들었다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Assets/ExcelSource/Localization.xlsx
+++ b/Assets/ExcelSource/Localization.xlsx
@@ -32493,7 +32493,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G1384"/>
+  <dimension ref="A1:G1397"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="212.125" customWidth="1"/>
@@ -34237,10 +34237,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>“강한 놈들이 득실거린다며?
-그럼 내가 가야지.”
-벨가드 용병단의 용병.
-호전적이고 거침없는 성격으로, 위험한 전투일수록 앞장서며 이번 탐사에서도 자신의 강함을 증명하려 한다.</t>
+          <t>“강한 놈들이 득실거린다며? 그럼 내가 가야지.”</t>
         </is>
       </c>
     </row>
@@ -34280,9 +34277,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>“임무라면 완수한다. 그뿐이야.”
-하쿠렌 가문의 검사.
-침착하고 냉철하며 어떤 상황에서도 흐트러지지 않는다. 미지의 적들과 맞서며 자신의 검술을 더욱 완성해 나간다.</t>
+          <t>“임무라면 완수한다. 그뿐이야.”</t>
         </is>
       </c>
     </row>
@@ -34322,9 +34317,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>“정말 제가 가야 하는 건가요?”
-아스텔 학회의 학자.
-겁이 많고 소심하지만 맡은 연구에서는 물러서지 않는다. 소환수 니아와 함께 탐사에 나서며 자신의 나약함을 극복하려 한다.</t>
+          <t>“정말 제가 가야 하는 건가요?”</t>
         </is>
       </c>
     </row>
@@ -34364,10 +34357,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>“걱정하지 마세요.
-모두 무사히 돌아갈 수 있도록 할게요.”
-세라피아 교단의 집행자.
-밝고 상냥한 성격으로 동료들을 살뜰히 보살핀다. 하지만 그들을 위협하는 존재 앞에서는 망설임 없이 냉혹한 모습을 드러낸다.</t>
+          <t>“걱정하지 마세요. 모두 무사히 돌아갈 수 있도록 할게요.”</t>
         </is>
       </c>
     </row>
@@ -34407,9 +34397,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>“그냥 내가 가고 싶어서 가는 거야.”
-자유롭게 떠도는 방랑자.
-말수가 적고 자유분방하며 타인의 규칙에 얽매이지 않는다. 자신의 관심이 향한 탐사대를 따라 스스로 위험 속으로 발을 들인다.</t>
+          <t>“그냥 내가 가고 싶어서 가는 거야.”</t>
         </is>
       </c>
     </row>
@@ -53481,220 +53469,208 @@
     <row r="1299">
       <c r="A1299" t="inlineStr">
         <is>
-          <t>ui.lobby.text.33abb2e3</t>
+          <t>ui.lobby.text.dae4b44d</t>
         </is>
       </c>
       <c r="C1299" t="inlineStr">
         <is>
-          <t>보관함</t>
+          <t>발현</t>
         </is>
       </c>
     </row>
     <row r="1300">
       <c r="A1300" t="inlineStr">
         <is>
-          <t>ui.lobby.text.dae4b44d</t>
+          <t>ui.lobby.text.506c14d8</t>
         </is>
       </c>
       <c r="C1300" t="inlineStr">
         <is>
-          <t>발현</t>
+          <t>NPC 이름</t>
         </is>
       </c>
     </row>
     <row r="1301">
       <c r="A1301" t="inlineStr">
         <is>
-          <t>ui.lobby.text.506c14d8</t>
+          <t>ui.lobby.text.de97bb9d</t>
         </is>
       </c>
       <c r="C1301" t="inlineStr">
         <is>
-          <t>NPC 이름</t>
+          <t>구현</t>
         </is>
       </c>
     </row>
     <row r="1302">
       <c r="A1302" t="inlineStr">
         <is>
-          <t>ui.lobby.text.de97bb9d</t>
+          <t>ui.lobby.text.48ab33a5</t>
         </is>
       </c>
       <c r="C1302" t="inlineStr">
         <is>
-          <t>구현</t>
+          <t>재료이름</t>
         </is>
       </c>
     </row>
     <row r="1303">
       <c r="A1303" t="inlineStr">
         <is>
-          <t>ui.lobby.text.48ab33a5</t>
+          <t>ui.lobby.text.e5980dc5</t>
         </is>
       </c>
       <c r="C1303" t="inlineStr">
         <is>
-          <t>재료이름</t>
+          <t>이름이름</t>
         </is>
       </c>
     </row>
     <row r="1304">
       <c r="A1304" t="inlineStr">
         <is>
-          <t>ui.lobby.text.e5980dc5</t>
+          <t>ui.lobby.text.42ef35e8</t>
         </is>
       </c>
       <c r="C1304" t="inlineStr">
         <is>
-          <t>이름이름</t>
+          <t>강화된 변이체</t>
         </is>
       </c>
     </row>
     <row r="1305">
       <c r="A1305" t="inlineStr">
         <is>
-          <t>ui.lobby.text.42ef35e8</t>
+          <t>ui.lobby.text.48bb3206</t>
         </is>
       </c>
       <c r="C1305" t="inlineStr">
         <is>
-          <t>강화된 변이체</t>
+          <t>본능</t>
         </is>
       </c>
     </row>
     <row r="1306">
       <c r="A1306" t="inlineStr">
         <is>
-          <t>ui.lobby.text.48bb3206</t>
+          <t>ui.lobby.text.d32c0fa0</t>
         </is>
       </c>
       <c r="C1306" t="inlineStr">
         <is>
-          <t>본능</t>
+          <t>오브젝트이름</t>
         </is>
       </c>
     </row>
     <row r="1307">
       <c r="A1307" t="inlineStr">
         <is>
-          <t>ui.lobby.text.d32c0fa0</t>
+          <t>ui.lobby.text.3bee5b16</t>
         </is>
       </c>
       <c r="C1307" t="inlineStr">
         <is>
-          <t>오브젝트이름</t>
+          <t>흉포한
+변이체</t>
         </is>
       </c>
     </row>
     <row r="1308">
       <c r="A1308" t="inlineStr">
         <is>
-          <t>ui.lobby.text.3bee5b16</t>
+          <t>ui.lobby.text.85573190</t>
         </is>
       </c>
       <c r="C1308" t="inlineStr">
         <is>
-          <t>흉포한
-변이체</t>
+          <t>뒤틀린
+운명</t>
         </is>
       </c>
     </row>
     <row r="1309">
       <c r="A1309" t="inlineStr">
         <is>
-          <t>ui.lobby.text.85573190</t>
+          <t>ui.lobby.text.34e70344</t>
         </is>
       </c>
       <c r="C1309" t="inlineStr">
         <is>
-          <t>뒤틀린
-운명</t>
+          <t>메마른
+보급</t>
         </is>
       </c>
     </row>
     <row r="1310">
       <c r="A1310" t="inlineStr">
         <is>
-          <t>ui.lobby.text.34e70344</t>
+          <t>ui.lobby.text.367b0594</t>
         </is>
       </c>
       <c r="C1310" t="inlineStr">
         <is>
-          <t>메마른
-보급</t>
+          <t>열악한
+탐사</t>
         </is>
       </c>
     </row>
     <row r="1311">
       <c r="A1311" t="inlineStr">
         <is>
-          <t>ui.lobby.text.367b0594</t>
+          <t>ui.lobby.text.ff6c8359</t>
         </is>
       </c>
       <c r="C1311" t="inlineStr">
         <is>
-          <t>열악한
-탐사</t>
+          <t>쇠약한
+육체</t>
         </is>
       </c>
     </row>
     <row r="1312">
       <c r="A1312" t="inlineStr">
         <is>
-          <t>ui.lobby.text.ff6c8359</t>
+          <t>ui.lobby.text.fbcc900a</t>
         </is>
       </c>
       <c r="C1312" t="inlineStr">
         <is>
-          <t>쇠약한
-육체</t>
+          <t>불길한
+징후</t>
         </is>
       </c>
     </row>
     <row r="1313">
       <c r="A1313" t="inlineStr">
         <is>
-          <t>ui.lobby.text.fbcc900a</t>
+          <t>ui.lobby.text.0385cd9d</t>
         </is>
       </c>
       <c r="C1313" t="inlineStr">
         <is>
-          <t>불길한
-징후</t>
+          <t>현재패널</t>
         </is>
       </c>
     </row>
     <row r="1314">
       <c r="A1314" t="inlineStr">
         <is>
-          <t>ui.lobby.text.0385cd9d</t>
+          <t>data.event.event_01.choice_description.0a84ed3f</t>
         </is>
       </c>
       <c r="C1314" t="inlineStr">
         <is>
-          <t>현재패널</t>
+          <t>무작위 유물 1개 획득</t>
         </is>
       </c>
     </row>
     <row r="1315">
       <c r="A1315" t="inlineStr">
         <is>
-          <t>data.event.event_01.choice_description.0a84ed3f</t>
+          <t>data.event.event_01.choice_description.c2b50b91</t>
         </is>
       </c>
       <c r="C1315" t="inlineStr">
-        <is>
-          <t>무작위 유물 1개 획득</t>
-        </is>
-      </c>
-    </row>
-    <row r="1316">
-      <c r="A1316" t="inlineStr">
-        <is>
-          <t>data.event.event_01.choice_description.c2b50b91</t>
-        </is>
-      </c>
-      <c r="C1316" t="inlineStr">
         <is>
           <t>주사위 판정
 보상 : 생명력 회복
@@ -53702,13 +53678,13 @@
         </is>
       </c>
     </row>
-    <row r="1317">
-      <c r="A1317" t="inlineStr">
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
         <is>
           <t>data.event.event_01.choice_description.f3b35683</t>
         </is>
       </c>
-      <c r="C1317" t="inlineStr">
+      <c r="C1316" t="inlineStr">
         <is>
           <t>주사위 판정
 보상 : 최대 생명력 증가
@@ -53716,61 +53692,61 @@
         </is>
       </c>
     </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>data.event.event_01_a.description</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>“조금이나마 도움이 되기를 바랍니다. 부디 조심해서 사용해 주세요.”</t>
+        </is>
+      </c>
+    </row>
     <row r="1318">
       <c r="A1318" t="inlineStr">
         <is>
-          <t>data.event.event_01_a.description</t>
+          <t>data.event.event_01_b.description</t>
         </is>
       </c>
       <c r="C1318" t="inlineStr">
         <is>
-          <t>“조금이나마 도움이 되기를 바랍니다. 부디 조심해서 사용해 주세요.”</t>
+          <t>“상처가 조금은 나아졌군요. 이 힘이 당신들의 여정에 보탬이 되기를 바랍니다.”</t>
         </is>
       </c>
     </row>
     <row r="1319">
       <c r="A1319" t="inlineStr">
         <is>
-          <t>data.event.event_01_b.description</t>
+          <t>data.event.event_01_c.description</t>
         </is>
       </c>
       <c r="C1319" t="inlineStr">
         <is>
-          <t>“상처가 조금은 나아졌군요. 이 힘이 당신들의 여정에 보탬이 되기를 바랍니다.”</t>
+          <t>“당신들의 생명에 축복이 머물기를.”</t>
         </is>
       </c>
     </row>
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>data.event.event_01_c.description</t>
+          <t>data.event.event_02.choice_description.a28ed6bd</t>
         </is>
       </c>
       <c r="C1320" t="inlineStr">
         <is>
-          <t>“당신들의 생명에 축복이 머물기를.”</t>
+          <t>레드 더스티움 35 획득</t>
         </is>
       </c>
     </row>
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
-          <t>data.event.event_02.choice_description.a28ed6bd</t>
+          <t>data.event.event_02_a.choice_description.dc6c676f</t>
         </is>
       </c>
       <c r="C1321" t="inlineStr">
-        <is>
-          <t>레드 더스티움 35 획득</t>
-        </is>
-      </c>
-    </row>
-    <row r="1322">
-      <c r="A1322" t="inlineStr">
-        <is>
-          <t>data.event.event_02_a.choice_description.dc6c676f</t>
-        </is>
-      </c>
-      <c r="C1322" t="inlineStr">
         <is>
           <t>주사위 판정 9
 성공 : 무작위 유물 1개 획득
@@ -53778,13 +53754,13 @@
         </is>
       </c>
     </row>
-    <row r="1323">
-      <c r="A1323" t="inlineStr">
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
         <is>
           <t>data.event.event_02.choice_description.4519e302</t>
         </is>
       </c>
-      <c r="C1323" t="inlineStr">
+      <c r="C1322" t="inlineStr">
         <is>
           <t>주사위 판정 11
 성공 : 마나 재생량 1 증가
@@ -53792,13 +53768,13 @@
         </is>
       </c>
     </row>
-    <row r="1324">
-      <c r="A1324" t="inlineStr">
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
         <is>
           <t>data.event.event_02.choice_description.265a2cf0</t>
         </is>
       </c>
-      <c r="C1324" t="inlineStr">
+      <c r="C1323" t="inlineStr">
         <is>
           <t>주사위 판정 13
 성공 : 에픽 유물 1개 획득
@@ -53806,146 +53782,146 @@
         </is>
       </c>
     </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>data.event.event_02_b.description</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>의식 도구에 남아 있던 힘이 몸 안으로 스며든다.</t>
+        </is>
+      </c>
+    </row>
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>data.event.event_02_b.description</t>
+          <t>data.event.event_02_c.description</t>
         </is>
       </c>
       <c r="C1325" t="inlineStr">
         <is>
-          <t>의식 도구에 남아 있던 힘이 몸 안으로 스며든다.</t>
+          <t>흔적을 헤집자 안쪽에서 강한 힘을 머금은 유물이 모습을 드러냈다.</t>
         </is>
       </c>
     </row>
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>data.event.event_02_c.description</t>
+          <t>data.event.event_02_d.description</t>
         </is>
       </c>
       <c r="C1326" t="inlineStr">
         <is>
-          <t>흔적을 헤집자 안쪽에서 강한 힘을 머금은 유물이 모습을 드러냈다.</t>
+          <t>의식 도구에 손을 대는 순간 불길한 기운이 역류한다.</t>
         </is>
       </c>
     </row>
     <row r="1327">
       <c r="A1327" t="inlineStr">
         <is>
-          <t>data.event.event_02_d.description</t>
+          <t>data.event.event_02_e.description</t>
         </is>
       </c>
       <c r="C1327" t="inlineStr">
         <is>
-          <t>의식 도구에 손을 대는 순간 불길한 기운이 역류한다.</t>
+          <t>흔적을 훼손한 순간 억눌려 있던 힘이 폭발한다.</t>
         </is>
       </c>
     </row>
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
-          <t>data.event.event_02_e.description</t>
+          <t>data.event.event_02_g.description</t>
         </is>
       </c>
       <c r="C1328" t="inlineStr">
         <is>
-          <t>흔적을 훼손한 순간 억눌려 있던 힘이 폭발한다.</t>
+          <t>더 이상 손대지 않기로 하고, 조용히 자리를 떠난다.</t>
         </is>
       </c>
     </row>
     <row r="1329">
       <c r="A1329" t="inlineStr">
         <is>
-          <t>data.event.event_02_g.description</t>
+          <t>data.event.event_02_h.description</t>
         </is>
       </c>
       <c r="C1329" t="inlineStr">
         <is>
-          <t>더 이상 손대지 않기로 하고, 조용히 자리를 떠난다.</t>
+          <t>뜻밖의 수확을 얻었다. 더 이상 손댈 것은 없어 보인다.</t>
         </is>
       </c>
     </row>
     <row r="1330">
       <c r="A1330" t="inlineStr">
         <is>
-          <t>data.event.event_02_h.description</t>
+          <t>data.event.event_02_i.description</t>
         </is>
       </c>
       <c r="C1330" t="inlineStr">
         <is>
-          <t>뜻밖의 수확을 얻었다. 더 이상 손댈 것은 없어 보인다.</t>
+          <t>예상치 못한 폭발에 휘말렸다.</t>
         </is>
       </c>
     </row>
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>data.event.event_02_i.description</t>
+          <t>data.event.event_03.choice_description.8f43bd81</t>
         </is>
       </c>
       <c r="C1331" t="inlineStr">
         <is>
-          <t>예상치 못한 폭발에 휘말렸다.</t>
+          <t>육면체 주사위 3개를 굴려 레드 더스티움을 획득한다.</t>
         </is>
       </c>
     </row>
     <row r="1332">
       <c r="A1332" t="inlineStr">
         <is>
-          <t>data.event.event_03.choice_description.8f43bd81</t>
+          <t>data.event.event_03.description.a958b0a2</t>
         </is>
       </c>
       <c r="C1332" t="inlineStr">
         <is>
-          <t>육면체 주사위 3개를 굴려 레드 더스티움을 획득한다.</t>
+          <t>시체들 사이로 아직 쓸 만한 물건이 보이지만, 더미 안쪽에서 희미한 움직임이 느껴진다.</t>
         </is>
       </c>
     </row>
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>data.event.event_03.description.a958b0a2</t>
+          <t>data.event.event_03.choice_description.72643f70</t>
         </is>
       </c>
       <c r="C1333" t="inlineStr">
         <is>
-          <t>시체들 사이로 아직 쓸 만한 물건이 보이지만, 더미 안쪽에서 희미한 움직임이 느껴진다.</t>
+          <t>무작위 기억 1개 획득</t>
         </is>
       </c>
     </row>
     <row r="1334">
       <c r="A1334" t="inlineStr">
         <is>
-          <t>data.event.event_03.choice_description.72643f70</t>
+          <t>data.event.event_04.choice_description.fec306f4</t>
         </is>
       </c>
       <c r="C1334" t="inlineStr">
         <is>
-          <t>무작위 기억 1개 획득</t>
+          <t>레드 더스티움 50 소모
+무작위 유물 1개 획득</t>
         </is>
       </c>
     </row>
     <row r="1335">
       <c r="A1335" t="inlineStr">
         <is>
-          <t>data.event.event_04.choice_description.fec306f4</t>
+          <t>data.event.event_04.choice_description.c390d5e2</t>
         </is>
       </c>
       <c r="C1335" t="inlineStr">
-        <is>
-          <t>레드 더스티움 50 소모
-무작위 유물 1개 획득</t>
-        </is>
-      </c>
-    </row>
-    <row r="1336">
-      <c r="A1336" t="inlineStr">
-        <is>
-          <t>data.event.event_04.choice_description.c390d5e2</t>
-        </is>
-      </c>
-      <c r="C1336" t="inlineStr">
         <is>
           <t>주사위 판정 11
 성공 : 무작위 유물 1개 획득
@@ -53953,248 +53929,248 @@
         </is>
       </c>
     </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>data.event.event_04.choice_description.b9221c68</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>보유 유물 1개 소모
+무작위 유물 1개 획득</t>
+        </is>
+      </c>
+    </row>
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>data.event.event_04.choice_description.b9221c68</t>
+          <t>data.event.event_04_a.description</t>
         </is>
       </c>
       <c r="C1337" t="inlineStr">
         <is>
-          <t>보유 유물 1개 소모
-무작위 유물 1개 획득</t>
+          <t>“좋아. 이 정도면 충분한 대가였군.”</t>
         </is>
       </c>
     </row>
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>data.event.event_04_a.description</t>
+          <t>data.event.event_04_b.description</t>
         </is>
       </c>
       <c r="C1338" t="inlineStr">
         <is>
-          <t>“좋아. 이 정도면 충분한 대가였군.”</t>
+          <t>“제법 운이 좋았군.”</t>
         </is>
       </c>
     </row>
     <row r="1339">
       <c r="A1339" t="inlineStr">
         <is>
-          <t>data.event.event_04_b.description</t>
+          <t>data.event.event_04_c.description</t>
         </is>
       </c>
       <c r="C1339" t="inlineStr">
         <is>
-          <t>“제법 운이 좋았군.”</t>
+          <t>“나쁘지 않은 거래였어..”</t>
         </is>
       </c>
     </row>
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>data.event.event_04_c.description</t>
+          <t>data.event.event_04_d.description</t>
         </is>
       </c>
       <c r="C1340" t="inlineStr">
         <is>
-          <t>“나쁘지 않은 거래였어..”</t>
+          <t>"모자란 몫은 생명으로 받아가겠다.”</t>
         </is>
       </c>
     </row>
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>data.event.event_04_d.description</t>
+          <t>data.event.event_05.choice_description.73af1899</t>
         </is>
       </c>
       <c r="C1341" t="inlineStr">
         <is>
-          <t>"모자란 몫은 생명으로 받아가겠다.”</t>
+          <t>주사위 판정 8
+레드 더스티움 15 누적</t>
         </is>
       </c>
     </row>
     <row r="1342">
       <c r="A1342" t="inlineStr">
         <is>
-          <t>data.event.event_05.choice_description.73af1899</t>
+          <t>data.event.event_05.choice_description.ca6b26a1</t>
         </is>
       </c>
       <c r="C1342" t="inlineStr">
+        <is>
+          <t>주사위 판정 12
+레드 더스티움 45 누적</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>data.event.event_05_a.choice_description.73af1899</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
         <is>
           <t>주사위 판정 8
 레드 더스티움 15 누적</t>
         </is>
       </c>
     </row>
-    <row r="1343">
-      <c r="A1343" t="inlineStr">
-        <is>
-          <t>data.event.event_05.choice_description.ca6b26a1</t>
-        </is>
-      </c>
-      <c r="C1343" t="inlineStr">
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>data.event.event_05_a.choice_description.ca6b26a1</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
         <is>
           <t>주사위 판정 12
 레드 더스티움 45 누적</t>
         </is>
       </c>
     </row>
-    <row r="1344">
-      <c r="A1344" t="inlineStr">
-        <is>
-          <t>data.event.event_05_a.choice_description.73af1899</t>
-        </is>
-      </c>
-      <c r="C1344" t="inlineStr">
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>data.event.event_05_b.choice_description.73af1899</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
         <is>
           <t>주사위 판정 8
 레드 더스티움 15 누적</t>
         </is>
       </c>
     </row>
-    <row r="1345">
-      <c r="A1345" t="inlineStr">
-        <is>
-          <t>data.event.event_05_a.choice_description.ca6b26a1</t>
-        </is>
-      </c>
-      <c r="C1345" t="inlineStr">
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>data.event.event_05_b.choice_description.ca6b26a1</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
         <is>
           <t>주사위 판정 12
 레드 더스티움 45 누적</t>
         </is>
       </c>
     </row>
-    <row r="1346">
-      <c r="A1346" t="inlineStr">
-        <is>
-          <t>data.event.event_05_b.choice_description.73af1899</t>
-        </is>
-      </c>
-      <c r="C1346" t="inlineStr">
-        <is>
-          <t>주사위 판정 8
-레드 더스티움 15 누적</t>
-        </is>
-      </c>
-    </row>
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>data.event.event_05_b.choice_description.ca6b26a1</t>
+          <t>data.event.event_05.choice_description.bcb7167c</t>
         </is>
       </c>
       <c r="C1347" t="inlineStr">
         <is>
-          <t>주사위 판정 12
-레드 더스티움 45 누적</t>
+          <t>누적한 레드 더스티움 획득</t>
         </is>
       </c>
     </row>
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>data.event.event_05.choice_description.bcb7167c</t>
+          <t>data.event.event_05_c.description</t>
         </is>
       </c>
       <c r="C1348" t="inlineStr">
         <is>
-          <t>누적한 레드 더스티움 획득</t>
+          <t>지금까지 채굴한 더스티움을 챙겨 자리를 떠났다.</t>
         </is>
       </c>
     </row>
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>data.event.event_05_c.description</t>
+          <t>data.event.event_05_d.description</t>
         </is>
       </c>
       <c r="C1349" t="inlineStr">
         <is>
-          <t>지금까지 채굴한 더스티움을 챙겨 자리를 떠났다.</t>
+          <t>채굴해 두었던 더스티움마저 잔해 속에 묻혀 버렸다.</t>
         </is>
       </c>
     </row>
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>data.event.event_05_d.description</t>
+          <t>data.event.event_05_e.description</t>
         </is>
       </c>
       <c r="C1350" t="inlineStr">
         <is>
-          <t>채굴해 두었던 더스티움마저 잔해 속에 묻혀 버렸다.</t>
+          <t>붕괴되기 전 모든 더스티움을 확보하는 데 성공했다.</t>
         </is>
       </c>
     </row>
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>data.event.event_05_e.description</t>
+          <t>data.event.event_06.choice_description.478b0fc3</t>
         </is>
       </c>
       <c r="C1351" t="inlineStr">
         <is>
-          <t>붕괴되기 전 모든 더스티움을 확보하는 데 성공했다.</t>
+          <t>상점 이용</t>
         </is>
       </c>
     </row>
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>data.event.event_06.choice_description.478b0fc3</t>
+          <t>data.event.event_06_a.description</t>
         </is>
       </c>
       <c r="C1352" t="inlineStr">
         <is>
-          <t>상점 이용</t>
+          <t>“이 정도면 됐겠지. 오래 붙잡아 둘 생각은 없어.”</t>
         </is>
       </c>
     </row>
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>data.event.event_06_a.description</t>
+          <t>data.event.event_07.choice_description.faf32be2</t>
         </is>
       </c>
       <c r="C1353" t="inlineStr">
         <is>
-          <t>“이 정도면 됐겠지. 오래 붙잡아 둘 생각은 없어.”</t>
+          <t>파티 전원의 최대 생명력 12 증가</t>
         </is>
       </c>
     </row>
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>data.event.event_07.choice_description.faf32be2</t>
+          <t>data.event.event_07.choice_description.eb5b4cdc</t>
         </is>
       </c>
       <c r="C1354" t="inlineStr">
         <is>
-          <t>파티 전원의 최대 생명력 12 증가</t>
+          <t>파티 전원의 최대 마나 2 증가</t>
         </is>
       </c>
     </row>
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>data.event.event_07.choice_description.eb5b4cdc</t>
+          <t>data.event.event_08.choice_description.f5ca5d59</t>
         </is>
       </c>
       <c r="C1355" t="inlineStr">
-        <is>
-          <t>파티 전원의 최대 마나 2 증가</t>
-        </is>
-      </c>
-    </row>
-    <row r="1356">
-      <c r="A1356" t="inlineStr">
-        <is>
-          <t>data.event.event_08.choice_description.f5ca5d59</t>
-        </is>
-      </c>
-      <c r="C1356" t="inlineStr">
         <is>
           <t>성공 확률 90%
 성공: 기억 1개 각성
@@ -54202,13 +54178,13 @@
         </is>
       </c>
     </row>
-    <row r="1357">
-      <c r="A1357" t="inlineStr">
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
         <is>
           <t>data.event.event_08_a.choice_description.4e1c1dc5</t>
         </is>
       </c>
-      <c r="C1357" t="inlineStr">
+      <c r="C1356" t="inlineStr">
         <is>
           <t>성공 확률 50%
 성공: 기억 1개 각성
@@ -54216,13 +54192,13 @@
         </is>
       </c>
     </row>
-    <row r="1358">
-      <c r="A1358" t="inlineStr">
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
         <is>
           <t>data.event.event_08_b.choice_description.a6c0012b</t>
         </is>
       </c>
-      <c r="C1358" t="inlineStr">
+      <c r="C1357" t="inlineStr">
         <is>
           <t>성공 확률 30%
 성공: 기억 1개 각성
@@ -54230,315 +54206,483 @@
         </is>
       </c>
     </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>data.event.event_08.choice_description.97db0284</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>이벤트 종료</t>
+        </is>
+      </c>
+    </row>
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>data.event.event_08.choice_description.97db0284</t>
+          <t>data.event.event_08_c.description</t>
         </is>
       </c>
       <c r="C1359" t="inlineStr">
         <is>
-          <t>이벤트 종료</t>
+          <t>"더 이상 끌어낼 힘은 남아 있지 않은 듯하다.”</t>
         </is>
       </c>
     </row>
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>data.event.event_08_c.description</t>
+          <t>data.event.event_08_d.description</t>
         </is>
       </c>
       <c r="C1360" t="inlineStr">
         <is>
-          <t>"더 이상 끌어낼 힘은 남아 있지 않은 듯하다.”</t>
+          <t>"기억의 흔적은 흩어지고, 더 이상 공명을 이어갈 수 없을 것 같다.”</t>
         </is>
       </c>
     </row>
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>data.event.event_08_d.description</t>
+          <t>data.event.event_09.choice_description.d4f3b6d8</t>
         </is>
       </c>
       <c r="C1361" t="inlineStr">
         <is>
-          <t>"기억의 흔적은 흩어지고, 더 이상 공명을 이어갈 수 없을 것 같다.”</t>
+          <t>무작위 일반~레어 기억 3개 획득</t>
         </is>
       </c>
     </row>
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>data.event.event_09.choice_description.d4f3b6d8</t>
+          <t>data.event.event_09.choice_description.999d991e</t>
         </is>
       </c>
       <c r="C1362" t="inlineStr">
         <is>
-          <t>무작위 일반~레어 기억 3개 획득</t>
+          <t>공격 기억 2개 획득</t>
         </is>
       </c>
     </row>
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>data.event.event_09.choice_description.999d991e</t>
+          <t>data.event.event_09.choice_description.c0517730</t>
         </is>
       </c>
       <c r="C1363" t="inlineStr">
         <is>
-          <t>공격 기억 2개 획득</t>
+          <t>에픽 기억 1개 획득</t>
         </is>
       </c>
     </row>
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>data.event.event_09.choice_description.c0517730</t>
+          <t>battle.skill.move_distance</t>
         </is>
       </c>
       <c r="C1364" t="inlineStr">
         <is>
-          <t>에픽 기억 1개 획득</t>
+          <t>이동 거리</t>
         </is>
       </c>
     </row>
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>battle.skill.move_distance</t>
+          <t>battle.skill_type.all</t>
         </is>
       </c>
       <c r="C1365" t="inlineStr">
         <is>
-          <t>이동 거리</t>
+          <t>전체</t>
         </is>
       </c>
     </row>
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>battle.skill_type.all</t>
+          <t>battle.skill_type.self</t>
         </is>
       </c>
       <c r="C1366" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>개인</t>
         </is>
       </c>
     </row>
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>battle.skill_type.self</t>
+          <t>battle.skill_type.ranged</t>
         </is>
       </c>
       <c r="C1367" t="inlineStr">
         <is>
-          <t>개인</t>
+          <t>원거리</t>
         </is>
       </c>
     </row>
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>battle.skill_type.ranged</t>
+          <t>battle.skill_type.melee</t>
         </is>
       </c>
       <c r="C1368" t="inlineStr">
         <is>
-          <t>원거리</t>
+          <t>근거리</t>
         </is>
       </c>
     </row>
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>battle.skill_type.melee</t>
+          <t>battle.skill_rarity.unique_memory</t>
         </is>
       </c>
       <c r="C1369" t="inlineStr">
         <is>
-          <t>근거리</t>
+          <t>발현기억</t>
         </is>
       </c>
     </row>
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>battle.skill_rarity.unique_memory</t>
+          <t>battle.skill_rarity.ability_memory</t>
         </is>
       </c>
       <c r="C1370" t="inlineStr">
         <is>
-          <t>발현기억</t>
+          <t>구현기억</t>
         </is>
       </c>
     </row>
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>battle.skill_rarity.ability_memory</t>
+          <t>battle.skill_rarity.passive_memory</t>
         </is>
       </c>
       <c r="C1371" t="inlineStr">
         <is>
-          <t>구현기억</t>
+          <t>본능기억</t>
         </is>
       </c>
     </row>
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>battle.skill_rarity.passive_memory</t>
+          <t>battle.skill_rarity.move</t>
         </is>
       </c>
       <c r="C1372" t="inlineStr">
         <is>
-          <t>본능기억</t>
+          <t>이동</t>
         </is>
       </c>
     </row>
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>battle.skill_rarity.move</t>
+          <t>battle.skill_rarity.common_memory</t>
         </is>
       </c>
       <c r="C1373" t="inlineStr">
         <is>
-          <t>이동</t>
+          <t>일반기억</t>
         </is>
       </c>
     </row>
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>battle.skill_rarity.common_memory</t>
+          <t>battle.skill_rarity.rare_memory</t>
         </is>
       </c>
       <c r="C1374" t="inlineStr">
         <is>
-          <t>일반기억</t>
+          <t>레어기억</t>
         </is>
       </c>
     </row>
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>battle.skill_rarity.rare_memory</t>
+          <t>battle.skill_rarity.epic_memory</t>
         </is>
       </c>
       <c r="C1375" t="inlineStr">
         <is>
-          <t>레어기억</t>
+          <t>에픽기억</t>
         </is>
       </c>
     </row>
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>battle.skill_rarity.epic_memory</t>
+          <t>battle.skill_rarity.unique</t>
         </is>
       </c>
       <c r="C1376" t="inlineStr">
         <is>
-          <t>에픽기억</t>
+          <t>유니크기억</t>
         </is>
       </c>
     </row>
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>battle.skill_rarity.unique</t>
+          <t>battle.skill_rarity.exclusive</t>
         </is>
       </c>
       <c r="C1377" t="inlineStr">
         <is>
-          <t>유니크기억</t>
+          <t>전용기억</t>
         </is>
       </c>
     </row>
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>battle.skill_rarity.exclusive</t>
+          <t>ui.battle.equip_panel.character_text</t>
         </is>
       </c>
       <c r="C1378" t="inlineStr">
         <is>
-          <t>전용기억</t>
+          <t>장착할 캐릭터를 선택하세요.</t>
         </is>
       </c>
     </row>
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>ui.battle.equip_panel.character_text</t>
+          <t>ui.check.slogan</t>
         </is>
       </c>
       <c r="C1379" t="inlineStr">
         <is>
-          <t>장착할 캐릭터를 선택하세요.</t>
+          <t>정말로 포기하시겠습니까?</t>
         </is>
       </c>
     </row>
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>ui.check.slogan</t>
+          <t>battle.dustium</t>
         </is>
       </c>
       <c r="C1380" t="inlineStr">
         <is>
-          <t>정말로 포기하시겠습니까?</t>
+          <t>더스티움</t>
         </is>
       </c>
     </row>
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>battle.dustium</t>
+          <t>lobby.karma.acquisition_title</t>
         </is>
       </c>
       <c r="C1381" t="inlineStr">
         <is>
-          <t>더스티움</t>
+          <t>카르마 획득 조건</t>
         </is>
       </c>
     </row>
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>lobby.karma.acquisition_title</t>
+          <t>lobby.karma.description</t>
         </is>
       </c>
       <c r="C1382" t="inlineStr">
         <is>
-          <t>카르마 획득 조건</t>
+          <t>각자의 전투 방식에 따라 축적되며, 기억을 발현하는 힘이 된다.</t>
         </is>
       </c>
     </row>
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>lobby.karma.description</t>
+          <t>lobby.stat.maximum_value</t>
         </is>
       </c>
       <c r="C1383" t="inlineStr">
         <is>
-          <t>각자의 전투 방식에 따라 축적되며, 기억을 발현하는 힘이 된다.</t>
+          <t>최대보유량 {0}</t>
         </is>
       </c>
     </row>
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>lobby.stat.maximum_value</t>
+          <t>ui.option.fullscreenlabel.bbf100b5</t>
         </is>
       </c>
       <c r="C1384" t="inlineStr">
         <is>
-          <t>최대보유량 {0}</t>
+          <t>전체화면</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>ui.option.battlespeedtext.1c466818</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>전투 배속</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>ui.battle.text.9f263f3d</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>유물의 효과</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>ui.battle.text.877a4575</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>유물이름길이</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>ui.lobby.text.79b934c8</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>희미한 흔적만이 남아 있다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>ui.lobby.text.738233fd</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>조합식</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>ui.lobby.text.dd196dfb</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>침식 징후</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>ui.lobby.text.d68c846f</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>유물 효과</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>ui.lobby.text.8229ead1</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>유물이름최대길이</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>ui.lobby.text.e06fba95</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>아이템 효과</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>ui.lobby.text.9361cb41</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>유물최대이름길이</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>ui.lobby.text.5fa154f1</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>아이템 이름</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>ui.lobby.text.ca49a4f1</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>새로고침</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>ui.lobby.text.ce00b05e</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>활성</t>
         </is>
       </c>
     </row>

--- a/Assets/ExcelSource/Localization.xlsx
+++ b/Assets/ExcelSource/Localization.xlsx
@@ -32493,7 +32493,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G1397"/>
+  <dimension ref="A1:G1399"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="212.125" customWidth="1"/>
@@ -54686,6 +54686,30 @@
         </is>
       </c>
     </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>ui.ydh.battletest.text.75dd6a4a</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>거미여왕</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>ui.battle.text.b9a1f4f3</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>타락한 성녀</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Assets/ExcelSource/Localization.xlsx
+++ b/Assets/ExcelSource/Localization.xlsx
@@ -23646,7 +23646,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G1799"/>
+  <dimension ref="A1:G1797"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="212.125" style="1" customWidth="1"/>
@@ -43131,12 +43131,7 @@
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>간파</t>
-        </is>
-      </c>
-      <c r="D870" t="inlineStr">
-        <is>
-          <t>Detection</t>
+          <t>일기당천</t>
         </is>
       </c>
     </row>
@@ -43153,12 +43148,7 @@
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>마나순환</t>
-        </is>
-      </c>
-      <c r="D871" t="inlineStr">
-        <is>
-          <t>Mana Circulation</t>
+          <t>마나리사이클</t>
         </is>
       </c>
     </row>
@@ -43175,12 +43165,7 @@
       </c>
       <c r="C872" t="inlineStr">
         <is>
-          <t>독기</t>
-        </is>
-      </c>
-      <c r="D872" t="inlineStr">
-        <is>
-          <t>Miasma</t>
+          <t>포이즌오라</t>
         </is>
       </c>
     </row>
@@ -43241,12 +43226,7 @@
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>분노의 일격</t>
-        </is>
-      </c>
-      <c r="D875" t="inlineStr">
-        <is>
-          <t>Strike of Fury</t>
+          <t>용의 발톱</t>
         </is>
       </c>
     </row>
@@ -43285,12 +43265,7 @@
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>절명일섬</t>
-        </is>
-      </c>
-      <c r="D877" t="inlineStr">
-        <is>
-          <t>One Day at a Time</t>
+          <t>월영참</t>
         </is>
       </c>
     </row>
@@ -43307,12 +43282,7 @@
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>마력상승</t>
-        </is>
-      </c>
-      <c r="D878" t="inlineStr">
-        <is>
-          <t>Increased Horsepower</t>
+          <t>마나부스트</t>
         </is>
       </c>
     </row>
@@ -43329,12 +43299,7 @@
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>독의 범람</t>
-        </is>
-      </c>
-      <c r="D879" t="inlineStr">
-        <is>
-          <t>Flood of Poison</t>
+          <t>포이즌버스트</t>
         </is>
       </c>
     </row>
@@ -43395,12 +43360,7 @@
       </c>
       <c r="C882" t="inlineStr">
         <is>
-          <t>반월참</t>
-        </is>
-      </c>
-      <c r="D882" t="inlineStr">
-        <is>
-          <t>Banwol Cham</t>
+          <t>휠 슬래시</t>
         </is>
       </c>
     </row>
@@ -43417,12 +43377,7 @@
       </c>
       <c r="C883" t="inlineStr">
         <is>
-          <t>반월참+</t>
-        </is>
-      </c>
-      <c r="D883" t="inlineStr">
-        <is>
-          <t>Half Moon Charm+</t>
+          <t>휠 슬래시+</t>
         </is>
       </c>
     </row>
@@ -43439,12 +43394,7 @@
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>낙룡격</t>
-        </is>
-      </c>
-      <c r="D884" t="inlineStr">
-        <is>
-          <t>Falling Dragon Attack</t>
+          <t>블러드 슬래시</t>
         </is>
       </c>
     </row>
@@ -43461,12 +43411,7 @@
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>낙룡격+</t>
-        </is>
-      </c>
-      <c r="D885" t="inlineStr">
-        <is>
-          <t>Falling Dragon Strike+</t>
+          <t>블러드 슬래시+</t>
         </is>
       </c>
     </row>
@@ -43615,12 +43560,7 @@
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>중독 각인</t>
-        </is>
-      </c>
-      <c r="D892" t="inlineStr">
-        <is>
-          <t>Addiction Imprint</t>
+          <t>베놈</t>
         </is>
       </c>
     </row>
@@ -43637,12 +43577,7 @@
       </c>
       <c r="C893" t="inlineStr">
         <is>
-          <t>중독 각인+</t>
-        </is>
-      </c>
-      <c r="D893" t="inlineStr">
-        <is>
-          <t>Addiction Mark+</t>
+          <t>베놈+</t>
         </is>
       </c>
     </row>
@@ -43747,7 +43682,7 @@
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>철갑 태세</t>
+          <t>가드 오라</t>
         </is>
       </c>
     </row>
@@ -43764,7 +43699,7 @@
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>철갑 태세</t>
+          <t>가드 오라+</t>
         </is>
       </c>
     </row>
@@ -43781,7 +43716,7 @@
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>피의 갑주</t>
+          <t>블러드 아머</t>
         </is>
       </c>
     </row>
@@ -43798,7 +43733,7 @@
       </c>
       <c r="C901" t="inlineStr">
         <is>
-          <t>피의 갑주</t>
+          <t>블러드 아머+</t>
         </is>
       </c>
     </row>
@@ -43815,7 +43750,7 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>불굴의 장막</t>
+          <t>드래곤 테일</t>
         </is>
       </c>
     </row>
@@ -43832,7 +43767,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>불굴의 장막</t>
+          <t>드래곤 테일+</t>
         </is>
       </c>
     </row>
@@ -43849,7 +43784,7 @@
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>피의 갈증</t>
+          <t>브레이크 슬래시</t>
         </is>
       </c>
     </row>
@@ -43866,7 +43801,7 @@
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>피의 갈증</t>
+          <t>브레이스 슬래시+</t>
         </is>
       </c>
     </row>
@@ -43883,7 +43818,7 @@
       </c>
       <c r="C906" t="inlineStr">
         <is>
-          <t>처형자의 기세</t>
+          <t>가시갑옷</t>
         </is>
       </c>
     </row>
@@ -43900,7 +43835,7 @@
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>처형자의 기세</t>
+          <t>가시갑옷+</t>
         </is>
       </c>
     </row>
@@ -43917,7 +43852,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>갑주 파쇄</t>
+          <t>파워 오라</t>
         </is>
       </c>
     </row>
@@ -43934,7 +43869,7 @@
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>갑주 파쇄</t>
+          <t>파워 오라+</t>
         </is>
       </c>
     </row>
@@ -43951,7 +43886,7 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>밀어치기</t>
+          <t>무모한 일격</t>
         </is>
       </c>
     </row>
@@ -43968,7 +43903,7 @@
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>밀어치기</t>
+          <t>무모한 일격+</t>
         </is>
       </c>
     </row>
@@ -43985,7 +43920,7 @@
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>철벽 돌진</t>
+          <t>갈증</t>
         </is>
       </c>
     </row>
@@ -44002,7 +43937,7 @@
       </c>
       <c r="C913" t="inlineStr">
         <is>
-          <t>철벽 돌진</t>
+          <t>갈증+</t>
         </is>
       </c>
     </row>
@@ -44019,7 +43954,7 @@
       </c>
       <c r="C914" t="inlineStr">
         <is>
-          <t>무모한 일격</t>
+          <t>헤비 쓰러스트</t>
         </is>
       </c>
     </row>
@@ -44036,7 +43971,7 @@
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>무모한 일격</t>
+          <t>헤비 쓰러스트+</t>
         </is>
       </c>
     </row>
@@ -44053,7 +43988,7 @@
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>포식하는 칼날</t>
+          <t>핏빛 수확</t>
         </is>
       </c>
     </row>
@@ -44070,7 +44005,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>포식하는 칼날</t>
+          <t>핏빛 수확+</t>
         </is>
       </c>
     </row>
@@ -44087,7 +44022,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>사각 포착</t>
+          <t>간파</t>
         </is>
       </c>
     </row>
@@ -44104,7 +44039,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>사각 포착</t>
+          <t>간파+</t>
         </is>
       </c>
     </row>
@@ -44121,7 +44056,7 @@
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>칼날 세우기</t>
+          <t>비상참</t>
         </is>
       </c>
     </row>
@@ -44138,7 +44073,7 @@
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>칼날 세우기</t>
+          <t>비상참+</t>
         </is>
       </c>
     </row>
@@ -44155,7 +44090,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>상처악화</t>
+          <t>비연참</t>
         </is>
       </c>
     </row>
@@ -44172,7 +44107,7 @@
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>상처악화</t>
+          <t>비연참+</t>
         </is>
       </c>
     </row>
@@ -44189,7 +44124,7 @@
       </c>
       <c r="C924" t="inlineStr">
         <is>
-          <t>혈선 베기</t>
+          <t>전투감각</t>
         </is>
       </c>
     </row>
@@ -44206,7 +44141,7 @@
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>혈선 베기</t>
+          <t>전투감각+</t>
         </is>
       </c>
     </row>
@@ -44223,7 +44158,7 @@
       </c>
       <c r="C926" t="inlineStr">
         <is>
-          <t>상처 벌리기</t>
+          <t>상흔 베기</t>
         </is>
       </c>
     </row>
@@ -44240,7 +44175,7 @@
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>상처 벌리기</t>
+          <t>상흔 베기+</t>
         </is>
       </c>
     </row>
@@ -44257,7 +44192,7 @@
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>흉터 헤집기</t>
+          <t>일섬</t>
         </is>
       </c>
     </row>
@@ -44274,7 +44209,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>흉터 헤집기</t>
+          <t>일섬+</t>
         </is>
       </c>
     </row>
@@ -52277,7 +52212,7 @@
       </c>
       <c r="C1297" t="inlineStr">
         <is>
-          <t>비연참</t>
+          <t>혈맥 찌르기</t>
         </is>
       </c>
     </row>
@@ -52311,7 +52246,7 @@
       </c>
       <c r="C1299" t="inlineStr">
         <is>
-          <t>비연참</t>
+          <t>혈맥 찌르기+</t>
         </is>
       </c>
     </row>
@@ -52345,7 +52280,7 @@
       </c>
       <c r="C1301" t="inlineStr">
         <is>
-          <t>추격참</t>
+          <t>끝없는 검세</t>
         </is>
       </c>
     </row>
@@ -52379,7 +52314,7 @@
       </c>
       <c r="C1303" t="inlineStr">
         <is>
-          <t>추격참</t>
+          <t>끝없는 검세+</t>
         </is>
       </c>
     </row>
@@ -52413,7 +52348,7 @@
       </c>
       <c r="C1305" t="inlineStr">
         <is>
-          <t>섬광베기</t>
+          <t>잔혈참</t>
         </is>
       </c>
     </row>
@@ -52447,7 +52382,7 @@
       </c>
       <c r="C1307" t="inlineStr">
         <is>
-          <t>섬광베기</t>
+          <t>잔혈참+</t>
         </is>
       </c>
     </row>
@@ -52481,7 +52416,7 @@
       </c>
       <c r="C1309" t="inlineStr">
         <is>
-          <t>끝없는 칼날</t>
+          <t>혈화만개</t>
         </is>
       </c>
     </row>
@@ -52515,7 +52450,7 @@
       </c>
       <c r="C1311" t="inlineStr">
         <is>
-          <t>끝없는 칼날</t>
+          <t>혈화만개+</t>
         </is>
       </c>
     </row>
@@ -52549,7 +52484,7 @@
       </c>
       <c r="C1313" t="inlineStr">
         <is>
-          <t>등불의 격려</t>
+          <t>인도하는 불빛</t>
         </is>
       </c>
     </row>
@@ -52583,7 +52518,7 @@
       </c>
       <c r="C1315" t="inlineStr">
         <is>
-          <t>등불의 격려</t>
+          <t>인도하는 불빛+</t>
         </is>
       </c>
     </row>
@@ -52617,7 +52552,7 @@
       </c>
       <c r="C1317" t="inlineStr">
         <is>
-          <t>마력의 불씨</t>
+          <t>희미한 불빛</t>
         </is>
       </c>
     </row>
@@ -52651,7 +52586,7 @@
       </c>
       <c r="C1319" t="inlineStr">
         <is>
-          <t>마력의 불씨</t>
+          <t>희미한 불빛+</t>
         </is>
       </c>
     </row>
@@ -52685,7 +52620,7 @@
       </c>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>인도하는 불빛</t>
+          <t>어두운 그림자</t>
         </is>
       </c>
     </row>
@@ -52719,7 +52654,7 @@
       </c>
       <c r="C1323" t="inlineStr">
         <is>
-          <t>인도하는 불빛</t>
+          <t>어두은 그림자+</t>
         </is>
       </c>
     </row>
@@ -52753,7 +52688,7 @@
       </c>
       <c r="C1325" t="inlineStr">
         <is>
-          <t>길잡이의 등불</t>
+          <t>마나 스파크</t>
         </is>
       </c>
     </row>
@@ -52787,7 +52722,7 @@
       </c>
       <c r="C1327" t="inlineStr">
         <is>
-          <t>길잡이의 등불</t>
+          <t>마나스파크+</t>
         </is>
       </c>
     </row>
@@ -52821,7 +52756,7 @@
       </c>
       <c r="C1329" t="inlineStr">
         <is>
-          <t>희미한 불빛</t>
+          <t>랜턴 샤인</t>
         </is>
       </c>
     </row>
@@ -52855,7 +52790,7 @@
       </c>
       <c r="C1331" t="inlineStr">
         <is>
-          <t>희미한 불빛</t>
+          <t>랜턴 샤인+</t>
         </is>
       </c>
     </row>
@@ -52889,7 +52824,7 @@
       </c>
       <c r="C1333" t="inlineStr">
         <is>
-          <t>쇠약의 연무</t>
+          <t>랜턴 엠버</t>
         </is>
       </c>
     </row>
@@ -52923,7 +52858,7 @@
       </c>
       <c r="C1335" t="inlineStr">
         <is>
-          <t>쇠약의 연무</t>
+          <t>랜턴 엠버+</t>
         </is>
       </c>
     </row>
@@ -52957,7 +52892,7 @@
       </c>
       <c r="C1337" t="inlineStr">
         <is>
-          <t>그림자 올가미</t>
+          <t>포이즌 바이러스</t>
         </is>
       </c>
     </row>
@@ -52991,7 +52926,7 @@
       </c>
       <c r="C1339" t="inlineStr">
         <is>
-          <t>그림자 올가미</t>
+          <t>포이즌 바이러스+</t>
         </is>
       </c>
     </row>
@@ -53025,7 +52960,7 @@
       </c>
       <c r="C1341" t="inlineStr">
         <is>
-          <t>독성 배양</t>
+          <t>소울 드레인</t>
         </is>
       </c>
     </row>
@@ -53059,7 +52994,7 @@
       </c>
       <c r="C1343" t="inlineStr">
         <is>
-          <t>독성 배양</t>
+          <t>소울 드레인+</t>
         </is>
       </c>
     </row>
@@ -53093,7 +53028,7 @@
       </c>
       <c r="C1345" t="inlineStr">
         <is>
-          <t>독충 깨우기</t>
+          <t>쉐도우 바인드</t>
         </is>
       </c>
     </row>
@@ -53127,7 +53062,7 @@
       </c>
       <c r="C1347" t="inlineStr">
         <is>
-          <t>독충 깨우기</t>
+          <t>쉐도우 바인드+</t>
         </is>
       </c>
     </row>
@@ -53161,7 +53096,7 @@
       </c>
       <c r="C1349" t="inlineStr">
         <is>
-          <t>영혼 수확등</t>
+          <t>베놈 어웨이크</t>
         </is>
       </c>
     </row>
@@ -53195,7 +53130,7 @@
       </c>
       <c r="C1351" t="inlineStr">
         <is>
-          <t>영혼 수확등</t>
+          <t>베놈 어웨이크+</t>
         </is>
       </c>
     </row>
@@ -53229,7 +53164,7 @@
       </c>
       <c r="C1353" t="inlineStr">
         <is>
-          <t>치유의 성흔</t>
+          <t>치유의 기도</t>
         </is>
       </c>
     </row>
@@ -53263,7 +53198,7 @@
       </c>
       <c r="C1355" t="inlineStr">
         <is>
-          <t>치유의 성흔</t>
+          <t>치유의 기도+</t>
         </is>
       </c>
     </row>
@@ -53331,7 +53266,7 @@
       </c>
       <c r="C1359" t="inlineStr">
         <is>
-          <t>수호의 기도</t>
+          <t>수호의 기도+</t>
         </is>
       </c>
     </row>
@@ -53365,7 +53300,7 @@
       </c>
       <c r="C1361" t="inlineStr">
         <is>
-          <t>결속의 성호</t>
+          <t>만인의 죄</t>
         </is>
       </c>
     </row>
@@ -53399,7 +53334,7 @@
       </c>
       <c r="C1363" t="inlineStr">
         <is>
-          <t>결속의 성호</t>
+          <t>만인의 죄+</t>
         </is>
       </c>
     </row>
@@ -53433,7 +53368,7 @@
       </c>
       <c r="C1365" t="inlineStr">
         <is>
-          <t>업의 기도</t>
+          <t>죄의 낙인</t>
         </is>
       </c>
     </row>
@@ -53467,7 +53402,7 @@
       </c>
       <c r="C1367" t="inlineStr">
         <is>
-          <t>업의 기도</t>
+          <t>죄의 낙인+</t>
         </is>
       </c>
     </row>
@@ -53501,7 +53436,7 @@
       </c>
       <c r="C1369" t="inlineStr">
         <is>
-          <t>죄의 낙인</t>
+          <t>메디테이션</t>
         </is>
       </c>
     </row>
@@ -53535,7 +53470,7 @@
       </c>
       <c r="C1371" t="inlineStr">
         <is>
-          <t>죄의 낙인</t>
+          <t>메디테이션+</t>
         </is>
       </c>
     </row>
@@ -53569,7 +53504,7 @@
       </c>
       <c r="C1373" t="inlineStr">
         <is>
-          <t>만인의 죄</t>
+          <t>제네시스</t>
         </is>
       </c>
     </row>
@@ -53603,7 +53538,7 @@
       </c>
       <c r="C1375" t="inlineStr">
         <is>
-          <t>만인의 죄</t>
+          <t>제네시스+</t>
         </is>
       </c>
     </row>
@@ -53637,7 +53572,7 @@
       </c>
       <c r="C1377" t="inlineStr">
         <is>
-          <t>징벌의 난타</t>
+          <t>디바인 바인드</t>
         </is>
       </c>
     </row>
@@ -53671,7 +53606,7 @@
       </c>
       <c r="C1379" t="inlineStr">
         <is>
-          <t>징벌의 난타</t>
+          <t>디바인 바인드+</t>
         </is>
       </c>
     </row>
@@ -53705,7 +53640,7 @@
       </c>
       <c r="C1381" t="inlineStr">
         <is>
-          <t>죄업 집행</t>
+          <t>단죄의 쐐기</t>
         </is>
       </c>
     </row>
@@ -53739,7 +53674,7 @@
       </c>
       <c r="C1383" t="inlineStr">
         <is>
-          <t>죄업 집행</t>
+          <t>단죄의 쐐기+</t>
         </is>
       </c>
     </row>
@@ -53773,7 +53708,7 @@
       </c>
       <c r="C1385" t="inlineStr">
         <is>
-          <t>갑주 분쇄</t>
+          <t>낙인 집행</t>
         </is>
       </c>
     </row>
@@ -53807,7 +53742,7 @@
       </c>
       <c r="C1387" t="inlineStr">
         <is>
-          <t>갑주 분쇄</t>
+          <t>낙인 집행+</t>
         </is>
       </c>
     </row>
@@ -53875,7 +53810,7 @@
       </c>
       <c r="C1391" t="inlineStr">
         <is>
-          <t>고해성사</t>
+          <t>고해서사+</t>
         </is>
       </c>
     </row>
@@ -61688,444 +61623,420 @@
     <row r="1763">
       <c r="A1763" t="inlineStr">
         <is>
-          <t>ui.monsterskill.name.f50b42ad</t>
+          <t>ui.monsterskill.detail.75591ba6</t>
         </is>
       </c>
       <c r="C1763" t="inlineStr">
         <is>
-          <t>스킬이름</t>
+          <t>캐릭터와 같은 라인을 맞추기 위해1칸 또는 2칸 최대 2회 이동한다.
+</t>
         </is>
       </c>
     </row>
     <row r="1764">
       <c r="A1764" t="inlineStr">
         <is>
-          <t>ui.monsterskill.detail.75591ba6</t>
+          <t>ui.monsterskill.typetext.d76003b9</t>
         </is>
       </c>
       <c r="C1764" t="inlineStr">
         <is>
-          <t>캐릭터와 같은 라인을 맞추기 위해1칸 또는 2칸 최대 2회 이동한다.
-</t>
+          <t>스킬효과</t>
         </is>
       </c>
     </row>
     <row r="1765">
       <c r="A1765" t="inlineStr">
         <is>
-          <t>ui.monsterskill.typetext.d76003b9</t>
+          <t>ui.monsterstatus.detail.54afa935</t>
         </is>
       </c>
       <c r="C1765" t="inlineStr">
         <is>
-          <t>스킬효과</t>
+          <t>이번 턴에 사망한 변이체 하나를 다음 턴 시작 시 30%의 생명력으로 되살린다.
+</t>
         </is>
       </c>
     </row>
     <row r="1766">
       <c r="A1766" t="inlineStr">
         <is>
-          <t>ui.monsterstatus.name.897a2005</t>
+          <t>ui.battle.monstername.9454ddb5</t>
         </is>
       </c>
       <c r="C1766" t="inlineStr">
         <is>
-          <t>효과이름 99</t>
+          <t>몬스터 이름</t>
         </is>
       </c>
     </row>
     <row r="1767">
       <c r="A1767" t="inlineStr">
         <is>
-          <t>ui.monsterstatus.detail.54afa935</t>
+          <t>ui.battle.name.2022f8c7</t>
         </is>
       </c>
       <c r="C1767" t="inlineStr">
         <is>
-          <t>이번 턴에 사망한 변이체 하나를 다음 턴 시작 시 30%의 생명력으로 되살린다.
-</t>
+          <t>행동</t>
         </is>
       </c>
     </row>
     <row r="1768">
       <c r="A1768" t="inlineStr">
         <is>
-          <t>ui.battle.monstername.9454ddb5</t>
+          <t>ui.battle.name.0f7c69b0</t>
         </is>
       </c>
       <c r="C1768" t="inlineStr">
         <is>
-          <t>몬스터 이름</t>
+          <t>상태</t>
         </is>
       </c>
     </row>
     <row r="1769">
       <c r="A1769" t="inlineStr">
         <is>
-          <t>ui.battle.name.2022f8c7</t>
+          <t>ui.battle.text.8bb824d4</t>
         </is>
       </c>
       <c r="C1769" t="inlineStr">
         <is>
-          <t>행동</t>
+          <t>튜토리얼 내용</t>
         </is>
       </c>
     </row>
     <row r="1770">
       <c r="A1770" t="inlineStr">
         <is>
-          <t>ui.battle.name.0f7c69b0</t>
+          <t>data.effect.e_armor_strike.name</t>
         </is>
       </c>
       <c r="C1770" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>방어도 비례 피해</t>
         </is>
       </c>
     </row>
     <row r="1771">
       <c r="A1771" t="inlineStr">
         <is>
-          <t>ui.battle.text.8bb824d4</t>
+          <t>data.effect.e_armor_strike.tooltip</t>
         </is>
       </c>
       <c r="C1771" t="inlineStr">
         <is>
-          <t>튜토리얼 내용</t>
+          <t>시전자의 현재 방어도에 수치계수를 곱한 피해를 준다.</t>
         </is>
       </c>
     </row>
     <row r="1772">
       <c r="A1772" t="inlineStr">
         <is>
-          <t>data.effect.e_armor_strike.name</t>
+          <t>data.effect.e_miss_self_damage.name</t>
         </is>
       </c>
       <c r="C1772" t="inlineStr">
         <is>
-          <t>방어도 비례 피해</t>
+          <t>빗나감 자해</t>
         </is>
       </c>
     </row>
     <row r="1773">
       <c r="A1773" t="inlineStr">
         <is>
-          <t>data.effect.e_armor_strike.tooltip</t>
+          <t>data.effect.e_miss_self_damage.tooltip</t>
         </is>
       </c>
       <c r="C1773" t="inlineStr">
         <is>
-          <t>시전자의 현재 방어도에 수치계수를 곱한 피해를 준다.</t>
+          <t>유효한 적을 맞히지 못하면 자신에게 수치만큼 피해를 준다.</t>
         </is>
       </c>
     </row>
     <row r="1774">
       <c r="A1774" t="inlineStr">
         <is>
-          <t>data.effect.e_miss_self_damage.name</t>
+          <t>data.effect.e_value_up_on_kill.name</t>
         </is>
       </c>
       <c r="C1774" t="inlineStr">
         <is>
-          <t>빗나감 자해</t>
+          <t>처치 시 영구 피해 증가</t>
         </is>
       </c>
     </row>
     <row r="1775">
       <c r="A1775" t="inlineStr">
         <is>
-          <t>data.effect.e_miss_self_damage.tooltip</t>
+          <t>data.effect.e_value_up_on_kill.tooltip</t>
         </is>
       </c>
       <c r="C1775" t="inlineStr">
         <is>
-          <t>유효한 적을 맞히지 못하면 자신에게 수치만큼 피해를 준다.</t>
+          <t>이 스킬로 처치한 적 하나당 다음 사용부터 피해 수치가 증가한다.</t>
         </is>
       </c>
     </row>
     <row r="1776">
       <c r="A1776" t="inlineStr">
         <is>
-          <t>data.effect.e_value_up_on_kill.name</t>
+          <t>data.effect.e_value_up_on_hit.name</t>
         </is>
       </c>
       <c r="C1776" t="inlineStr">
         <is>
-          <t>처치 시 영구 피해 증가</t>
+          <t>명중 시 전투 피해 증가</t>
         </is>
       </c>
     </row>
     <row r="1777">
       <c r="A1777" t="inlineStr">
         <is>
-          <t>data.effect.e_value_up_on_kill.tooltip</t>
+          <t>data.effect.e_value_up_on_hit.tooltip</t>
         </is>
       </c>
       <c r="C1777" t="inlineStr">
         <is>
-          <t>이 스킬로 처치한 적 하나당 다음 사용부터 피해 수치가 증가한다.</t>
+          <t>성공한 타격마다 이 전투 동안 다음 사용부터 피해 수치가 증가한다.</t>
         </is>
       </c>
     </row>
     <row r="1778">
       <c r="A1778" t="inlineStr">
         <is>
-          <t>data.effect.e_value_up_on_hit.name</t>
+          <t>data.effect.e_damage_up_if_bleeding.name</t>
         </is>
       </c>
       <c r="C1778" t="inlineStr">
         <is>
-          <t>명중 시 전투 피해 증가</t>
+          <t>출혈 대상 피해 증가</t>
         </is>
       </c>
     </row>
     <row r="1779">
       <c r="A1779" t="inlineStr">
         <is>
-          <t>data.effect.e_value_up_on_hit.tooltip</t>
+          <t>data.effect.e_damage_up_if_bleeding.tooltip</t>
         </is>
       </c>
       <c r="C1779" t="inlineStr">
         <is>
-          <t>성공한 타격마다 이 전투 동안 다음 사용부터 피해 수치가 증가한다.</t>
+          <t>출혈이 있는 대상에게 주는 피해가 50% 증가한다.</t>
         </is>
       </c>
     </row>
     <row r="1780">
       <c r="A1780" t="inlineStr">
         <is>
-          <t>data.effect.e_damage_up_if_bleeding.name</t>
+          <t>data.effect.e_rush.name</t>
         </is>
       </c>
       <c r="C1780" t="inlineStr">
         <is>
-          <t>출혈 대상 피해 증가</t>
+          <t>돌진</t>
         </is>
       </c>
     </row>
     <row r="1781">
       <c r="A1781" t="inlineStr">
         <is>
-          <t>data.effect.e_damage_up_if_bleeding.tooltip</t>
+          <t>data.effect.e_rush.tooltip</t>
         </is>
       </c>
       <c r="C1781" t="inlineStr">
         <is>
-          <t>출혈이 있는 대상에게 주는 피해가 50% 증가한다.</t>
+          <t>지정 칸만큼 전진하며 첫 충돌 대상 앞에서 멈춘다.</t>
         </is>
       </c>
     </row>
     <row r="1782">
       <c r="A1782" t="inlineStr">
         <is>
-          <t>data.effect.e_rush.name</t>
+          <t>data.effect.e_bondage.name</t>
         </is>
       </c>
       <c r="C1782" t="inlineStr">
         <is>
-          <t>돌진</t>
+          <t>속박</t>
         </is>
       </c>
     </row>
     <row r="1783">
       <c r="A1783" t="inlineStr">
         <is>
-          <t>data.effect.e_rush.tooltip</t>
+          <t>data.effect.e_bondage.tooltip</t>
         </is>
       </c>
       <c r="C1783" t="inlineStr">
         <is>
-          <t>지정 칸만큼 전진하며 첫 충돌 대상 앞에서 멈춘다.</t>
+          <t>다음 이동 시도 1회를 막고 수치가 1 감소한다.</t>
         </is>
       </c>
     </row>
     <row r="1784">
       <c r="A1784" t="inlineStr">
         <is>
-          <t>data.effect.e_bondage.name</t>
+          <t>data.effect.e_poison_by_target_poison.name</t>
         </is>
       </c>
       <c r="C1784" t="inlineStr">
         <is>
-          <t>속박</t>
+          <t>중독 비례 중독</t>
         </is>
       </c>
     </row>
     <row r="1785">
       <c r="A1785" t="inlineStr">
         <is>
-          <t>data.effect.e_bondage.tooltip</t>
+          <t>data.effect.e_poison_by_target_poison.tooltip</t>
         </is>
       </c>
       <c r="C1785" t="inlineStr">
         <is>
-          <t>다음 이동 시도 1회를 막고 수치가 1 감소한다.</t>
+          <t>대상의 중독 수치를 수치계수로 나눈 몫만큼 중독을 추가한다.</t>
         </is>
       </c>
     </row>
     <row r="1786">
       <c r="A1786" t="inlineStr">
         <is>
-          <t>data.effect.e_poison_by_target_poison.name</t>
+          <t>data.effect.e_trigger_poison.name</t>
         </is>
       </c>
       <c r="C1786" t="inlineStr">
         <is>
-          <t>중독 비례 중독</t>
+          <t>중독 즉시 발동</t>
         </is>
       </c>
     </row>
     <row r="1787">
       <c r="A1787" t="inlineStr">
         <is>
-          <t>data.effect.e_poison_by_target_poison.tooltip</t>
+          <t>data.effect.e_trigger_poison.tooltip</t>
         </is>
       </c>
       <c r="C1787" t="inlineStr">
         <is>
-          <t>대상의 중독 수치를 수치계수로 나눈 몫만큼 중독을 추가한다.</t>
+          <t>현재 중독 수치만큼 즉시 피해를 주고 중독 수치를 1 감소시킨다.</t>
         </is>
       </c>
     </row>
     <row r="1788">
       <c r="A1788" t="inlineStr">
         <is>
-          <t>data.effect.e_trigger_poison.name</t>
+          <t>data.effect.e_restore_mana_per_hit_target.name</t>
         </is>
       </c>
       <c r="C1788" t="inlineStr">
         <is>
-          <t>중독 즉시 발동</t>
+          <t>타격당 마나 회복</t>
         </is>
       </c>
     </row>
     <row r="1789">
       <c r="A1789" t="inlineStr">
         <is>
-          <t>data.effect.e_trigger_poison.tooltip</t>
+          <t>data.effect.e_restore_mana_per_hit_target.tooltip</t>
         </is>
       </c>
       <c r="C1789" t="inlineStr">
         <is>
-          <t>현재 중독 수치만큼 즉시 피해를 주고 중독 수치를 1 감소시킨다.</t>
+          <t>성공한 총 타격 수에 비례해 마나를 회복한다.</t>
         </is>
       </c>
     </row>
     <row r="1790">
       <c r="A1790" t="inlineStr">
         <is>
-          <t>data.effect.e_restore_mana_per_hit_target.name</t>
+          <t>data.effect.e_random_strike.name</t>
         </is>
       </c>
       <c r="C1790" t="inlineStr">
         <is>
-          <t>타격당 마나 회복</t>
+          <t>무작위 연속 타격</t>
         </is>
       </c>
     </row>
     <row r="1791">
       <c r="A1791" t="inlineStr">
         <is>
-          <t>data.effect.e_restore_mana_per_hit_target.tooltip</t>
+          <t>data.effect.e_random_strike.tooltip</t>
         </is>
       </c>
       <c r="C1791" t="inlineStr">
         <is>
-          <t>성공한 총 타격 수에 비례해 마나를 회복한다.</t>
+          <t>범위 내 살아 있는 적을 매 타격마다 다시 추첨해 피해를 준다.</t>
         </is>
       </c>
     </row>
     <row r="1792">
       <c r="A1792" t="inlineStr">
         <is>
-          <t>data.effect.e_random_strike.name</t>
+          <t>data.effect.e_strike_by_vulnerable.name</t>
         </is>
       </c>
       <c r="C1792" t="inlineStr">
         <is>
-          <t>무작위 연속 타격</t>
+          <t>취약 비례 피해</t>
         </is>
       </c>
     </row>
     <row r="1793">
       <c r="A1793" t="inlineStr">
         <is>
-          <t>data.effect.e_random_strike.tooltip</t>
+          <t>data.effect.e_strike_by_vulnerable.tooltip</t>
         </is>
       </c>
       <c r="C1793" t="inlineStr">
         <is>
-          <t>범위 내 살아 있는 적을 매 타격마다 다시 추첨해 피해를 준다.</t>
+          <t>기본 피해에 대상 취약 수치와 횟수계수의 곱을 더한다.</t>
         </is>
       </c>
     </row>
     <row r="1794">
       <c r="A1794" t="inlineStr">
         <is>
-          <t>data.effect.e_strike_by_vulnerable.name</t>
+          <t>data.effect.e_strike_count_by_buff.name</t>
         </is>
       </c>
       <c r="C1794" t="inlineStr">
         <is>
-          <t>취약 비례 피해</t>
+          <t>버프 종류 비례 타격</t>
         </is>
       </c>
     </row>
     <row r="1795">
       <c r="A1795" t="inlineStr">
         <is>
-          <t>data.effect.e_strike_by_vulnerable.tooltip</t>
+          <t>data.effect.e_strike_count_by_buff.tooltip</t>
         </is>
       </c>
       <c r="C1795" t="inlineStr">
         <is>
-          <t>기본 피해에 대상 취약 수치와 횟수계수의 곱을 더한다.</t>
+          <t>시전자의 서로 다른 이로운 효과 종류 수만큼 타격 횟수가 증가한다.</t>
         </is>
       </c>
     </row>
     <row r="1796">
       <c r="A1796" t="inlineStr">
         <is>
-          <t>data.effect.e_strike_count_by_buff.name</t>
+          <t>data.effect.e_strike_count_by_debuff.name</t>
         </is>
       </c>
       <c r="C1796" t="inlineStr">
         <is>
-          <t>버프 종류 비례 타격</t>
+          <t>디버프 종류 비례 타격</t>
         </is>
       </c>
     </row>
     <row r="1797">
       <c r="A1797" t="inlineStr">
         <is>
-          <t>data.effect.e_strike_count_by_buff.tooltip</t>
+          <t>data.effect.e_strike_count_by_debuff.tooltip</t>
         </is>
       </c>
       <c r="C1797" t="inlineStr">
-        <is>
-          <t>시전자의 서로 다른 이로운 효과 종류 수만큼 타격 횟수가 증가한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1798">
-      <c r="A1798" t="inlineStr">
-        <is>
-          <t>data.effect.e_strike_count_by_debuff.name</t>
-        </is>
-      </c>
-      <c r="C1798" t="inlineStr">
-        <is>
-          <t>디버프 종류 비례 타격</t>
-        </is>
-      </c>
-    </row>
-    <row r="1799">
-      <c r="A1799" t="inlineStr">
-        <is>
-          <t>data.effect.e_strike_count_by_debuff.tooltip</t>
-        </is>
-      </c>
-      <c r="C1799" t="inlineStr">
         <is>
           <t>대상의 서로 다른 해로운 효과 종류 수만큼 타격 횟수가 증가한다.</t>
         </is>

--- a/Assets/ExcelSource/Localization.xlsx
+++ b/Assets/ExcelSource/Localization.xlsx
@@ -51934,7 +51934,7 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>발현검무</t>
+          <t>환영검무</t>
         </is>
       </c>
     </row>
@@ -51968,7 +51968,7 @@
       </c>
       <c r="C1290" t="inlineStr">
         <is>
-          <t>발현검무+</t>
+          <t>환영검무+</t>
         </is>
       </c>
     </row>
@@ -52002,7 +52002,7 @@
       </c>
       <c r="C1292" t="inlineStr">
         <is>
-          <t>끝없는 검세</t>
+          <t>공단참</t>
         </is>
       </c>
     </row>
@@ -52036,7 +52036,7 @@
       </c>
       <c r="C1294" t="inlineStr">
         <is>
-          <t>끝없는 검세+</t>
+          <t>공단참+</t>
         </is>
       </c>
     </row>

--- a/Assets/ExcelSource/Localization.xlsx
+++ b/Assets/ExcelSource/Localization.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8831B8-5BB4-41C9-9436-F206391CB196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8682FD9A-9C04-4CE6-B14F-331B32E3C24F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7999" uniqueCount="7384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8120" uniqueCount="7505">
   <si>
     <t>Key</t>
   </si>
@@ -22275,6 +22275,369 @@
   </si>
   <si>
     <t>Si falla el ataque, la vida disminuye en {0}.</t>
+  </si>
+  <si>
+    <t>skill.sentence.count.single</t>
+  </si>
+  <si>
+    <t>8700601600000000000</t>
+  </si>
+  <si>
+    <t>skill.sentence.count.multiple</t>
+  </si>
+  <si>
+    <t>8700601600000000001</t>
+  </si>
+  <si>
+    <t>{0}회</t>
+  </si>
+  <si>
+    <t>{0} times</t>
+  </si>
+  <si>
+    <t>，共{0}次</t>
+  </si>
+  <si>
+    <t>{0}回</t>
+  </si>
+  <si>
+    <t>{0} veces</t>
+  </si>
+  <si>
+    <t>skill.sentence.effect.e_move.e_strike</t>
+  </si>
+  <si>
+    <t>8700601600000000002</t>
+  </si>
+  <si>
+    <t>{1}칸 전진한 후 {0}를 {2}만큼{3} 준다.</t>
+  </si>
+  <si>
+    <t>Advance {1} tile(s), then deal {2} damage{3}.</t>
+  </si>
+  <si>
+    <t>向前移动{1}格，然后造成{2}点伤害{3}。</t>
+  </si>
+  <si>
+    <t>{1}マス前進後、{2}ダメージを{3}与える。</t>
+  </si>
+  <si>
+    <t>Avanza {1} casillas y luego inflige {2} de daño{3}.</t>
+  </si>
+  <si>
+    <t>skill.sentence.effect.e_strike.e_move</t>
+  </si>
+  <si>
+    <t>8700601600000000003</t>
+  </si>
+  <si>
+    <t>{0}를 {1}만큼{3} 주고 {2}칸 후퇴한다.</t>
+  </si>
+  <si>
+    <t>Deal {1} damage{3}, then retreat {2} tile(s).</t>
+  </si>
+  <si>
+    <t>造成{1}点伤害{3}，然后后退{2}格。</t>
+  </si>
+  <si>
+    <t>{1}ダメージを{3}与えた後、{2}マス後退する。</t>
+  </si>
+  <si>
+    <t>Inflige {1} de daño{3} y luego retrocede {2} casillas.</t>
+  </si>
+  <si>
+    <t>skill.sentence.effect.e_damageupifbleeding</t>
+  </si>
+  <si>
+    <t>8700601600000000004</t>
+  </si>
+  <si>
+    <t>{0}를 {1}만큼{3} 준다. {5}을 보유한 적에게 주는 피해량이 50% 증가한다.</t>
+  </si>
+  <si>
+    <t>Deal {1} damage{3}. Deal 50% more damage to enemies affected by {5}.</t>
+  </si>
+  <si>
+    <t>造成{1}点伤害{3}。对带有{5}的敌人造成的伤害提高50%。</t>
+  </si>
+  <si>
+    <t>{1}ダメージを{3}与える。{5}状態の敵へのダメージが50%増加する。</t>
+  </si>
+  <si>
+    <t>Inflige {1} de daño{3}. El daño aumenta un 50% contra enemigos con {5}.</t>
+  </si>
+  <si>
+    <t>skill.sentence.effect.e_strikecountbybuff</t>
+  </si>
+  <si>
+    <t>8700601600000000005</t>
+  </si>
+  <si>
+    <t>{0}를 {1}만큼{3} 준다. 보유한 버프 1종마다 공격 횟수가 1 증가한다.</t>
+  </si>
+  <si>
+    <t>Deal {1} damage{3}. Gain one additional hit for each different buff you have.</t>
+  </si>
+  <si>
+    <t>造成{1}点伤害{3}。每拥有一种不同的增益效果，攻击次数增加1次。</t>
+  </si>
+  <si>
+    <t>{1}ダメージを{3}与える。所持しているバフ1種類につき攻撃回数が1回増加する。</t>
+  </si>
+  <si>
+    <t>Inflige {1} de daño{3}. Añade un golpe por cada tipo de mejora que tengas.</t>
+  </si>
+  <si>
+    <t>skill.sentence.effect.e_pierce.e_valueuponhit</t>
+  </si>
+  <si>
+    <t>8700601600000000006</t>
+  </si>
+  <si>
+    <t>{4}를 {1}만큼{3} 준다. 적중 시 이번 전투 동안 피해량이 {2} 증가한다.</t>
+  </si>
+  <si>
+    <t>Deal {1} piercing damage{3}. On hit, increase this skill’s damage by {2} for the rest of the battle.</t>
+  </si>
+  <si>
+    <t>造成{1}点穿透伤害{3}。命中时，此技能在本场战斗中的伤害增加{2}点。</t>
+  </si>
+  <si>
+    <t>{1}の貫通ダメージを{3}与える。命中時、この戦闘中はこのスキルのダメージが{2}増加する。</t>
+  </si>
+  <si>
+    <t>Inflige {1} de daño perforante{3}. Al impactar, el daño de esta habilidad aumenta {2} durante el combate.</t>
+  </si>
+  <si>
+    <t>skill.sentence.effect.e_pierce.e_bleed</t>
+  </si>
+  <si>
+    <t>8700601600000000007</t>
+  </si>
+  <si>
+    <t>{4}를 {1}만큼{3} 준다. 최대 사거리에서 적중 시 {5}을 {2}만큼 부여한다.</t>
+  </si>
+  <si>
+    <t>Deal {1} piercing damage{3}. On a hit at maximum range, apply {2} {5}.</t>
+  </si>
+  <si>
+    <t>造成{1}点穿透伤害{3}。在最大射程命中时施加{2}层{5}。</t>
+  </si>
+  <si>
+    <t>{1}の貫通ダメージを{3}与える。最大射程で命中すると{5}を{2}付与する。</t>
+  </si>
+  <si>
+    <t>Inflige {1} de daño perforante{3}. Al impactar al alcance máximo, aplica {2} de {5}.</t>
+  </si>
+  <si>
+    <t>skill.sentence.effect.e_armor.e_cure</t>
+  </si>
+  <si>
+    <t>8700601600000000200</t>
+  </si>
+  <si>
+    <t>{6}를 {1}만큼 부여하고, {7}을 {2}만큼 회복한다.</t>
+  </si>
+  <si>
+    <t>Grant {1} Armor and restore {2} HP.</t>
+  </si>
+  <si>
+    <t>赋予{1}点护甲，并恢复{2}点生命值。</t>
+  </si>
+  <si>
+    <t>防御力を{1}付与し、HPを{2}回復する。</t>
+  </si>
+  <si>
+    <t>Otorga {1} de armadura y restaura {2} PV.</t>
+  </si>
+  <si>
+    <t>skill.sentence.effect.e_strike.e_grab</t>
+  </si>
+  <si>
+    <t>8700601600000000201</t>
+  </si>
+  <si>
+    <t>{0}를 {1}만큼{3} 주고, {8}을 {2}칸 적용한다.</t>
+  </si>
+  <si>
+    <t>Deal {1} damage{3} and pull the target {2} tile(s).</t>
+  </si>
+  <si>
+    <t>造成{1}点伤害{3}，并将目标拉近{2}格。</t>
+  </si>
+  <si>
+    <t>{1}ダメージを{3}与え、対象を{2}マス引き寄せる。</t>
+  </si>
+  <si>
+    <t>Inflige {1} de daño{3} y atrae al objetivo {2} casillas.</t>
+  </si>
+  <si>
+    <t>skill.sentence.effect.e_armor.e_ward</t>
+  </si>
+  <si>
+    <t>8700601600000000202</t>
+  </si>
+  <si>
+    <t>{6}를 {1}만큼 부여하고, 가시를 {2}만큼 부여한다.</t>
+  </si>
+  <si>
+    <t>Grant {1} Armor and {2} Thorns.</t>
+  </si>
+  <si>
+    <t>赋予{1}点护甲和{2}层荆棘。</t>
+  </si>
+  <si>
+    <t>防御力を{1}、棘を{2}付与する。</t>
+  </si>
+  <si>
+    <t>Otorga {1} de armadura y {2} de espinas.</t>
+  </si>
+  <si>
+    <t>skill.sentence.effect.e_karma</t>
+  </si>
+  <si>
+    <t>8700601600000000203</t>
+  </si>
+  <si>
+    <t>{10}를 {1}만큼 획득한다.</t>
+  </si>
+  <si>
+    <t>Gain {1} Karma.</t>
+  </si>
+  <si>
+    <t>获得{1}点业力。</t>
+  </si>
+  <si>
+    <t>カルマを{1}獲得する。</t>
+  </si>
+  <si>
+    <t>Obtén {1} de karma.</t>
+  </si>
+  <si>
+    <t>skill.sentence.effect.e_randomstrike</t>
+  </si>
+  <si>
+    <t>8700601600000000204</t>
+  </si>
+  <si>
+    <t>범위 내 무작위 적의 위치에 {0}를 {1}만큼{3} 준다.</t>
+  </si>
+  <si>
+    <t>Deal {1} damage{3} to randomly selected enemy positions within range.</t>
+  </si>
+  <si>
+    <t>对范围内随机敌人所在位置造成{1}点伤害{3}。</t>
+  </si>
+  <si>
+    <t>範囲内の敵の位置をランダムに選び、{1}ダメージを{3}与える。</t>
+  </si>
+  <si>
+    <t>Inflige {1} de daño{3} en posiciones de enemigos elegidas al azar dentro del alcance.</t>
+  </si>
+  <si>
+    <t>skill.sentence.effect.e_vulnerable</t>
+  </si>
+  <si>
+    <t>8700601600000000205</t>
+  </si>
+  <si>
+    <t>{11}을 {1}만큼 부여한다.</t>
+  </si>
+  <si>
+    <t>Apply {1} Vulnerable.</t>
+  </si>
+  <si>
+    <t>施加{1}层易伤。</t>
+  </si>
+  <si>
+    <t>脆弱を{1}付与する。</t>
+  </si>
+  <si>
+    <t>Aplica {1} de Vulnerabilidad.</t>
+  </si>
+  <si>
+    <t>skill.sentence.effect.e_bond</t>
+  </si>
+  <si>
+    <t>8700601600000000206</t>
+  </si>
+  <si>
+    <t>{12}를 {1}만큼 부여한다.</t>
+  </si>
+  <si>
+    <t>Grant {1} Bond.</t>
+  </si>
+  <si>
+    <t>赋予{1}层羁绊。</t>
+  </si>
+  <si>
+    <t>絆を{1}付与する。</t>
+  </si>
+  <si>
+    <t>Otorga {1} de vínculo.</t>
+  </si>
+  <si>
+    <t>skill.sentence.effect.e_strike.e_strikebyvulnerable</t>
+  </si>
+  <si>
+    <t>8700601600000000207</t>
+  </si>
+  <si>
+    <t>{0}를 {1}만큼{3} 준다. 대상이 보유한 {11} 수치만큼 피해량이 증가한다.</t>
+  </si>
+  <si>
+    <t>Deal {1} damage{3}. Increase damage by the target’s Vulnerable stacks.</t>
+  </si>
+  <si>
+    <t>造成{1}点伤害{3}。根据目标持有的易伤层数提高伤害。</t>
+  </si>
+  <si>
+    <t>{1}ダメージを{3}与える。対象の脆弱の数値に応じてダメージが増加する。</t>
+  </si>
+  <si>
+    <t>Inflige {1} de daño{3}. Aumenta el daño según las acumulaciones de Vulnerabilidad del objetivo.</t>
+  </si>
+  <si>
+    <t>skill.sentence.effect.e_debuffdouble</t>
+  </si>
+  <si>
+    <t>8700601600000000208</t>
+  </si>
+  <si>
+    <t>대상이 보유한 수치가 가장 높은 디버프 1종의 수치를 {1}배로 만든다.</t>
+  </si>
+  <si>
+    <t>Multiply the highest-stack debuff on the target by {1}.</t>
+  </si>
+  <si>
+    <t>将目标层数最高的一种减益效果变为原来的{1}倍。</t>
+  </si>
+  <si>
+    <t>対象が持つ最も数値の高いデバフ1種類の数値を{1}倍にする。</t>
+  </si>
+  <si>
+    <t>Multiplica por {1} el efecto negativo con más acumulaciones del objetivo.</t>
+  </si>
+  <si>
+    <t>skill.sentence.effect.e_removearmor</t>
+  </si>
+  <si>
+    <t>8700601600000000209</t>
+  </si>
+  <si>
+    <t>대상의 {6}를 제거한다.</t>
+  </si>
+  <si>
+    <t>Remove the target’s Armor.</t>
+  </si>
+  <si>
+    <t>移除目标的护甲。</t>
+  </si>
+  <si>
+    <t>対象の防御力を除去する。</t>
+  </si>
+  <si>
+    <t>Elimina la armadura del objetivo.</t>
   </si>
 </sst>
 </file>
@@ -23183,7 +23546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1744"/>
+  <dimension ref="A1:M1762"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="9" style="7"/>
@@ -50718,6 +51081,406 @@
         <v>7383</v>
       </c>
     </row>
+    <row r="1745" spans="1:7">
+      <c r="A1745" s="7" t="s">
+        <v>7384</v>
+      </c>
+      <c r="B1745" s="7" t="s">
+        <v>7385</v>
+      </c>
+      <c r="C1745" s="7"/>
+    </row>
+    <row r="1746" spans="1:7">
+      <c r="A1746" s="7" t="s">
+        <v>7386</v>
+      </c>
+      <c r="B1746" s="7" t="s">
+        <v>7387</v>
+      </c>
+      <c r="C1746" s="7" t="s">
+        <v>7388</v>
+      </c>
+      <c r="D1746" s="7" t="s">
+        <v>7389</v>
+      </c>
+      <c r="E1746" s="7" t="s">
+        <v>7390</v>
+      </c>
+      <c r="F1746" s="7" t="s">
+        <v>7391</v>
+      </c>
+      <c r="G1746" s="7" t="s">
+        <v>7392</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:7">
+      <c r="A1747" s="7" t="s">
+        <v>7393</v>
+      </c>
+      <c r="B1747" s="7" t="s">
+        <v>7394</v>
+      </c>
+      <c r="C1747" s="7" t="s">
+        <v>7395</v>
+      </c>
+      <c r="D1747" s="7" t="s">
+        <v>7396</v>
+      </c>
+      <c r="E1747" s="7" t="s">
+        <v>7397</v>
+      </c>
+      <c r="F1747" s="7" t="s">
+        <v>7398</v>
+      </c>
+      <c r="G1747" s="7" t="s">
+        <v>7399</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:7">
+      <c r="A1748" s="7" t="s">
+        <v>7400</v>
+      </c>
+      <c r="B1748" s="7" t="s">
+        <v>7401</v>
+      </c>
+      <c r="C1748" s="7" t="s">
+        <v>7402</v>
+      </c>
+      <c r="D1748" s="7" t="s">
+        <v>7403</v>
+      </c>
+      <c r="E1748" s="7" t="s">
+        <v>7404</v>
+      </c>
+      <c r="F1748" s="7" t="s">
+        <v>7405</v>
+      </c>
+      <c r="G1748" s="7" t="s">
+        <v>7406</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:7">
+      <c r="A1749" s="7" t="s">
+        <v>7407</v>
+      </c>
+      <c r="B1749" s="7" t="s">
+        <v>7408</v>
+      </c>
+      <c r="C1749" s="7" t="s">
+        <v>7409</v>
+      </c>
+      <c r="D1749" s="7" t="s">
+        <v>7410</v>
+      </c>
+      <c r="E1749" s="7" t="s">
+        <v>7411</v>
+      </c>
+      <c r="F1749" s="7" t="s">
+        <v>7412</v>
+      </c>
+      <c r="G1749" s="7" t="s">
+        <v>7413</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:7">
+      <c r="A1750" s="7" t="s">
+        <v>7414</v>
+      </c>
+      <c r="B1750" s="7" t="s">
+        <v>7415</v>
+      </c>
+      <c r="C1750" s="7" t="s">
+        <v>7416</v>
+      </c>
+      <c r="D1750" s="7" t="s">
+        <v>7417</v>
+      </c>
+      <c r="E1750" s="7" t="s">
+        <v>7418</v>
+      </c>
+      <c r="F1750" s="7" t="s">
+        <v>7419</v>
+      </c>
+      <c r="G1750" s="7" t="s">
+        <v>7420</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:7">
+      <c r="A1751" s="7" t="s">
+        <v>7421</v>
+      </c>
+      <c r="B1751" s="7" t="s">
+        <v>7422</v>
+      </c>
+      <c r="C1751" s="7" t="s">
+        <v>7423</v>
+      </c>
+      <c r="D1751" s="7" t="s">
+        <v>7424</v>
+      </c>
+      <c r="E1751" s="7" t="s">
+        <v>7425</v>
+      </c>
+      <c r="F1751" s="7" t="s">
+        <v>7426</v>
+      </c>
+      <c r="G1751" s="7" t="s">
+        <v>7427</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:7">
+      <c r="A1752" s="7" t="s">
+        <v>7428</v>
+      </c>
+      <c r="B1752" s="7" t="s">
+        <v>7429</v>
+      </c>
+      <c r="C1752" s="7" t="s">
+        <v>7430</v>
+      </c>
+      <c r="D1752" s="7" t="s">
+        <v>7431</v>
+      </c>
+      <c r="E1752" s="7" t="s">
+        <v>7432</v>
+      </c>
+      <c r="F1752" s="7" t="s">
+        <v>7433</v>
+      </c>
+      <c r="G1752" s="7" t="s">
+        <v>7434</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:7">
+      <c r="A1753" s="7" t="s">
+        <v>7435</v>
+      </c>
+      <c r="B1753" s="7" t="s">
+        <v>7436</v>
+      </c>
+      <c r="C1753" s="7" t="s">
+        <v>7437</v>
+      </c>
+      <c r="D1753" s="7" t="s">
+        <v>7438</v>
+      </c>
+      <c r="E1753" s="7" t="s">
+        <v>7439</v>
+      </c>
+      <c r="F1753" s="7" t="s">
+        <v>7440</v>
+      </c>
+      <c r="G1753" s="7" t="s">
+        <v>7441</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:7">
+      <c r="A1754" s="7" t="s">
+        <v>7442</v>
+      </c>
+      <c r="B1754" s="7" t="s">
+        <v>7443</v>
+      </c>
+      <c r="C1754" s="7" t="s">
+        <v>7444</v>
+      </c>
+      <c r="D1754" s="7" t="s">
+        <v>7445</v>
+      </c>
+      <c r="E1754" s="7" t="s">
+        <v>7446</v>
+      </c>
+      <c r="F1754" s="7" t="s">
+        <v>7447</v>
+      </c>
+      <c r="G1754" s="7" t="s">
+        <v>7448</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:7">
+      <c r="A1755" s="7" t="s">
+        <v>7449</v>
+      </c>
+      <c r="B1755" s="7" t="s">
+        <v>7450</v>
+      </c>
+      <c r="C1755" s="7" t="s">
+        <v>7451</v>
+      </c>
+      <c r="D1755" s="7" t="s">
+        <v>7452</v>
+      </c>
+      <c r="E1755" s="7" t="s">
+        <v>7453</v>
+      </c>
+      <c r="F1755" s="7" t="s">
+        <v>7454</v>
+      </c>
+      <c r="G1755" s="7" t="s">
+        <v>7455</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:7">
+      <c r="A1756" s="7" t="s">
+        <v>7456</v>
+      </c>
+      <c r="B1756" s="7" t="s">
+        <v>7457</v>
+      </c>
+      <c r="C1756" s="7" t="s">
+        <v>7458</v>
+      </c>
+      <c r="D1756" s="7" t="s">
+        <v>7459</v>
+      </c>
+      <c r="E1756" s="7" t="s">
+        <v>7460</v>
+      </c>
+      <c r="F1756" s="7" t="s">
+        <v>7461</v>
+      </c>
+      <c r="G1756" s="7" t="s">
+        <v>7462</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:7">
+      <c r="A1757" s="7" t="s">
+        <v>7463</v>
+      </c>
+      <c r="B1757" s="7" t="s">
+        <v>7464</v>
+      </c>
+      <c r="C1757" s="7" t="s">
+        <v>7465</v>
+      </c>
+      <c r="D1757" s="7" t="s">
+        <v>7466</v>
+      </c>
+      <c r="E1757" s="7" t="s">
+        <v>7467</v>
+      </c>
+      <c r="F1757" s="7" t="s">
+        <v>7468</v>
+      </c>
+      <c r="G1757" s="7" t="s">
+        <v>7469</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:7">
+      <c r="A1758" s="7" t="s">
+        <v>7470</v>
+      </c>
+      <c r="B1758" s="7" t="s">
+        <v>7471</v>
+      </c>
+      <c r="C1758" s="7" t="s">
+        <v>7472</v>
+      </c>
+      <c r="D1758" s="7" t="s">
+        <v>7473</v>
+      </c>
+      <c r="E1758" s="7" t="s">
+        <v>7474</v>
+      </c>
+      <c r="F1758" s="7" t="s">
+        <v>7475</v>
+      </c>
+      <c r="G1758" s="7" t="s">
+        <v>7476</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:7">
+      <c r="A1759" s="7" t="s">
+        <v>7477</v>
+      </c>
+      <c r="B1759" s="7" t="s">
+        <v>7478</v>
+      </c>
+      <c r="C1759" s="7" t="s">
+        <v>7479</v>
+      </c>
+      <c r="D1759" s="7" t="s">
+        <v>7480</v>
+      </c>
+      <c r="E1759" s="7" t="s">
+        <v>7481</v>
+      </c>
+      <c r="F1759" s="7" t="s">
+        <v>7482</v>
+      </c>
+      <c r="G1759" s="7" t="s">
+        <v>7483</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:7">
+      <c r="A1760" s="7" t="s">
+        <v>7484</v>
+      </c>
+      <c r="B1760" s="7" t="s">
+        <v>7485</v>
+      </c>
+      <c r="C1760" s="7" t="s">
+        <v>7486</v>
+      </c>
+      <c r="D1760" s="7" t="s">
+        <v>7487</v>
+      </c>
+      <c r="E1760" s="7" t="s">
+        <v>7488</v>
+      </c>
+      <c r="F1760" s="7" t="s">
+        <v>7489</v>
+      </c>
+      <c r="G1760" s="7" t="s">
+        <v>7490</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:7">
+      <c r="A1761" s="7" t="s">
+        <v>7491</v>
+      </c>
+      <c r="B1761" s="7" t="s">
+        <v>7492</v>
+      </c>
+      <c r="C1761" s="7" t="s">
+        <v>7493</v>
+      </c>
+      <c r="D1761" s="7" t="s">
+        <v>7494</v>
+      </c>
+      <c r="E1761" s="7" t="s">
+        <v>7495</v>
+      </c>
+      <c r="F1761" s="7" t="s">
+        <v>7496</v>
+      </c>
+      <c r="G1761" s="7" t="s">
+        <v>7497</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:7">
+      <c r="A1762" s="7" t="s">
+        <v>7498</v>
+      </c>
+      <c r="B1762" s="7" t="s">
+        <v>7499</v>
+      </c>
+      <c r="C1762" s="7" t="s">
+        <v>7500</v>
+      </c>
+      <c r="D1762" s="7" t="s">
+        <v>7501</v>
+      </c>
+      <c r="E1762" s="7" t="s">
+        <v>7502</v>
+      </c>
+      <c r="F1762" s="7" t="s">
+        <v>7503</v>
+      </c>
+      <c r="G1762" s="7" t="s">
+        <v>7504</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/ExcelSource/Localization.xlsx
+++ b/Assets/ExcelSource/Localization.xlsx
@@ -922,7 +922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1773"/>
+  <dimension ref="A1:M1776"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9" customWidth="1" style="1" min="1" max="2"/>
@@ -32009,22 +32009,22 @@
       </c>
       <c r="D1164" s="1" t="inlineStr">
         <is>
-          <t>{E_Strike} {ValueRate1} 적중 실패 시 생명력 -{ValueRate2}</t>
+          <t>{E_Strike} {ValueRate1} / On miss, lose {ValueRate2} HP</t>
         </is>
       </c>
       <c r="E1164" s="1" t="inlineStr">
         <is>
-          <t>{E_Strike} {ValueRate1} 적중 실패 시 생명력 -{ValueRate2}</t>
+          <t>{E_Strike} {ValueRate1} / 未命中时失去 {ValueRate2} 点生命值</t>
         </is>
       </c>
       <c r="F1164" s="1" t="inlineStr">
         <is>
-          <t>{E_Strike} {ValueRate1} 적중 실패 시 생명력 -{ValueRate2}</t>
+          <t>{E_Strike} {ValueRate1} / ミス時、HPを{ValueRate2}失う</t>
         </is>
       </c>
       <c r="G1164" s="1" t="inlineStr">
         <is>
-          <t>{E_Strike} {ValueRate1} 적중 실패 시 생명력 -{ValueRate2}</t>
+          <t>{E_Strike} {ValueRate1} / Al fallar, pierde {ValueRate2} de PS</t>
         </is>
       </c>
     </row>
@@ -32120,22 +32120,22 @@
       </c>
       <c r="D1167" s="1" t="inlineStr">
         <is>
-          <t>{E_Strike} {ValueRate1} 처치 시 영구히 피해량 {ValueRate2}</t>
+          <t>{E_Strike} {ValueRate1} / On kill, permanently increase damage by {ValueRate2}</t>
         </is>
       </c>
       <c r="E1167" s="1" t="inlineStr">
         <is>
-          <t>{E_Strike} {ValueRate1} 처치 시 영구히 피해량 {ValueRate2}</t>
+          <t>{E_Strike} {ValueRate1} / 击杀时，伤害永久提高 {ValueRate2}</t>
         </is>
       </c>
       <c r="F1167" s="1" t="inlineStr">
         <is>
-          <t>{E_Strike} {ValueRate1} 처치 시 영구히 피해량 {ValueRate2}</t>
+          <t>{E_Strike} {ValueRate1} / 撃破時、ダメージが永続的に{ValueRate2}増加</t>
         </is>
       </c>
       <c r="G1167" s="1" t="inlineStr">
         <is>
-          <t>{E_Strike} {ValueRate1} 처치 시 영구히 피해량 {ValueRate2}</t>
+          <t>{E_Strike} {ValueRate1} / Al matar, aumenta permanentemente el daño en {ValueRate2}</t>
         </is>
       </c>
     </row>
@@ -45592,27 +45592,27 @@
       </c>
       <c r="C1768" s="1" t="inlineStr">
         <is>
-          <t>{0}턴 시작</t>
+          <t>{0}턴</t>
         </is>
       </c>
       <c r="D1768" s="1" t="inlineStr">
         <is>
-          <t>Turn {0} Start</t>
+          <t>Turn {0}</t>
         </is>
       </c>
       <c r="E1768" s="1" t="inlineStr">
         <is>
-          <t>第{0}回合开始</t>
+          <t>第{0}回合</t>
         </is>
       </c>
       <c r="F1768" s="1" t="inlineStr">
         <is>
-          <t>ターン{0}開始</t>
+          <t>{0}ターン</t>
         </is>
       </c>
       <c r="G1768" s="1" t="inlineStr">
         <is>
-          <t>Inicio del turno {0}</t>
+          <t>Turno {0}</t>
         </is>
       </c>
     </row>
@@ -45728,72 +45728,183 @@
       </c>
     </row>
     <row r="1772">
-      <c r="A1772" t="inlineStr">
+      <c r="A1772" s="1" t="inlineStr">
         <is>
           <t>battle.reward.red_dustium</t>
         </is>
       </c>
-      <c r="B1772" t="n">
+      <c r="B1772" s="1" t="n">
         <v>9.164888147097976e+18</v>
       </c>
-      <c r="C1772" t="inlineStr">
+      <c r="C1772" s="1" t="inlineStr">
         <is>
           <t>레드 더스티움</t>
         </is>
       </c>
-      <c r="D1772" t="inlineStr">
+      <c r="D1772" s="1" t="inlineStr">
         <is>
           <t>Red Dustium</t>
         </is>
       </c>
-      <c r="E1772" t="inlineStr">
+      <c r="E1772" s="1" t="inlineStr">
         <is>
           <t>红尘晶</t>
         </is>
       </c>
-      <c r="F1772" t="inlineStr">
+      <c r="F1772" s="1" t="inlineStr">
         <is>
           <t>レッドダスティウム</t>
         </is>
       </c>
-      <c r="G1772" t="inlineStr">
+      <c r="G1772" s="1" t="inlineStr">
         <is>
           <t>Dustium rojo</t>
         </is>
       </c>
     </row>
     <row r="1773">
-      <c r="A1773" t="inlineStr">
+      <c r="A1773" s="1" t="inlineStr">
         <is>
           <t>battle.reward.relic_acquired</t>
         </is>
       </c>
-      <c r="B1773" t="n">
+      <c r="B1773" s="1" t="n">
         <v>9.164888147097976e+18</v>
       </c>
-      <c r="C1773" t="inlineStr">
+      <c r="C1773" s="1" t="inlineStr">
         <is>
           <t>유물 획득</t>
         </is>
       </c>
-      <c r="D1773" t="inlineStr">
+      <c r="D1773" s="1" t="inlineStr">
         <is>
           <t>Relic Acquired</t>
         </is>
       </c>
-      <c r="E1773" t="inlineStr">
+      <c r="E1773" s="1" t="inlineStr">
         <is>
           <t>获得遗物</t>
         </is>
       </c>
-      <c r="F1773" t="inlineStr">
+      <c r="F1773" s="1" t="inlineStr">
         <is>
           <t>レリック獲得</t>
         </is>
       </c>
-      <c r="G1773" t="inlineStr">
+      <c r="G1773" s="1" t="inlineStr">
         <is>
           <t>Reliquia obtenida</t>
+        </is>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" s="1" t="inlineStr">
+        <is>
+          <t>battle.reward.skill_panel_title</t>
+        </is>
+      </c>
+      <c r="B1774" s="1" t="inlineStr">
+        <is>
+          <t>9164888147097975811</t>
+        </is>
+      </c>
+      <c r="C1774" s="1" t="inlineStr">
+        <is>
+          <t>기억</t>
+        </is>
+      </c>
+      <c r="D1774" s="1" t="inlineStr">
+        <is>
+          <t>Memory</t>
+        </is>
+      </c>
+      <c r="E1774" s="1" t="inlineStr">
+        <is>
+          <t>记忆</t>
+        </is>
+      </c>
+      <c r="F1774" s="1" t="inlineStr">
+        <is>
+          <t>記憶</t>
+        </is>
+      </c>
+      <c r="G1774" s="1" t="inlineStr">
+        <is>
+          <t>Memoria</t>
+        </is>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" s="1" t="inlineStr">
+        <is>
+          <t>battle.reward.skill_acquired</t>
+        </is>
+      </c>
+      <c r="B1775" s="1" t="inlineStr">
+        <is>
+          <t>9164888147097975812</t>
+        </is>
+      </c>
+      <c r="C1775" s="1" t="inlineStr">
+        <is>
+          <t>기억 획득</t>
+        </is>
+      </c>
+      <c r="D1775" s="1" t="inlineStr">
+        <is>
+          <t>Memory Acquired</t>
+        </is>
+      </c>
+      <c r="E1775" s="1" t="inlineStr">
+        <is>
+          <t>获得记忆</t>
+        </is>
+      </c>
+      <c r="F1775" s="1" t="inlineStr">
+        <is>
+          <t>記憶獲得</t>
+        </is>
+      </c>
+      <c r="G1775" s="1" t="inlineStr">
+        <is>
+          <t>Memoria adquirida</t>
+        </is>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" s="1" t="inlineStr">
+        <is>
+          <t>event.result.memory_acquired_format</t>
+        </is>
+      </c>
+      <c r="B1776" s="1" t="inlineStr">
+        <is>
+          <t>9164888147097975813</t>
+        </is>
+      </c>
+      <c r="C1776" s="1" t="inlineStr">
+        <is>
+          <t>기억 획득: {0}</t>
+        </is>
+      </c>
+      <c r="D1776" s="1" t="inlineStr">
+        <is>
+          <t>Memory Acquired: {0}</t>
+        </is>
+      </c>
+      <c r="E1776" s="1" t="inlineStr">
+        <is>
+          <t>获得记忆：{0}</t>
+        </is>
+      </c>
+      <c r="F1776" s="1" t="inlineStr">
+        <is>
+          <t>記憶獲得：{0}</t>
+        </is>
+      </c>
+      <c r="G1776" s="1" t="inlineStr">
+        <is>
+          <t>Memoria adquirida: {0}</t>
         </is>
       </c>
     </row>

--- a/Assets/ExcelSource/Localization.xlsx
+++ b/Assets/ExcelSource/Localization.xlsx
@@ -22120,7 +22120,7 @@
     <t>skill.sentence.deal.amount.multiple.final</t>
   </si>
   <si>
-    <t>{0}{1} {2}만큼 {3}회 피해를 준다</t>
+    <t>{0}{1} {2}만큼 {3}회 준다</t>
   </si>
   <si>
     <t>Deal {2} {0} {3} times</t>
@@ -22129,7 +22129,7 @@
     <t>skill.sentence.deal.amount.single.final</t>
   </si>
   <si>
-    <t>{0}{1} {2}만큼 피해를 준다</t>
+    <t>{0}{1} {2}만큼 준다</t>
   </si>
   <si>
     <t>Deal {2} {0}</t>
@@ -22138,7 +22138,7 @@
     <t>skill.sentence.deal.amount.single.linked</t>
   </si>
   <si>
-    <t>{0}{1} {2}만큼 피해를 주고</t>
+    <t>{0}{1} {2}만큼 주고</t>
   </si>
   <si>
     <t>skill.sentence.gain.amount.single.final</t>

--- a/Assets/ExcelSource/Localization.xlsx
+++ b/Assets/ExcelSource/Localization.xlsx
@@ -44055,17 +44055,20 @@
       </c>
     </row>
     <row r="1278" spans="1:4">
-      <c r="A1278" s="1" t="s">
-        <v>5870</v>
-      </c>
-      <c r="B1278" s="1" t="s">
-        <v>5871</v>
-      </c>
-      <c r="C1278" s="1" t="s">
-        <v>5872</v>
-      </c>
-      <c r="D1278" s="1" t="s">
-        <v>5873</v>
+      <c r="A1278" s="1" t="inlineStr">
+        <is>
+          <t>data.grid_effect.gr_debris.tooltip</t>
+        </is>
+      </c>
+      <c r="B1278" s="1" t="inlineStr">
+        <is>
+          <t>17531528627626026</t>
+        </is>
+      </c>
+      <c r="C1278" s="1" t="inlineStr">
+        <is>
+          <t>이동을 방해하는 부서진 구조물.</t>
+        </is>
       </c>
     </row>
     <row r="1279" spans="1:4">
@@ -44251,17 +44254,20 @@
       </c>
     </row>
     <row r="1292" spans="1:4">
-      <c r="A1292" s="1" t="s">
-        <v>5920</v>
-      </c>
-      <c r="B1292" s="1" t="s">
-        <v>5921</v>
-      </c>
-      <c r="C1292" s="1" t="s">
-        <v>5922</v>
-      </c>
-      <c r="D1292" s="1" t="s">
-        <v>5923</v>
+      <c r="A1292" s="1" t="inlineStr">
+        <is>
+          <t>data.grid_effect.gr_nocturn_portal_preview.tooltip</t>
+        </is>
+      </c>
+      <c r="B1292" s="1" t="inlineStr">
+        <is>
+          <t>17531528627626042</t>
+        </is>
+      </c>
+      <c r="C1292" s="1" t="inlineStr">
+        <is>
+          <t>어둠이 깃든 공간.</t>
+        </is>
       </c>
     </row>
     <row r="1293" spans="1:4">
@@ -49533,17 +49539,20 @@
       </c>
     </row>
     <row r="1692" spans="1:4">
-      <c r="A1692" s="1" t="s">
-        <v>7172</v>
-      </c>
-      <c r="B1692" s="1" t="s">
-        <v>7173</v>
-      </c>
-      <c r="C1692" s="1" t="s">
-        <v>7174</v>
-      </c>
-      <c r="D1692" s="1" t="s">
-        <v>7175</v>
+      <c r="A1692" s="1" t="inlineStr">
+        <is>
+          <t>data.effect.e_necromancy.tooltip</t>
+        </is>
+      </c>
+      <c r="B1692" s="1" t="inlineStr">
+        <is>
+          <t>9164888147097975827</t>
+        </is>
+      </c>
+      <c r="C1692" s="1" t="inlineStr">
+        <is>
+          <t>유골이 된 변이체를 최대 생명력의 30%로 부활시킨다.</t>
+        </is>
       </c>
     </row>
     <row r="1693" spans="1:4">
@@ -50414,6 +50423,30 @@
       </c>
       <c r="D1770" s="1" t="s">
         <v>7347</v>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" t="inlineStr">
+        <is>
+          <t>data.grid_effect.gr_skull_bone.name</t>
+        </is>
+      </c>
+      <c r="C1771" t="inlineStr">
+        <is>
+          <t>유골</t>
+        </is>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" t="inlineStr">
+        <is>
+          <t>data.grid_effect.gr_skull_bone.tooltip</t>
+        </is>
+      </c>
+      <c r="C1772" t="inlineStr">
+        <is>
+          <t>이동을 방해하는 뼈 무더기.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Assets/ExcelSource/Localization.xlsx
+++ b/Assets/ExcelSource/Localization.xlsx
@@ -44013,31 +44013,37 @@
       </c>
     </row>
     <row r="1275" spans="1:4">
-      <c r="A1275" s="1" t="s">
-        <v>5862</v>
-      </c>
-      <c r="B1275" s="1" t="s">
-        <v>5863</v>
-      </c>
-      <c r="C1275" s="1" t="s">
-        <v>5712</v>
-      </c>
-      <c r="D1275" s="1" t="s">
-        <v>5713</v>
+      <c r="A1275" s="1" t="inlineStr">
+        <is>
+          <t>data.monster_skill.s_monster_39.effect_description</t>
+        </is>
+      </c>
+      <c r="B1275" s="1" t="inlineStr">
+        <is>
+          <t>17531528627626017</t>
+        </is>
+      </c>
+      <c r="C1275" s="1" t="inlineStr">
+        <is>
+          <t>낙인에 도약하여 {E_Strike}를 {ValueRate1}만큼 주고, {E_Knockback}을 {ValueRate2}칸 적용한다.</t>
+        </is>
       </c>
     </row>
     <row r="1276" spans="1:4">
-      <c r="A1276" s="1" t="s">
-        <v>5864</v>
-      </c>
-      <c r="B1276" s="1" t="s">
-        <v>5865</v>
-      </c>
-      <c r="C1276" s="1" t="s">
-        <v>5738</v>
-      </c>
-      <c r="D1276" s="1" t="s">
-        <v>5739</v>
+      <c r="A1276" s="1" t="inlineStr">
+        <is>
+          <t>data.monster_skill.s_monster_40.effect_description</t>
+        </is>
+      </c>
+      <c r="B1276" s="1" t="inlineStr">
+        <is>
+          <t>17531528627626020</t>
+        </is>
+      </c>
+      <c r="C1276" s="1" t="inlineStr">
+        <is>
+          <t>가장 먼 대상의 위치에 {E_Strike}를 {ValueRate1}만큼 주고, {E_Poison}을 {ValueRate2} 부여한다.</t>
+        </is>
       </c>
     </row>
     <row r="1277" spans="1:4">
@@ -44887,143 +44893,139 @@
       </c>
     </row>
     <row r="1337" spans="1:4">
-      <c r="A1337" s="1" t="s">
-        <v>6084</v>
-      </c>
-      <c r="B1337" s="1" t="s">
-        <v>6085</v>
-      </c>
-      <c r="C1337" s="1" t="s">
-        <v>6086</v>
-      </c>
-      <c r="D1337" s="1" t="s">
-        <v>6087</v>
+      <c r="A1337" s="1" t="inlineStr">
+        <is>
+          <t>data.battle_map.battlemap_01.description</t>
+        </is>
+      </c>
+      <c r="B1337" s="1" t="inlineStr">
+        <is>
+          <t>17531528627626087</t>
+        </is>
+      </c>
+      <c r="C1337" s="1" t="inlineStr">
+        <is>
+          <t>블롭, 머크, 머크</t>
+        </is>
       </c>
     </row>
     <row r="1338" spans="1:4">
-      <c r="A1338" s="1" t="s">
-        <v>6088</v>
-      </c>
-      <c r="B1338" s="1" t="s">
-        <v>6089</v>
-      </c>
-      <c r="C1338" s="1" t="s">
-        <v>6090</v>
-      </c>
-      <c r="D1338" s="1" t="s">
-        <v>6091</v>
+      <c r="A1338" s="1" t="inlineStr">
+        <is>
+          <t>data.battle_map.battlemap_02.description</t>
+        </is>
+      </c>
+      <c r="B1338" s="1" t="inlineStr">
+        <is>
+          <t>17531528627626088</t>
+        </is>
+      </c>
+      <c r="C1338" s="1" t="inlineStr">
+        <is>
+          <t>블롭, 블롭</t>
+        </is>
       </c>
     </row>
     <row r="1339" spans="1:4">
-      <c r="A1339" s="1" t="s">
-        <v>6092</v>
-      </c>
-      <c r="B1339" s="1" t="s">
-        <v>6093</v>
-      </c>
-      <c r="C1339" s="1" t="s">
-        <v>6094</v>
-      </c>
-      <c r="D1339" s="1" t="s">
-        <v>6095</v>
+      <c r="A1339" s="1" t="inlineStr">
+        <is>
+          <t>data.battle_map.battlemap_03.description</t>
+        </is>
+      </c>
+      <c r="B1339" s="1" t="inlineStr">
+        <is>
+          <t>17531528627626089</t>
+        </is>
+      </c>
+      <c r="C1339" s="1" t="inlineStr">
+        <is>
+          <t>베스파, 베스파</t>
+        </is>
       </c>
     </row>
     <row r="1340" spans="1:4">
-      <c r="A1340" s="1" t="s">
-        <v>6096</v>
-      </c>
-      <c r="B1340" s="1" t="s">
-        <v>6097</v>
-      </c>
-      <c r="C1340" s="1" t="s">
-        <v>6098</v>
-      </c>
-      <c r="D1340" s="1" t="s">
-        <v>6099</v>
+      <c r="A1340" s="1" t="inlineStr">
+        <is>
+          <t>data.battle_map.battlemap_04.description</t>
+        </is>
+      </c>
+      <c r="B1340" s="1" t="inlineStr">
+        <is>
+          <t>17531528627626090</t>
+        </is>
+      </c>
+      <c r="C1340" s="1" t="inlineStr">
+        <is>
+          <t>드라우그, 신더, 랜서</t>
+        </is>
       </c>
     </row>
     <row r="1341" spans="1:4">
-      <c r="A1341" s="1" t="s">
-        <v>6100</v>
-      </c>
-      <c r="B1341" s="1" t="s">
-        <v>6101</v>
-      </c>
-      <c r="C1341" s="1" t="s">
-        <v>6102</v>
-      </c>
-      <c r="D1341" s="1" t="s">
-        <v>6103</v>
+      <c r="A1341" s="1" t="inlineStr">
+        <is>
+          <t>data.battle_map.battlemap_05.description</t>
+        </is>
+      </c>
+      <c r="B1341" s="1" t="inlineStr">
+        <is>
+          <t>17531528627626091</t>
+        </is>
+      </c>
+      <c r="C1341" s="1" t="inlineStr">
+        <is>
+          <t>바로우, 신더, 블라이트</t>
+        </is>
       </c>
     </row>
     <row r="1342" spans="1:4">
-      <c r="A1342" s="1" t="s">
-        <v>6104</v>
-      </c>
-      <c r="B1342" s="1" t="s">
-        <v>6105</v>
-      </c>
-      <c r="C1342" s="1" t="s">
-        <v>6106</v>
-      </c>
-      <c r="D1342" s="1" t="s">
-        <v>6107</v>
+      <c r="A1342" s="1" t="inlineStr">
+        <is>
+          <t>data.battle_map.battlemap_06.description</t>
+        </is>
+      </c>
+      <c r="B1342" s="1" t="inlineStr">
+        <is>
+          <t>17531528627626092</t>
+        </is>
+      </c>
+      <c r="C1342" s="1" t="inlineStr">
+        <is>
+          <t>드라우그, 바로우</t>
+        </is>
       </c>
     </row>
     <row r="1343" spans="1:4">
-      <c r="A1343" s="1" t="s">
-        <v>6108</v>
-      </c>
-      <c r="B1343" s="1" t="s">
-        <v>6109</v>
-      </c>
-      <c r="C1343" s="1" t="s">
-        <v>6110</v>
-      </c>
-      <c r="D1343" s="1" t="s">
-        <v>6111</v>
+      <c r="A1343" s="1" t="inlineStr">
+        <is>
+          <t>data.battle_map.battlemap_07.description</t>
+        </is>
+      </c>
+      <c r="B1343" s="1" t="inlineStr">
+        <is>
+          <t>17531528627626093</t>
+        </is>
+      </c>
+      <c r="C1343" s="1" t="inlineStr">
+        <is>
+          <t>베스파, 드라우그, 랜서</t>
+        </is>
       </c>
     </row>
     <row r="1344" spans="1:4">
-      <c r="A1344" s="1" t="s">
-        <v>6112</v>
-      </c>
-      <c r="B1344" s="1" t="s">
-        <v>6113</v>
-      </c>
-      <c r="C1344" s="1" t="s">
-        <v>6114</v>
-      </c>
-      <c r="D1344" s="1" t="s">
-        <v>6115</v>
-      </c>
-    </row>
-    <row r="1345" spans="1:4">
-      <c r="A1345" s="1" t="s">
-        <v>6116</v>
-      </c>
-      <c r="B1345" s="1" t="s">
-        <v>6117</v>
-      </c>
-      <c r="C1345" s="1" t="s">
-        <v>6118</v>
-      </c>
-      <c r="D1345" s="1" t="s">
-        <v>6119</v>
-      </c>
-    </row>
-    <row r="1346" spans="1:4">
-      <c r="A1346" s="1" t="s">
-        <v>6120</v>
-      </c>
-      <c r="B1346" s="1" t="s">
-        <v>6121</v>
-      </c>
-      <c r="C1346" s="1" t="s">
-        <v>6122</v>
-      </c>
-      <c r="D1346" s="1" t="s">
-        <v>6123</v>
+      <c r="A1344" s="1" t="inlineStr">
+        <is>
+          <t>data.battle_map.battlemap_08.description</t>
+        </is>
+      </c>
+      <c r="B1344" s="1" t="inlineStr">
+        <is>
+          <t>17531528627626094</t>
+        </is>
+      </c>
+      <c r="C1344" s="1" t="inlineStr">
+        <is>
+          <t>바로우, 바로우, 블라이트</t>
+        </is>
       </c>
     </row>
     <row r="1347" spans="1:4">
@@ -45097,17 +45099,20 @@
       </c>
     </row>
     <row r="1352" spans="1:4">
-      <c r="A1352" s="1" t="s">
-        <v>6144</v>
-      </c>
-      <c r="B1352" s="1" t="s">
-        <v>6145</v>
-      </c>
-      <c r="C1352" s="1" t="s">
-        <v>6146</v>
-      </c>
-      <c r="D1352" s="1" t="s">
-        <v>6147</v>
+      <c r="A1352" s="1" t="inlineStr">
+        <is>
+          <t>data.battle_map.battlemap_16.description</t>
+        </is>
+      </c>
+      <c r="B1352" s="1" t="inlineStr">
+        <is>
+          <t>17531528627626102</t>
+        </is>
+      </c>
+      <c r="C1352" s="1" t="inlineStr">
+        <is>
+          <t>아라벨라</t>
+        </is>
       </c>
     </row>
     <row r="1353" spans="1:4">
@@ -50449,6 +50454,54 @@
         </is>
       </c>
     </row>
+    <row r="1773">
+      <c r="A1773" t="inlineStr">
+        <is>
+          <t>data.monster_skill.s_monster_39.name</t>
+        </is>
+      </c>
+      <c r="C1773" t="inlineStr">
+        <is>
+          <t>사냥 강습</t>
+        </is>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" t="inlineStr">
+        <is>
+          <t>data.monster_skill.s_monster_40.name</t>
+        </is>
+      </c>
+      <c r="C1774" t="inlineStr">
+        <is>
+          <t>맹독 세례</t>
+        </is>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" t="inlineStr">
+        <is>
+          <t>data.grid_effect.gr_stigma.name</t>
+        </is>
+      </c>
+      <c r="C1775" t="inlineStr">
+        <is>
+          <t>낙인</t>
+        </is>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" t="inlineStr">
+        <is>
+          <t>data.grid_effect.gr_stigma.tooltip</t>
+        </is>
+      </c>
+      <c r="C1776" t="inlineStr">
+        <is>
+          <t>사냥감에게 드리운 포식의 징조.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Assets/ExcelSource/Localization.xlsx
+++ b/Assets/ExcelSource/Localization.xlsx
@@ -23084,7 +23084,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1735"/>
+  <dimension ref="A1:G1738"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="9" style="1" customWidth="1"/>
@@ -35176,7 +35176,8 @@
       </c>
       <c r="C653" s="1" t="inlineStr">
         <is>
-          <t>레드 더스티움 15 소모, 무작위 일반~에픽 기억 발현</t>
+          <t>레드 더스티움 15 소모
+무작위 일반~에픽 기억 발현</t>
         </is>
       </c>
     </row>
@@ -35210,7 +35211,8 @@
       </c>
       <c r="C655" s="1" t="inlineStr">
         <is>
-          <t>주사위 6 이상, 무작위 일반~레어 유물 획득</t>
+          <t>주사위 6 이상
+무작위 일반~레어 유물 획득</t>
         </is>
       </c>
     </row>
@@ -35244,7 +35246,9 @@
       </c>
       <c r="C657" s="1" t="inlineStr">
         <is>
-          <t>주사위 6 이상, 레드 더스티움 30 획득</t>
+          <t>주사위 6 이상
+레드 더스티움 30 획득
+실패 : 생명력 5 감소</t>
         </is>
       </c>
     </row>
@@ -35278,7 +35282,8 @@
       </c>
       <c r="C659" s="1" t="inlineStr">
         <is>
-          <t>예측 성공 시, 레드 더스티움 25 획득</t>
+          <t>예측 : 앞면 or 뒷면
+레드 더스티움 25 획득</t>
         </is>
       </c>
     </row>
@@ -35312,7 +35317,7 @@
       </c>
       <c r="C661" s="1" t="inlineStr">
         <is>
-          <t>모든 파티원 최대 생명력 5 증가</t>
+          <t>모든 파티원 최대 생명력 10 증가</t>
         </is>
       </c>
     </row>
@@ -38577,7 +38582,9 @@
       </c>
       <c r="C894" s="1" t="inlineStr">
         <is>
-          <t>주사위 10 이상, 레드 더스티움 50 획득</t>
+          <t>주사위 10 이상
+레드 더스티움 50 획득
+실패 : 생명력 5 감소</t>
         </is>
       </c>
     </row>
@@ -49137,79 +49144,79 @@
     <row r="1669">
       <c r="A1669" t="inlineStr">
         <is>
-          <t>data.event.event_04.description.cceaa4ca</t>
+          <t>data.event.event_04.choice_2_disabled_description</t>
         </is>
       </c>
       <c r="C1669" t="inlineStr">
         <is>
-          <t>레드 더스티움 30 소모, 무작위 레어~유니크 기억 발현</t>
+          <t>레드 더스티움 부족</t>
         </is>
       </c>
     </row>
     <row r="1670">
       <c r="A1670" t="inlineStr">
         <is>
-          <t>data.event.event_04.choice_2_disabled_description</t>
+          <t>data.event.event_04.description.97db0284</t>
         </is>
       </c>
       <c r="C1670" t="inlineStr">
         <is>
-          <t>레드 더스티움 부족</t>
+          <t>이벤트 종료</t>
         </is>
       </c>
     </row>
     <row r="1671">
       <c r="A1671" t="inlineStr">
         <is>
-          <t>data.event.event_04.description.97db0284</t>
+          <t>data.event.event_06.choice_2_name</t>
         </is>
       </c>
       <c r="C1671" t="inlineStr">
+        <is>
+          <t>지나친다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>data.event.event_06.description.97db0284</t>
+        </is>
+      </c>
+      <c r="C1672" t="inlineStr">
         <is>
           <t>이벤트 종료</t>
         </is>
       </c>
     </row>
-    <row r="1672">
-      <c r="A1672" t="inlineStr">
-        <is>
-          <t>data.event.event_05.description.6a125e1c</t>
-        </is>
-      </c>
-      <c r="C1672" t="inlineStr">
-        <is>
-          <t>주사위 8 이상, 무작위 레어~에픽 유물 획득</t>
-        </is>
-      </c>
-    </row>
     <row r="1673">
       <c r="A1673" t="inlineStr">
         <is>
-          <t>data.event.event_05.description.251b1503</t>
+          <t>data.event.event_06_a.choice_1_name</t>
         </is>
       </c>
       <c r="C1673" t="inlineStr">
         <is>
-          <t>주사위 10 이상, 무작위 에픽~유니크 유물 획득</t>
+          <t>다른 상자도 열어본다.</t>
         </is>
       </c>
     </row>
     <row r="1674">
       <c r="A1674" t="inlineStr">
         <is>
-          <t>data.event.event_06.choice_2_name</t>
+          <t>data.event.event_06_a.choice_2_name</t>
         </is>
       </c>
       <c r="C1674" t="inlineStr">
         <is>
-          <t>지나친다.</t>
+          <t>그만둔다.</t>
         </is>
       </c>
     </row>
     <row r="1675">
       <c r="A1675" t="inlineStr">
         <is>
-          <t>data.event.event_06.description.97db0284</t>
+          <t>data.event.event_06_a.description.97db0284</t>
         </is>
       </c>
       <c r="C1675" t="inlineStr">
@@ -49221,115 +49228,119 @@
     <row r="1676">
       <c r="A1676" t="inlineStr">
         <is>
-          <t>data.event.event_06_a.choice_1_name</t>
+          <t>data.event.event_06_b.choice_1_name</t>
         </is>
       </c>
       <c r="C1676" t="inlineStr">
         <is>
-          <t>다른 상자도 열어본다.</t>
+          <t>하나 더 열어본다.</t>
         </is>
       </c>
     </row>
     <row r="1677">
       <c r="A1677" t="inlineStr">
         <is>
-          <t>data.event.event_06_a.choice_2_name</t>
+          <t>data.event.event_06_b.description</t>
         </is>
       </c>
       <c r="C1677" t="inlineStr">
+        <is>
+          <t>주사위 14 이상
+무작위 에픽 유물 획득
+실패 : 생명력 5 감소</t>
+        </is>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>data.event.event_06_b.choice_2_name</t>
+        </is>
+      </c>
+      <c r="C1678" t="inlineStr">
         <is>
           <t>그만둔다.</t>
         </is>
       </c>
     </row>
-    <row r="1678">
-      <c r="A1678" t="inlineStr">
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
         <is>
-          <t>data.event.event_06_a.description.97db0284</t>
+          <t>data.event.event_06_b.description.97db0284</t>
         </is>
       </c>
-      <c r="C1678" t="inlineStr">
+      <c r="C1679" t="inlineStr">
         <is>
           <t>이벤트 종료</t>
         </is>
       </c>
     </row>
-    <row r="1679">
-      <c r="A1679" t="inlineStr">
-        <is>
-          <t>data.event.event_06_b.choice_1_name</t>
-        </is>
-      </c>
-      <c r="C1679" t="inlineStr">
-        <is>
-          <t>하나 더 열어본다.</t>
-        </is>
-      </c>
-    </row>
     <row r="1680">
       <c r="A1680" t="inlineStr">
         <is>
-          <t>data.event.event_06_b.description</t>
+          <t>data.event.event_07_a.choice_1_name</t>
         </is>
       </c>
       <c r="C1680" t="inlineStr">
         <is>
-          <t>주사위 14 이상, 무작위 에픽 유물 획득</t>
+          <t>계속 파헤친다.</t>
         </is>
       </c>
     </row>
     <row r="1681">
       <c r="A1681" t="inlineStr">
         <is>
-          <t>data.event.event_06_b.choice_2_name</t>
+          <t>data.event.event_07_a.description</t>
         </is>
       </c>
       <c r="C1681" t="inlineStr">
         <is>
-          <t>그만둔다.</t>
+          <t>예측 : 앞면 or 뒷면
+레드 더스티움 30 획득</t>
         </is>
       </c>
     </row>
     <row r="1682">
       <c r="A1682" t="inlineStr">
         <is>
-          <t>data.event.event_06_b.description.97db0284</t>
+          <t>data.event.event_07_a.choice_2_name</t>
         </is>
       </c>
       <c r="C1682" t="inlineStr">
         <is>
-          <t>이벤트 종료</t>
+          <t>그만한다.</t>
         </is>
       </c>
     </row>
     <row r="1683">
       <c r="A1683" t="inlineStr">
         <is>
-          <t>data.event.event_07_a.choice_1_name</t>
+          <t>data.event.event_07_b.choice_1_name</t>
         </is>
       </c>
       <c r="C1683" t="inlineStr">
         <is>
-          <t>계속 파헤친다.</t>
+          <t>다시 파헤친다.</t>
         </is>
       </c>
     </row>
     <row r="1684">
       <c r="A1684" t="inlineStr">
         <is>
-          <t>data.event.event_07_a.description</t>
+          <t>data.event.event_07_b.description</t>
         </is>
       </c>
       <c r="C1684" t="inlineStr">
         <is>
-          <t>예측 성공 시, 레드 더스티움 30 획득</t>
+          <t>예측 : 앞면 or 뒷면
+레드 더스티움 35 획득</t>
         </is>
       </c>
     </row>
     <row r="1685">
       <c r="A1685" t="inlineStr">
         <is>
-          <t>data.event.event_07_a.choice_2_name</t>
+          <t>data.event.event_07_b.choice_2_name</t>
         </is>
       </c>
       <c r="C1685" t="inlineStr">
@@ -49341,602 +49352,646 @@
     <row r="1686">
       <c r="A1686" t="inlineStr">
         <is>
-          <t>data.event.event_07_b.choice_1_name</t>
+          <t>data.event.event_08.name</t>
         </is>
       </c>
       <c r="C1686" t="inlineStr">
         <is>
-          <t>다시 파헤친다.</t>
+          <t>고대의 각인</t>
         </is>
       </c>
     </row>
     <row r="1687">
       <c r="A1687" t="inlineStr">
         <is>
-          <t>data.event.event_07_b.description</t>
+          <t>data.event.event_08.choice_1_name</t>
         </is>
       </c>
       <c r="C1687" t="inlineStr">
         <is>
-          <t>예측 성공 시, 레드 더스티움 35 획득</t>
+          <t>{Party1Name}{이가} 다가간다.</t>
         </is>
       </c>
     </row>
     <row r="1688">
       <c r="A1688" t="inlineStr">
         <is>
-          <t>data.event.event_07_b.choice_2_name</t>
+          <t>data.event.event_08.choice_2_name</t>
         </is>
       </c>
       <c r="C1688" t="inlineStr">
         <is>
-          <t>그만한다.</t>
+          <t>{Party2Name}{이가} 다가간다.</t>
         </is>
       </c>
     </row>
     <row r="1689">
       <c r="A1689" t="inlineStr">
         <is>
-          <t>data.event.event_08.name</t>
+          <t>data.event.event_08.choice_3_name</t>
         </is>
       </c>
       <c r="C1689" t="inlineStr">
         <is>
-          <t>고대의 각인</t>
+          <t>{Party3Name}{이가} 다가간다.</t>
         </is>
       </c>
     </row>
     <row r="1690">
       <c r="A1690" t="inlineStr">
         <is>
-          <t>data.event.event_08.choice_1_name</t>
+          <t>data.event.event_08_a.choice_1_name</t>
         </is>
       </c>
       <c r="C1690" t="inlineStr">
         <is>
-          <t>{Party1Name}{이가} 만진다.</t>
+          <t>잔향에 귀 기울인다.</t>
         </is>
       </c>
     </row>
     <row r="1691">
       <c r="A1691" t="inlineStr">
         <is>
-          <t>data.event.event_08.choice_2_name</t>
+          <t>data.event.event_08_a.description</t>
         </is>
       </c>
       <c r="C1691" t="inlineStr">
         <is>
-          <t>{Party2Name}{이가} 만진다.</t>
+          <t>{PartyName}의 생명력 5 회복</t>
         </is>
       </c>
     </row>
     <row r="1692">
       <c r="A1692" t="inlineStr">
         <is>
-          <t>data.event.event_08.choice_3_name</t>
+          <t>data.event.event_08_a.choice_2_name</t>
         </is>
       </c>
       <c r="C1692" t="inlineStr">
         <is>
-          <t>{Party3Name}{이가} 만진다.</t>
+          <t>희미한 기억을 일깨운다.</t>
         </is>
       </c>
     </row>
     <row r="1693">
       <c r="A1693" t="inlineStr">
         <is>
-          <t>data.event.event_08_a.choice_1_name</t>
+          <t>data.event.event_08_a.choice_2_disabled_description</t>
         </is>
       </c>
       <c r="C1693" t="inlineStr">
         <is>
-          <t>잔향에 귀 기울인다.</t>
+          <t>레드 더스티움 부족</t>
         </is>
       </c>
     </row>
     <row r="1694">
       <c r="A1694" t="inlineStr">
         <is>
-          <t>data.event.event_08_a.description</t>
+          <t>data.event.event_08_a.choice_3_name</t>
         </is>
       </c>
       <c r="C1694" t="inlineStr">
         <is>
-          <t>{PartyName}의 생명력 5 회복</t>
+          <t>강렬한 기억을 일깨운다.</t>
         </is>
       </c>
     </row>
     <row r="1695">
       <c r="A1695" t="inlineStr">
         <is>
-          <t>data.event.event_08_a.choice_2_name</t>
+          <t>data.event.event_08_a.choice_3_disabled_description</t>
         </is>
       </c>
       <c r="C1695" t="inlineStr">
         <is>
-          <t>희미한 기억을 일깨운다.</t>
+          <t>레드 더스티움 부족</t>
         </is>
       </c>
     </row>
     <row r="1696">
       <c r="A1696" t="inlineStr">
         <is>
-          <t>data.event.event_08_a.description.b220488f</t>
+          <t>data.event.event_09.description.0c0e6cc0</t>
         </is>
       </c>
       <c r="C1696" t="inlineStr">
         <is>
-          <t>레드 더스티움 20 소모, 레어~에픽 기억 발현</t>
+          <t>모든 파티원 최대 마나 2 증가</t>
         </is>
       </c>
     </row>
     <row r="1697">
       <c r="A1697" t="inlineStr">
         <is>
-          <t>data.event.event_08_a.choice_2_disabled_description</t>
+          <t>data.event.event_09.description.3ef68afc</t>
         </is>
       </c>
       <c r="C1697" t="inlineStr">
         <is>
-          <t>레드 더스티움 부족</t>
+          <t>침식도 20 감소</t>
         </is>
       </c>
     </row>
     <row r="1698">
       <c r="A1698" t="inlineStr">
         <is>
-          <t>data.event.event_08_a.choice_3_name</t>
+          <t>data.event.event_10.name</t>
         </is>
       </c>
       <c r="C1698" t="inlineStr">
         <is>
-          <t>강렬한 기억을 일깨운다.</t>
+          <t>의문의 이방인</t>
         </is>
       </c>
     </row>
     <row r="1699">
       <c r="A1699" t="inlineStr">
         <is>
-          <t>data.event.event_08_a.description.60a173d6</t>
+          <t>data.event.event_10.choice_1_name</t>
         </is>
       </c>
       <c r="C1699" t="inlineStr">
         <is>
-          <t>레드 더스티움 45 소모, 에픽~유니크 기억 발현</t>
+          <t>생명을 대가로 바친다.</t>
         </is>
       </c>
     </row>
     <row r="1700">
       <c r="A1700" t="inlineStr">
         <is>
-          <t>data.event.event_08_a.choice_3_disabled_description</t>
+          <t>data.event.event_10.description</t>
         </is>
       </c>
       <c r="C1700" t="inlineStr">
         <is>
-          <t>레드 더스티움 부족</t>
+          <t>전체 생명력 5 감소
+무작위 레어~유니크 유물 획득</t>
         </is>
       </c>
     </row>
     <row r="1701">
       <c r="A1701" t="inlineStr">
         <is>
-          <t>data.event.event_09.description.0c0e6cc0</t>
+          <t>data.event.event_10.choice_1_disabled_description</t>
         </is>
       </c>
       <c r="C1701" t="inlineStr">
         <is>
-          <t>모든 파티원 최대 마나 2 증가</t>
+          <t>생명력 부족</t>
         </is>
       </c>
     </row>
     <row r="1702">
       <c r="A1702" t="inlineStr">
         <is>
-          <t>data.event.event_09.description.3ef68afc</t>
+          <t>data.event.event_10.choice_2_name</t>
         </is>
       </c>
       <c r="C1702" t="inlineStr">
         <is>
-          <t>침식도 20 감소</t>
+          <t>운명에 맡긴다.</t>
         </is>
       </c>
     </row>
     <row r="1703">
       <c r="A1703" t="inlineStr">
         <is>
-          <t>data.event.event_10.name</t>
+          <t>data.event.event_10.choice_3_name</t>
         </is>
       </c>
       <c r="C1703" t="inlineStr">
         <is>
-          <t>의문의 이방인</t>
+          <t>침식을 받아들인다.</t>
         </is>
       </c>
     </row>
     <row r="1704">
       <c r="A1704" t="inlineStr">
         <is>
-          <t>data.event.event_10.choice_1_name</t>
+          <t>ui.menupanel.menupanel.button.record.record_text.6db3f2f6</t>
         </is>
       </c>
       <c r="C1704" t="inlineStr">
         <is>
-          <t>생명을 대가로 바친다.</t>
+          <t>기록</t>
         </is>
       </c>
     </row>
     <row r="1705">
       <c r="A1705" t="inlineStr">
         <is>
-          <t>data.event.event_10.description</t>
+          <t>ui.battle.roomroot.eventroom.canvas.dataeventroot.eventcoinflippresenter.detailtext.38d9d6cb</t>
         </is>
       </c>
       <c r="C1705" t="inlineStr">
         <is>
-          <t>전체 생명력 5감소, 무작위 레어~유니크 유물 획득</t>
+          <t>성공</t>
         </is>
       </c>
     </row>
     <row r="1706">
       <c r="A1706" t="inlineStr">
         <is>
-          <t>data.event.event_10.choice_1_disabled_description</t>
+          <t>ui.lobby.text.eafccb6c</t>
         </is>
       </c>
       <c r="C1706" t="inlineStr">
         <is>
-          <t>생명력 부족</t>
+          <t>스탯이름</t>
         </is>
       </c>
     </row>
     <row r="1707">
       <c r="A1707" t="inlineStr">
         <is>
-          <t>data.event.event_10.choice_2_name</t>
+          <t>ui.lobby.canvas.positionpanel.ready.panel.ready_panel.playbutton.playtext.bde74899</t>
         </is>
       </c>
       <c r="C1707" t="inlineStr">
         <is>
-          <t>운명에 맡긴다.</t>
+          <t>탐사</t>
         </is>
       </c>
     </row>
     <row r="1708">
       <c r="A1708" t="inlineStr">
         <is>
-          <t>data.event.event_10.choice_3_name</t>
+          <t>ui.title.canvas.buttongroup.recodebutton.text.6db3f2f6</t>
         </is>
       </c>
       <c r="C1708" t="inlineStr">
         <is>
-          <t>침식을 받아들인다.</t>
+          <t>기록</t>
         </is>
       </c>
     </row>
     <row r="1709">
       <c r="A1709" t="inlineStr">
         <is>
-          <t>data.event.event_10.description.82b5c6fa</t>
+          <t>ui.title.canvas.buttongroup.quitbutton.text.ec48e3e4</t>
         </is>
       </c>
       <c r="C1709" t="inlineStr">
         <is>
-          <t>침식도 20 증가, 무작위 일반~유니크 유물 획득</t>
+          <t>종료</t>
         </is>
       </c>
     </row>
     <row r="1710">
       <c r="A1710" t="inlineStr">
         <is>
-          <t>ui.menupanel.menupanel.button.record.record_text.6db3f2f6</t>
+          <t>ui.assets.project.scripts.battlecharacterpanelui.text.4e152716</t>
         </is>
       </c>
       <c r="C1710" t="inlineStr">
         <is>
-          <t>기록</t>
+          <t>지속</t>
         </is>
       </c>
     </row>
     <row r="1711">
       <c r="A1711" t="inlineStr">
         <is>
-          <t>ui.battle.roomroot.eventroom.canvas.dataeventroot.eventcoinflippresenter.detailtext.38d9d6cb</t>
+          <t>data.event.event_07.description.97db0284</t>
         </is>
       </c>
       <c r="C1711" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>이벤트 종료</t>
         </is>
       </c>
     </row>
     <row r="1712">
       <c r="A1712" t="inlineStr">
         <is>
-          <t>ui.lobby.text.eafccb6c</t>
+          <t>data.event.event_07_a.description.97db0284</t>
         </is>
       </c>
       <c r="C1712" t="inlineStr">
         <is>
-          <t>스탯이름</t>
+          <t>이벤트 종료</t>
         </is>
       </c>
     </row>
     <row r="1713">
       <c r="A1713" t="inlineStr">
         <is>
-          <t>ui.lobby.canvas.positionpanel.ready.panel.ready_panel.playbutton.playtext.bde74899</t>
+          <t>data.event.event_07_b.description.97db0284</t>
         </is>
       </c>
       <c r="C1713" t="inlineStr">
         <is>
-          <t>탐사</t>
+          <t>이벤트 종료</t>
         </is>
       </c>
     </row>
     <row r="1714">
       <c r="A1714" t="inlineStr">
         <is>
-          <t>ui.title.canvas.buttongroup.recodebutton.text.6db3f2f6</t>
+          <t>ui.battle.roomroot.eventroom.canvas.dataeventroot.eventcoinflippresenter.headsbutton.text_tmp.da9f7c01</t>
         </is>
       </c>
       <c r="C1714" t="inlineStr">
         <is>
-          <t>기록</t>
+          <t>앞</t>
         </is>
       </c>
     </row>
     <row r="1715">
       <c r="A1715" t="inlineStr">
         <is>
-          <t>ui.title.canvas.buttongroup.quitbutton.text.ec48e3e4</t>
+          <t>ui.battle.roomroot.eventroom.canvas.dataeventroot.eventcoinflippresenter.tailsbutton.text_tmp.a05523b3</t>
         </is>
       </c>
       <c r="C1715" t="inlineStr">
         <is>
-          <t>종료</t>
+          <t>뒤</t>
         </is>
       </c>
     </row>
     <row r="1716">
       <c r="A1716" t="inlineStr">
         <is>
-          <t>ui.assets.project.scripts.battlecharacterpanelui.text.4e152716</t>
-        </is>
-      </c>
-      <c r="C1716" t="inlineStr">
-        <is>
-          <t>지속</t>
-        </is>
-      </c>
-    </row>
-    <row r="1717">
-      <c r="A1717" t="inlineStr">
-        <is>
-          <t>data.event.event_07.description.97db0284</t>
-        </is>
-      </c>
-      <c r="C1717" t="inlineStr">
-        <is>
-          <t>이벤트 종료</t>
-        </is>
-      </c>
-    </row>
-    <row r="1718">
-      <c r="A1718" t="inlineStr">
-        <is>
-          <t>data.event.event_07_a.description.97db0284</t>
-        </is>
-      </c>
-      <c r="C1718" t="inlineStr">
-        <is>
-          <t>이벤트 종료</t>
-        </is>
-      </c>
-    </row>
-    <row r="1719">
-      <c r="A1719" t="inlineStr">
-        <is>
-          <t>data.event.event_07_b.description.97db0284</t>
-        </is>
-      </c>
-      <c r="C1719" t="inlineStr">
-        <is>
-          <t>이벤트 종료</t>
-        </is>
-      </c>
-    </row>
-    <row r="1720">
-      <c r="A1720" t="inlineStr">
-        <is>
-          <t>ui.battle.roomroot.eventroom.canvas.dataeventroot.eventcoinflippresenter.headsbutton.text_tmp.da9f7c01</t>
-        </is>
-      </c>
-      <c r="C1720" t="inlineStr">
-        <is>
-          <t>앞</t>
-        </is>
-      </c>
-    </row>
-    <row r="1721">
-      <c r="A1721" t="inlineStr">
-        <is>
-          <t>ui.battle.roomroot.eventroom.canvas.dataeventroot.eventcoinflippresenter.tailsbutton.text_tmp.a05523b3</t>
-        </is>
-      </c>
-      <c r="C1721" t="inlineStr">
-        <is>
-          <t>뒤</t>
-        </is>
-      </c>
-    </row>
-    <row r="1722">
-      <c r="A1722" t="inlineStr">
-        <is>
           <t>ui.battle.explorationreportstagename.33aee447</t>
         </is>
       </c>
-      <c r="C1722" t="inlineStr">
+      <c r="C1716" t="inlineStr">
         <is>
           <t>소요 시간
 00:00:00</t>
         </is>
       </c>
     </row>
-    <row r="1723">
-      <c r="A1723" t="inlineStr">
+    <row r="1717">
+      <c r="A1717" t="inlineStr">
         <is>
           <t>ui.battle.explorationreportstageresult.6fd57db4</t>
         </is>
       </c>
-      <c r="C1723" t="inlineStr">
+      <c r="C1717" t="inlineStr">
         <is>
           <t>침식도
 0</t>
         </is>
       </c>
     </row>
+    <row r="1718">
+      <c r="A1718" t="inlineStr">
+        <is>
+          <t>ui.lobby.text_tmp.fc777a3e</t>
+        </is>
+      </c>
+      <c r="C1718" t="inlineStr">
+        <is>
+          <t>침식</t>
+        </is>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="inlineStr">
+        <is>
+          <t>ui.lobby.text_tmp.6c00dd0f</t>
+        </is>
+      </c>
+      <c r="C1719" t="inlineStr">
+        <is>
+          <t>공명</t>
+        </is>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="inlineStr">
+        <is>
+          <t>ui.lobby.text_tmp.bde74899</t>
+        </is>
+      </c>
+      <c r="C1720" t="inlineStr">
+        <is>
+          <t>탐사</t>
+        </is>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="inlineStr">
+        <is>
+          <t>ui.lobby.text_tmp.9873c6b9</t>
+        </is>
+      </c>
+      <c r="C1721" t="inlineStr">
+        <is>
+          <t>연구</t>
+        </is>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="inlineStr">
+        <is>
+          <t>ui.exploration.result.monster_kills</t>
+        </is>
+      </c>
+      <c r="C1722" t="inlineStr">
+        <is>
+          <t>몬스터 처치</t>
+        </is>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="inlineStr">
+        <is>
+          <t>ui.exploration.result.damage_dealt</t>
+        </is>
+      </c>
+      <c r="C1723" t="inlineStr">
+        <is>
+          <t>입힌 피해량</t>
+        </is>
+      </c>
+    </row>
     <row r="1724">
       <c r="A1724" t="inlineStr">
         <is>
-          <t>ui.lobby.text_tmp.fc777a3e</t>
+          <t>ui.exploration.result.damage_taken</t>
         </is>
       </c>
       <c r="C1724" t="inlineStr">
         <is>
-          <t>침식</t>
+          <t>받은 피해량</t>
         </is>
       </c>
     </row>
     <row r="1725">
       <c r="A1725" t="inlineStr">
         <is>
-          <t>ui.lobby.text_tmp.6c00dd0f</t>
+          <t>ui.exploration.result.buffs_applied</t>
         </is>
       </c>
       <c r="C1725" t="inlineStr">
         <is>
-          <t>공명</t>
+          <t>버프 부여량</t>
         </is>
       </c>
     </row>
     <row r="1726">
       <c r="A1726" t="inlineStr">
         <is>
-          <t>ui.lobby.text_tmp.bde74899</t>
+          <t>ui.exploration.result.incapacitated</t>
         </is>
       </c>
       <c r="C1726" t="inlineStr">
         <is>
-          <t>탐사</t>
+          <t>전투불능 횟수</t>
         </is>
       </c>
     </row>
     <row r="1727">
       <c r="A1727" t="inlineStr">
         <is>
-          <t>ui.lobby.text_tmp.9873c6b9</t>
+          <t>ui.exploration.result.title</t>
         </is>
       </c>
       <c r="C1727" t="inlineStr">
         <is>
-          <t>연구</t>
+          <t>탐사 보고</t>
         </is>
       </c>
     </row>
     <row r="1728">
       <c r="A1728" t="inlineStr">
         <is>
-          <t>ui.exploration.result.monster_kills</t>
+          <t>ui.exploration.result.elapsed_time</t>
         </is>
       </c>
       <c r="C1728" t="inlineStr">
         <is>
-          <t>몬스터 처치</t>
+          <t>소요 시간</t>
         </is>
       </c>
     </row>
     <row r="1729">
       <c r="A1729" t="inlineStr">
         <is>
-          <t>ui.exploration.result.damage_dealt</t>
+          <t>data.event.event_04.description.69f4aca0</t>
         </is>
       </c>
       <c r="C1729" t="inlineStr">
         <is>
-          <t>입힌 피해량</t>
+          <t>레드 더스티움 30 소모
+무작위 레어~유니크 기억 발현</t>
         </is>
       </c>
     </row>
     <row r="1730">
       <c r="A1730" t="inlineStr">
         <is>
-          <t>ui.exploration.result.damage_taken</t>
+          <t>data.event.event_05.description.d1d72d3e</t>
         </is>
       </c>
       <c r="C1730" t="inlineStr">
         <is>
-          <t>받은 피해량</t>
+          <t>주사위 8 이상
+무작위 레어~에픽 유물 획득</t>
         </is>
       </c>
     </row>
     <row r="1731">
       <c r="A1731" t="inlineStr">
         <is>
-          <t>ui.exploration.result.buffs_applied</t>
+          <t>data.event.event_05.description.1ab191c7</t>
         </is>
       </c>
       <c r="C1731" t="inlineStr">
         <is>
-          <t>버프 부여량</t>
+          <t>주사위 10 이상
+무작위 에픽~유니크 유물 획득</t>
         </is>
       </c>
     </row>
     <row r="1732">
       <c r="A1732" t="inlineStr">
         <is>
-          <t>ui.exploration.result.incapacitated</t>
+          <t>data.event.event_08.description</t>
         </is>
       </c>
       <c r="C1732" t="inlineStr">
         <is>
-          <t>전투불능 횟수</t>
+          <t>{Party1Name}의 생명력 회복 또는 기억 발현</t>
         </is>
       </c>
     </row>
     <row r="1733">
       <c r="A1733" t="inlineStr">
         <is>
-          <t>ui.exploration.result.title</t>
+          <t>data.event.event_08.description.f0849093</t>
         </is>
       </c>
       <c r="C1733" t="inlineStr">
         <is>
-          <t>탐사 보고</t>
+          <t>{Party2Name}의 생명력 회복 또는 기억 발현</t>
         </is>
       </c>
     </row>
     <row r="1734">
       <c r="A1734" t="inlineStr">
         <is>
-          <t>ui.exploration.result.elapsed_time</t>
+          <t>data.event.event_08.description.71cb48a8</t>
         </is>
       </c>
       <c r="C1734" t="inlineStr">
         <is>
-          <t>소요 시간</t>
+          <t>{Party3Name}의 생명력 회복 또는 기억 발현</t>
         </is>
       </c>
     </row>
     <row r="1735">
       <c r="A1735" t="inlineStr">
         <is>
-          <t>data.event.event_10.description.ba57ea67</t>
+          <t>data.event.event_08_a.description.84fa59c3</t>
         </is>
       </c>
       <c r="C1735" t="inlineStr">
         <is>
-          <t>예측 성공 시, 무작위 유물 획득</t>
+          <t>레드 더스티움 20 소모
+레어~에픽 기억 발현</t>
+        </is>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" t="inlineStr">
+        <is>
+          <t>data.event.event_08_a.description.f0ad2cb4</t>
+        </is>
+      </c>
+      <c r="C1736" t="inlineStr">
+        <is>
+          <t>레드 더스티움 45 소모
+에픽~유니크 기억 발현</t>
+        </is>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" t="inlineStr">
+        <is>
+          <t>data.event.event_10.description.ea5b316b</t>
+        </is>
+      </c>
+      <c r="C1737" t="inlineStr">
+        <is>
+          <t>예측 : 앞면 or 뒷면
+무작위 유물 획득</t>
+        </is>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="inlineStr">
+        <is>
+          <t>data.event.event_10.description.da2e3146</t>
+        </is>
+      </c>
+      <c r="C1738" t="inlineStr">
+        <is>
+          <t>침식도 20 증가
+무작위 일반~유니크 유물 획득</t>
         </is>
       </c>
     </row>

--- a/Assets/ExcelSource/Localization.xlsx
+++ b/Assets/ExcelSource/Localization.xlsx
@@ -49102,19 +49102,8 @@
       <c r="C1698" s="0" t="inlineStr">
         <is>
           <t>주사위 6 이상
-무작위 일반~레어 유물 획득</t>
-        </is>
-      </c>
-      <c r="D1698" s="0" t="inlineStr">
-        <is>
-          <t>Roll 6 or higher
-Gain a random Common–Rare relic</t>
-        </is>
-      </c>
-      <c r="F1698" s="0" t="inlineStr">
-        <is>
-          <t>ダイス6以上
-ランダムなコモン～レアの遺物を獲得</t>
+성공 : 무작위 일반~레어 유물 획득
+실패 : 이벤트 종료</t>
         </is>
       </c>
     </row>
@@ -49132,19 +49121,8 @@
       <c r="C1699" s="0" t="inlineStr">
         <is>
           <t>주사위 8 이상
-무작위 레어~에픽 유물 획득</t>
-        </is>
-      </c>
-      <c r="D1699" s="0" t="inlineStr">
-        <is>
-          <t>Roll 8 or higher
-Gain a random Rare–Epic relic</t>
-        </is>
-      </c>
-      <c r="F1699" s="0" t="inlineStr">
-        <is>
-          <t>ダイス8以上
-ランダムなレア～エピックの遺物を獲得</t>
+성공 : 무작위 레어~에픽 유물 획득
+실패 : 이벤트 종료</t>
         </is>
       </c>
     </row>
@@ -49162,19 +49140,8 @@
       <c r="C1700" s="0" t="inlineStr">
         <is>
           <t>주사위 10 이상
-무작위 에픽~유니크 유물 획득</t>
-        </is>
-      </c>
-      <c r="D1700" s="0" t="inlineStr">
-        <is>
-          <t>Roll 10 or higher
-Gain a random Epic–Unique relic</t>
-        </is>
-      </c>
-      <c r="F1700" s="0" t="inlineStr">
-        <is>
-          <t>ダイス10以上
-ランダムなエピック～ユニークの遺物を獲得</t>
+성공 : 무작위 에픽~유니크 유물 획득
+실패 : 이벤트 종료</t>
         </is>
       </c>
     </row>
@@ -49192,22 +49159,8 @@
       <c r="C1701" s="0" t="inlineStr">
         <is>
           <t>주사위 6 이상
-레드 더스티움 30 획득
+성공 : 레드 더스티움 30 획득
 실패 : 생명력 5 감소</t>
-        </is>
-      </c>
-      <c r="D1701" s="0" t="inlineStr">
-        <is>
-          <t>Roll 6 or higher
-Gain 30 Red Dustium
-Failure: Lose 5 HP</t>
-        </is>
-      </c>
-      <c r="F1701" s="0" t="inlineStr">
-        <is>
-          <t>ダイス6以上
-レッドダスティウムを30獲得
-失敗：HPが5減少</t>
         </is>
       </c>
     </row>
@@ -49252,22 +49205,8 @@
       <c r="C1703" s="0" t="inlineStr">
         <is>
           <t>주사위 10 이상
-레드 더스티움 50 획득
+성공 : 레드 더스티움 50 획득
 실패 : 생명력 5 감소</t>
-        </is>
-      </c>
-      <c r="D1703" s="0" t="inlineStr">
-        <is>
-          <t>Roll 10 or higher
-Gain 50 Red Dustium
-Failure: Lose 5 HP</t>
-        </is>
-      </c>
-      <c r="F1703" s="0" t="inlineStr">
-        <is>
-          <t>ダイス10以上
-レッドダスティウムを50獲得
-失敗：HPが5減少</t>
         </is>
       </c>
     </row>
@@ -49312,7 +49251,7 @@
       <c r="C1705" s="0" t="inlineStr">
         <is>
           <t>주사위 12 이상
-무작위 에픽 유물 획득
+성공 : 무작위 에픽 유물 획득
 실패 : 생명력 5 감소</t>
         </is>
       </c>
@@ -49357,20 +49296,8 @@
       </c>
       <c r="C1707" s="0" t="inlineStr">
         <is>
-          <t>예측 : 앞면 or 뒷면
+          <t>주사위 6 이상
 레드 더스티움 25 획득</t>
-        </is>
-      </c>
-      <c r="D1707" s="0" t="inlineStr">
-        <is>
-          <t>Predict: Heads or Tails
-Gain 25 Red Dustium</t>
-        </is>
-      </c>
-      <c r="F1707" s="0" t="inlineStr">
-        <is>
-          <t>予測：表か裏
-レッドダスティウムを25獲得</t>
         </is>
       </c>
     </row>
@@ -49414,20 +49341,8 @@
       </c>
       <c r="C1709" s="0" t="inlineStr">
         <is>
-          <t>예측 : 앞면 or 뒷면
+          <t>주사위 8 이상
 레드 더스티움 30 획득</t>
-        </is>
-      </c>
-      <c r="D1709" s="0" t="inlineStr">
-        <is>
-          <t>Predict: Heads or Tails
-Gain 30 Red Dustium</t>
-        </is>
-      </c>
-      <c r="F1709" s="0" t="inlineStr">
-        <is>
-          <t>予測：表か裏
-レッドダスティウムを30獲得</t>
         </is>
       </c>
     </row>
@@ -49471,20 +49386,8 @@
       </c>
       <c r="C1711" s="0" t="inlineStr">
         <is>
-          <t>예측 : 앞면 or 뒷면
+          <t>주사위 10 이상
 레드 더스티움 35 획득</t>
-        </is>
-      </c>
-      <c r="D1711" s="0" t="inlineStr">
-        <is>
-          <t>Predict: Heads or Tails
-Gain 35 Red Dustium</t>
-        </is>
-      </c>
-      <c r="F1711" s="0" t="inlineStr">
-        <is>
-          <t>予測：表か裏
-レッドダスティウムを35獲得</t>
         </is>
       </c>
     </row>
@@ -49807,20 +49710,9 @@
       </c>
       <c r="C1723" s="0" t="inlineStr">
         <is>
-          <t>예측 : 앞면 or 뒷면
-무작위 유물 획득</t>
-        </is>
-      </c>
-      <c r="D1723" s="0" t="inlineStr">
-        <is>
-          <t>Predict: Heads or Tails
-Gain a random relic</t>
-        </is>
-      </c>
-      <c r="F1723" s="0" t="inlineStr">
-        <is>
-          <t>予測：表か裏
-ランダムな遺物を獲得</t>
+          <t>주사위 9 이상
+성공 : 무작위 유물 획득
+실패 : 이벤트 종료</t>
         </is>
       </c>
     </row>

--- a/Assets/ExcelSource/Localization.xlsx
+++ b/Assets/ExcelSource/Localization.xlsx
@@ -50231,6 +50231,102 @@
         </is>
       </c>
     </row>
+    <row r="1745">
+      <c r="A1745" t="inlineStr">
+        <is>
+          <t>ui.battle.heal_text.fa6ad4a6</t>
+        </is>
+      </c>
+      <c r="C1745" t="inlineStr">
+        <is>
+          <t>생명력을 30% 회복하고 침식도가 10 감소합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="inlineStr">
+        <is>
+          <t>ui.battle.meditation_text.b83e0a88</t>
+        </is>
+      </c>
+      <c r="C1746" t="inlineStr">
+        <is>
+          <t>무작위 기억 중 발현할 기억을 1개 선택합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="inlineStr">
+        <is>
+          <t>ui.battle.heal.1fac8b81</t>
+        </is>
+      </c>
+      <c r="C1747" t="inlineStr">
+        <is>
+          <t>잠시 숨을 고르며 몸과 마음의 안정을 되찾았습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="inlineStr">
+        <is>
+          <t>ui.battle.meditation.bafe8da3</t>
+        </is>
+      </c>
+      <c r="C1748" t="inlineStr">
+        <is>
+          <t>고요한 명상 속에서 한순간 기억이 번뜩였습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" t="inlineStr">
+        <is>
+          <t>ui.battle.roomroot.restroom.choicecanvas.healbutton.text_tmp.26090c1a</t>
+        </is>
+      </c>
+      <c r="C1749" t="inlineStr">
+        <is>
+          <t>휴식</t>
+        </is>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" t="inlineStr">
+        <is>
+          <t>ui.battle.text_tmp.6d912c93</t>
+        </is>
+      </c>
+      <c r="C1750" t="inlineStr">
+        <is>
+          <t>명상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" t="inlineStr">
+        <is>
+          <t>ui.battle.name.1a7fa664</t>
+        </is>
+      </c>
+      <c r="C1751" t="inlineStr">
+        <is>
+          <t>슬롯이름</t>
+        </is>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" t="inlineStr">
+        <is>
+          <t>ui.assets.project.scripts.gameplay.scene.battle.restroom.restroomcontroller.text.45e08243</t>
+        </is>
+      </c>
+      <c r="C1752" t="inlineStr">
+        <is>
+          <t>발현할 기억이 없습니다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
